--- a/03_内部設計/022-クラス仕様書/jsp/商品検索結果画面のJSP仕様書.xlsx
+++ b/03_内部設計/022-クラス仕様書/jsp/商品検索結果画面のJSP仕様書.xlsx
@@ -3,16 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D75274B-0457-42A4-A9B9-91A1EC17B1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E3CF82-5F0C-4A99-B2AB-4359AB7A5A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JSP仕様" sheetId="4" r:id="rId1"/>
     <sheet name="（データリスト）" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">JSP仕様!$A$1:$BC$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">JSP仕様!$A$1:$BC$44</definedName>
     <definedName name="部品種別">OFFSET('（データリスト）'!$A$1,0,0,COUNTA('（データリスト）'!$A:$A),1)</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
@@ -256,34 +256,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>検索結果が2ページ以上あり、かつ、現在が2ページ目以降の場合はリンク処理を行う。</t>
-    <rPh sb="0" eb="4">
-      <t>ケンサクケッカ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>イコウ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>color</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -304,22 +276,6 @@
   </si>
   <si>
     <t>page</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>現在のページ番号以外を、リンク処理をして表示する。</t>
-    <rPh sb="0" eb="2">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>バンゴウイガイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ヒョウジ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -393,13 +349,6 @@
       <t>カカク</t>
     </rPh>
     <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>検索結果が2ページ以上あり、かつ、現在が最後のページでない場合はリンク処理を行う。</t>
-    <rPh sb="20" eb="22">
-      <t>サイゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>オススメ</t>
@@ -511,6 +460,72 @@
     </rPh>
     <rPh sb="44" eb="46">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索結果が2ページ以上あり、かつ、現在が2ページ目以降の場合はリンク処理を行う。
+検索結果が1ページ分しかないときは、文字列として表示する。</t>
+    <rPh sb="0" eb="4">
+      <t>ケンサクケッカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="41" eb="45">
+      <t>ケンサクケッカ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="59" eb="62">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在のページ番号以外を、リンク処理をして表示する。
+検索結果が1ページ分しかないときは、文字列として表示する。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>バンゴウイガイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索結果が2ページ以上あり、かつ、現在が最後のページでない場合はリンク処理を行う。
+検索結果が1ページ分しかないときは、文字列として表示する。</t>
+    <rPh sb="20" eb="22">
+      <t>サイゴ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -798,7 +813,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1027,9 +1042,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1054,15 +1066,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1117,17 +1141,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1475,12 +1541,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:HY42"/>
-  <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="14.4"/>
+  <dimension ref="A1:HY45"/>
+  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="22" width="2.453125" style="2"/>
-    <col min="23" max="30" width="2.7265625" style="2" customWidth="1"/>
-    <col min="31" max="16384" width="2.453125" style="2"/>
+    <col min="1" max="22" width="2.5" style="2"/>
+    <col min="23" max="30" width="2.75" style="2" customWidth="1"/>
+    <col min="31" max="16384" width="2.5" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:233" ht="15" customHeight="1">
@@ -1749,7 +1815,7 @@
       <c r="AV2" s="36"/>
       <c r="AW2" s="36"/>
       <c r="AX2" s="33">
-        <v>45569</v>
+        <v>45589</v>
       </c>
       <c r="AY2" s="33"/>
       <c r="AZ2" s="33"/>
@@ -3131,7 +3197,7 @@
     </row>
     <row r="9" spans="1:233" ht="15" customHeight="1">
       <c r="A9" s="56" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B9" s="57"/>
       <c r="C9" s="57"/>
@@ -3141,7 +3207,7 @@
       <c r="G9" s="57"/>
       <c r="H9" s="58"/>
       <c r="I9" s="56" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J9" s="57"/>
       <c r="K9" s="57"/>
@@ -3159,7 +3225,7 @@
       <c r="U9" s="54"/>
       <c r="V9" s="55"/>
       <c r="W9" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X9" s="14"/>
       <c r="Y9" s="14"/>
@@ -3169,7 +3235,7 @@
       <c r="AC9" s="14"/>
       <c r="AD9" s="14"/>
       <c r="AE9" s="62" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="AF9" s="63"/>
       <c r="AG9" s="63"/>
@@ -3329,28 +3395,28 @@
       <c r="GE9" s="8"/>
     </row>
     <row r="10" spans="1:233" ht="15" customHeight="1">
-      <c r="A10" s="79" t="s">
+      <c r="A10" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="79"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="82" t="s">
+      <c r="J10" s="82"/>
+      <c r="K10" s="82"/>
+      <c r="L10" s="82"/>
+      <c r="M10" s="82"/>
+      <c r="N10" s="82"/>
+      <c r="O10" s="82"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="53" t="s">
         <v>44</v>
-      </c>
-      <c r="J10" s="83"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="83"/>
-      <c r="M10" s="83"/>
-      <c r="N10" s="83"/>
-      <c r="O10" s="83"/>
-      <c r="P10" s="84"/>
-      <c r="Q10" s="53" t="s">
-        <v>45</v>
       </c>
       <c r="R10" s="54"/>
       <c r="S10" s="54"/>
@@ -3358,7 +3424,7 @@
       <c r="U10" s="54"/>
       <c r="V10" s="55"/>
       <c r="W10" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X10" s="14"/>
       <c r="Y10" s="14"/>
@@ -3368,7 +3434,7 @@
       <c r="AC10" s="14"/>
       <c r="AD10" s="14"/>
       <c r="AE10" s="62" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AF10" s="63"/>
       <c r="AG10" s="63"/>
@@ -3528,36 +3594,36 @@
       <c r="GE10" s="8"/>
     </row>
     <row r="11" spans="1:233" customFormat="1" ht="15" customHeight="1">
-      <c r="A11" s="85" t="s">
-        <v>65</v>
+      <c r="A11" s="89" t="s">
+        <v>62</v>
       </c>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="86" t="s">
-        <v>66</v>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="89"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="90" t="s">
+        <v>63</v>
       </c>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
-      <c r="L11" s="86"/>
-      <c r="M11" s="86"/>
-      <c r="N11" s="86"/>
-      <c r="O11" s="86"/>
-      <c r="P11" s="86"/>
-      <c r="Q11" s="85" t="s">
-        <v>45</v>
+      <c r="J11" s="90"/>
+      <c r="K11" s="90"/>
+      <c r="L11" s="90"/>
+      <c r="M11" s="90"/>
+      <c r="N11" s="90"/>
+      <c r="O11" s="90"/>
+      <c r="P11" s="90"/>
+      <c r="Q11" s="89" t="s">
+        <v>44</v>
       </c>
-      <c r="R11" s="85"/>
-      <c r="S11" s="85"/>
-      <c r="T11" s="85"/>
-      <c r="U11" s="85"/>
-      <c r="V11" s="85"/>
+      <c r="R11" s="89"/>
+      <c r="S11" s="89"/>
+      <c r="T11" s="89"/>
+      <c r="U11" s="89"/>
+      <c r="V11" s="89"/>
       <c r="W11" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X11" s="14"/>
       <c r="Y11" s="14"/>
@@ -3566,33 +3632,33 @@
       <c r="AB11" s="14"/>
       <c r="AC11" s="14"/>
       <c r="AD11" s="14"/>
-      <c r="AE11" s="87" t="s">
-        <v>67</v>
+      <c r="AE11" s="84" t="s">
+        <v>64</v>
       </c>
-      <c r="AF11" s="87"/>
-      <c r="AG11" s="87"/>
-      <c r="AH11" s="87"/>
-      <c r="AI11" s="87"/>
-      <c r="AJ11" s="87"/>
-      <c r="AK11" s="87"/>
-      <c r="AL11" s="87"/>
-      <c r="AM11" s="87"/>
-      <c r="AN11" s="87"/>
-      <c r="AO11" s="87"/>
-      <c r="AP11" s="87"/>
-      <c r="AQ11" s="87"/>
-      <c r="AR11" s="87"/>
-      <c r="AS11" s="87"/>
-      <c r="AT11" s="87"/>
-      <c r="AU11" s="87"/>
-      <c r="AV11" s="87"/>
-      <c r="AW11" s="87"/>
-      <c r="AX11" s="87"/>
-      <c r="AY11" s="87"/>
-      <c r="AZ11" s="87"/>
-      <c r="BA11" s="87"/>
-      <c r="BB11" s="87"/>
-      <c r="BC11" s="87"/>
+      <c r="AF11" s="84"/>
+      <c r="AG11" s="84"/>
+      <c r="AH11" s="84"/>
+      <c r="AI11" s="84"/>
+      <c r="AJ11" s="84"/>
+      <c r="AK11" s="84"/>
+      <c r="AL11" s="84"/>
+      <c r="AM11" s="84"/>
+      <c r="AN11" s="84"/>
+      <c r="AO11" s="84"/>
+      <c r="AP11" s="84"/>
+      <c r="AQ11" s="84"/>
+      <c r="AR11" s="84"/>
+      <c r="AS11" s="84"/>
+      <c r="AT11" s="84"/>
+      <c r="AU11" s="84"/>
+      <c r="AV11" s="84"/>
+      <c r="AW11" s="84"/>
+      <c r="AX11" s="84"/>
+      <c r="AY11" s="84"/>
+      <c r="AZ11" s="84"/>
+      <c r="BA11" s="84"/>
+      <c r="BB11" s="84"/>
+      <c r="BC11" s="84"/>
     </row>
     <row r="12" spans="1:233" s="10" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="74" t="s">
@@ -3606,7 +3672,7 @@
       <c r="G12" s="75"/>
       <c r="H12" s="75"/>
       <c r="I12" s="74" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J12" s="75"/>
       <c r="K12" s="75"/>
@@ -3632,7 +3698,7 @@
       <c r="AC12" s="14"/>
       <c r="AD12" s="14"/>
       <c r="AE12" s="15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AF12" s="15"/>
       <c r="AG12" s="15"/>
@@ -3792,132 +3858,132 @@
       <c r="GE12" s="9"/>
     </row>
     <row r="13" spans="1:233" s="11" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="88" t="s">
-        <v>55</v>
+      <c r="A13" s="91" t="s">
+        <v>53</v>
       </c>
-      <c r="B13" s="89"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89"/>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="89"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="88" t="s">
-        <v>52</v>
+      <c r="B13" s="92"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="91" t="s">
+        <v>50</v>
       </c>
-      <c r="J13" s="89"/>
-      <c r="K13" s="89"/>
-      <c r="L13" s="89"/>
-      <c r="M13" s="89"/>
-      <c r="N13" s="89"/>
-      <c r="O13" s="89"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="94" t="s">
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="92"/>
+      <c r="P13" s="93"/>
+      <c r="Q13" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="R13" s="95"/>
-      <c r="S13" s="95"/>
-      <c r="T13" s="95"/>
-      <c r="U13" s="95"/>
-      <c r="V13" s="96"/>
-      <c r="W13" s="100" t="s">
-        <v>64</v>
+      <c r="R13" s="98"/>
+      <c r="S13" s="98"/>
+      <c r="T13" s="98"/>
+      <c r="U13" s="98"/>
+      <c r="V13" s="99"/>
+      <c r="W13" s="103" t="s">
+        <v>61</v>
       </c>
-      <c r="X13" s="101"/>
-      <c r="Y13" s="101"/>
-      <c r="Z13" s="101"/>
-      <c r="AA13" s="101"/>
-      <c r="AB13" s="101"/>
-      <c r="AC13" s="101"/>
-      <c r="AD13" s="102"/>
-      <c r="AE13" s="106" t="s">
-        <v>71</v>
+      <c r="X13" s="104"/>
+      <c r="Y13" s="104"/>
+      <c r="Z13" s="104"/>
+      <c r="AA13" s="104"/>
+      <c r="AB13" s="104"/>
+      <c r="AC13" s="104"/>
+      <c r="AD13" s="105"/>
+      <c r="AE13" s="85" t="s">
+        <v>68</v>
       </c>
-      <c r="AF13" s="77"/>
-      <c r="AG13" s="77"/>
-      <c r="AH13" s="77"/>
-      <c r="AI13" s="77"/>
-      <c r="AJ13" s="77"/>
-      <c r="AK13" s="77"/>
-      <c r="AL13" s="77"/>
-      <c r="AM13" s="77"/>
-      <c r="AN13" s="77"/>
-      <c r="AO13" s="77"/>
-      <c r="AP13" s="77"/>
-      <c r="AQ13" s="77"/>
-      <c r="AR13" s="77"/>
-      <c r="AS13" s="77"/>
-      <c r="AT13" s="77"/>
-      <c r="AU13" s="77"/>
-      <c r="AV13" s="77"/>
-      <c r="AW13" s="77"/>
-      <c r="AX13" s="77"/>
-      <c r="AY13" s="77"/>
-      <c r="AZ13" s="77"/>
-      <c r="BA13" s="77"/>
-      <c r="BB13" s="77"/>
-      <c r="BC13" s="78"/>
+      <c r="AF13" s="76"/>
+      <c r="AG13" s="76"/>
+      <c r="AH13" s="76"/>
+      <c r="AI13" s="76"/>
+      <c r="AJ13" s="76"/>
+      <c r="AK13" s="76"/>
+      <c r="AL13" s="76"/>
+      <c r="AM13" s="76"/>
+      <c r="AN13" s="76"/>
+      <c r="AO13" s="76"/>
+      <c r="AP13" s="76"/>
+      <c r="AQ13" s="76"/>
+      <c r="AR13" s="76"/>
+      <c r="AS13" s="76"/>
+      <c r="AT13" s="76"/>
+      <c r="AU13" s="76"/>
+      <c r="AV13" s="76"/>
+      <c r="AW13" s="76"/>
+      <c r="AX13" s="76"/>
+      <c r="AY13" s="76"/>
+      <c r="AZ13" s="76"/>
+      <c r="BA13" s="76"/>
+      <c r="BB13" s="76"/>
+      <c r="BC13" s="77"/>
     </row>
     <row r="14" spans="1:233" s="11" customFormat="1" ht="15" customHeight="1">
-      <c r="A14" s="91"/>
-      <c r="B14" s="92"/>
-      <c r="C14" s="92"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="92"/>
-      <c r="F14" s="92"/>
-      <c r="G14" s="92"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="91"/>
-      <c r="J14" s="92"/>
-      <c r="K14" s="92"/>
-      <c r="L14" s="92"/>
-      <c r="M14" s="92"/>
-      <c r="N14" s="92"/>
-      <c r="O14" s="92"/>
-      <c r="P14" s="93"/>
-      <c r="Q14" s="97"/>
-      <c r="R14" s="98"/>
-      <c r="S14" s="98"/>
-      <c r="T14" s="98"/>
-      <c r="U14" s="98"/>
-      <c r="V14" s="99"/>
-      <c r="W14" s="103"/>
-      <c r="X14" s="104"/>
-      <c r="Y14" s="104"/>
-      <c r="Z14" s="104"/>
-      <c r="AA14" s="104"/>
-      <c r="AB14" s="104"/>
-      <c r="AC14" s="104"/>
-      <c r="AD14" s="105"/>
-      <c r="AE14" s="107"/>
-      <c r="AF14" s="108"/>
-      <c r="AG14" s="108"/>
-      <c r="AH14" s="108"/>
-      <c r="AI14" s="108"/>
-      <c r="AJ14" s="108"/>
-      <c r="AK14" s="108"/>
-      <c r="AL14" s="108"/>
-      <c r="AM14" s="108"/>
-      <c r="AN14" s="108"/>
-      <c r="AO14" s="108"/>
-      <c r="AP14" s="108"/>
-      <c r="AQ14" s="108"/>
-      <c r="AR14" s="108"/>
-      <c r="AS14" s="108"/>
-      <c r="AT14" s="108"/>
-      <c r="AU14" s="108"/>
-      <c r="AV14" s="108"/>
-      <c r="AW14" s="108"/>
-      <c r="AX14" s="108"/>
-      <c r="AY14" s="108"/>
-      <c r="AZ14" s="108"/>
-      <c r="BA14" s="108"/>
-      <c r="BB14" s="108"/>
-      <c r="BC14" s="109"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="95"/>
+      <c r="O14" s="95"/>
+      <c r="P14" s="96"/>
+      <c r="Q14" s="100"/>
+      <c r="R14" s="101"/>
+      <c r="S14" s="101"/>
+      <c r="T14" s="101"/>
+      <c r="U14" s="101"/>
+      <c r="V14" s="102"/>
+      <c r="W14" s="106"/>
+      <c r="X14" s="107"/>
+      <c r="Y14" s="107"/>
+      <c r="Z14" s="107"/>
+      <c r="AA14" s="107"/>
+      <c r="AB14" s="107"/>
+      <c r="AC14" s="107"/>
+      <c r="AD14" s="108"/>
+      <c r="AE14" s="86"/>
+      <c r="AF14" s="87"/>
+      <c r="AG14" s="87"/>
+      <c r="AH14" s="87"/>
+      <c r="AI14" s="87"/>
+      <c r="AJ14" s="87"/>
+      <c r="AK14" s="87"/>
+      <c r="AL14" s="87"/>
+      <c r="AM14" s="87"/>
+      <c r="AN14" s="87"/>
+      <c r="AO14" s="87"/>
+      <c r="AP14" s="87"/>
+      <c r="AQ14" s="87"/>
+      <c r="AR14" s="87"/>
+      <c r="AS14" s="87"/>
+      <c r="AT14" s="87"/>
+      <c r="AU14" s="87"/>
+      <c r="AV14" s="87"/>
+      <c r="AW14" s="87"/>
+      <c r="AX14" s="87"/>
+      <c r="AY14" s="87"/>
+      <c r="AZ14" s="87"/>
+      <c r="BA14" s="87"/>
+      <c r="BB14" s="87"/>
+      <c r="BC14" s="88"/>
     </row>
     <row r="15" spans="1:233" s="10" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="74" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B15" s="75"/>
       <c r="C15" s="75"/>
@@ -3927,7 +3993,7 @@
       <c r="G15" s="75"/>
       <c r="H15" s="75"/>
       <c r="I15" s="74" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J15" s="75"/>
       <c r="K15" s="75"/>
@@ -3945,7 +4011,7 @@
       <c r="U15" s="69"/>
       <c r="V15" s="70"/>
       <c r="W15" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X15" s="14"/>
       <c r="Y15" s="14"/>
@@ -3955,7 +4021,7 @@
       <c r="AC15" s="14"/>
       <c r="AD15" s="14"/>
       <c r="AE15" s="15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AF15" s="15"/>
       <c r="AG15" s="15"/>
@@ -4126,7 +4192,7 @@
       <c r="G16" s="75"/>
       <c r="H16" s="75"/>
       <c r="I16" s="74" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J16" s="75"/>
       <c r="K16" s="75"/>
@@ -4152,7 +4218,7 @@
       <c r="AC16" s="14"/>
       <c r="AD16" s="14"/>
       <c r="AE16" s="15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AF16" s="15"/>
       <c r="AG16" s="15"/>
@@ -4313,7 +4379,7 @@
     </row>
     <row r="17" spans="1:187" s="10" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="74" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B17" s="75"/>
       <c r="C17" s="75"/>
@@ -4323,7 +4389,7 @@
       <c r="G17" s="75"/>
       <c r="H17" s="75"/>
       <c r="I17" s="74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J17" s="75"/>
       <c r="K17" s="75"/>
@@ -4333,7 +4399,7 @@
       <c r="O17" s="75"/>
       <c r="P17" s="75"/>
       <c r="Q17" s="68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R17" s="69"/>
       <c r="S17" s="69"/>
@@ -4341,7 +4407,7 @@
       <c r="U17" s="69"/>
       <c r="V17" s="70"/>
       <c r="W17" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X17" s="14"/>
       <c r="Y17" s="14"/>
@@ -4351,7 +4417,7 @@
       <c r="AC17" s="14"/>
       <c r="AD17" s="14"/>
       <c r="AE17" s="15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AF17" s="15"/>
       <c r="AG17" s="15"/>
@@ -4522,7 +4588,7 @@
       <c r="G18" s="75"/>
       <c r="H18" s="75"/>
       <c r="I18" s="74" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J18" s="75"/>
       <c r="K18" s="75"/>
@@ -4548,7 +4614,7 @@
       <c r="AC18" s="14"/>
       <c r="AD18" s="14"/>
       <c r="AE18" s="15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AF18" s="15"/>
       <c r="AG18" s="15"/>
@@ -4709,7 +4775,7 @@
     </row>
     <row r="19" spans="1:187" ht="15" customHeight="1">
       <c r="A19" s="74" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B19" s="75"/>
       <c r="C19" s="75"/>
@@ -4719,7 +4785,7 @@
       <c r="G19" s="75"/>
       <c r="H19" s="75"/>
       <c r="I19" s="74" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J19" s="75"/>
       <c r="K19" s="75"/>
@@ -4729,7 +4795,7 @@
       <c r="O19" s="75"/>
       <c r="P19" s="75"/>
       <c r="Q19" s="56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R19" s="57"/>
       <c r="S19" s="57"/>
@@ -4737,7 +4803,7 @@
       <c r="U19" s="57"/>
       <c r="V19" s="58"/>
       <c r="W19" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X19" s="14"/>
       <c r="Y19" s="14"/>
@@ -4747,7 +4813,7 @@
       <c r="AC19" s="14"/>
       <c r="AD19" s="14"/>
       <c r="AE19" s="15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AF19" s="15"/>
       <c r="AG19" s="15"/>
@@ -4918,7 +4984,7 @@
       <c r="G20" s="75"/>
       <c r="H20" s="75"/>
       <c r="I20" s="74" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J20" s="75"/>
       <c r="K20" s="75"/>
@@ -4944,7 +5010,7 @@
       <c r="AC20" s="14"/>
       <c r="AD20" s="14"/>
       <c r="AE20" s="15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AF20" s="15"/>
       <c r="AG20" s="15"/>
@@ -5105,7 +5171,7 @@
     </row>
     <row r="21" spans="1:187" ht="15" customHeight="1">
       <c r="A21" s="74" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B21" s="75"/>
       <c r="C21" s="75"/>
@@ -5125,7 +5191,7 @@
       <c r="O21" s="75"/>
       <c r="P21" s="75"/>
       <c r="Q21" s="53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R21" s="54"/>
       <c r="S21" s="54"/>
@@ -5133,7 +5199,7 @@
       <c r="U21" s="54"/>
       <c r="V21" s="55"/>
       <c r="W21" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="X21" s="14"/>
       <c r="Y21" s="14"/>
@@ -5143,7 +5209,7 @@
       <c r="AC21" s="14"/>
       <c r="AD21" s="14"/>
       <c r="AE21" s="15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AF21" s="15"/>
       <c r="AG21" s="15"/>
@@ -5303,851 +5369,843 @@
       <c r="GE21" s="8"/>
     </row>
     <row r="22" spans="1:187" ht="15" customHeight="1">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="51"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="50" t="s">
+      <c r="B22" s="110"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="111"/>
+      <c r="I22" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="53" t="s">
+      <c r="J22" s="92"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="92"/>
+      <c r="M22" s="92"/>
+      <c r="N22" s="92"/>
+      <c r="O22" s="92"/>
+      <c r="P22" s="93"/>
+      <c r="Q22" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="R22" s="54"/>
-      <c r="S22" s="54"/>
-      <c r="T22" s="54"/>
-      <c r="U22" s="54"/>
-      <c r="V22" s="55"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14"/>
-      <c r="AC22" s="14"/>
-      <c r="AD22" s="14"/>
-      <c r="AE22" s="76" t="s">
-        <v>40</v>
+      <c r="R22" s="116"/>
+      <c r="S22" s="116"/>
+      <c r="T22" s="116"/>
+      <c r="U22" s="116"/>
+      <c r="V22" s="117"/>
+      <c r="W22" s="103"/>
+      <c r="X22" s="104"/>
+      <c r="Y22" s="104"/>
+      <c r="Z22" s="104"/>
+      <c r="AA22" s="104"/>
+      <c r="AB22" s="104"/>
+      <c r="AC22" s="104"/>
+      <c r="AD22" s="105"/>
+      <c r="AE22" s="85" t="s">
+        <v>71</v>
       </c>
-      <c r="AF22" s="77"/>
-      <c r="AG22" s="77"/>
-      <c r="AH22" s="77"/>
-      <c r="AI22" s="77"/>
-      <c r="AJ22" s="77"/>
-      <c r="AK22" s="77"/>
-      <c r="AL22" s="77"/>
-      <c r="AM22" s="77"/>
-      <c r="AN22" s="77"/>
-      <c r="AO22" s="77"/>
-      <c r="AP22" s="77"/>
-      <c r="AQ22" s="77"/>
-      <c r="AR22" s="77"/>
-      <c r="AS22" s="77"/>
-      <c r="AT22" s="77"/>
-      <c r="AU22" s="77"/>
-      <c r="AV22" s="77"/>
-      <c r="AW22" s="77"/>
-      <c r="AX22" s="77"/>
-      <c r="AY22" s="77"/>
-      <c r="AZ22" s="77"/>
-      <c r="BA22" s="77"/>
-      <c r="BB22" s="77"/>
-      <c r="BC22" s="78"/>
-      <c r="BD22" s="1"/>
-      <c r="BE22" s="1"/>
-      <c r="BF22" s="1"/>
-      <c r="BG22" s="1"/>
-      <c r="BH22" s="1"/>
-      <c r="BI22" s="1"/>
-      <c r="BJ22" s="1"/>
-      <c r="BK22" s="1"/>
-      <c r="BL22" s="1"/>
-      <c r="BM22" s="1"/>
-      <c r="BN22" s="1"/>
-      <c r="BO22" s="1"/>
-      <c r="BP22" s="1"/>
-      <c r="BQ22" s="1"/>
-      <c r="BR22" s="1"/>
-      <c r="BS22" s="1"/>
-      <c r="BT22" s="1"/>
-      <c r="BU22" s="1"/>
-      <c r="BV22" s="1"/>
-      <c r="BW22" s="1"/>
-      <c r="BX22" s="1"/>
-      <c r="BY22" s="1"/>
-      <c r="BZ22" s="1"/>
-      <c r="CA22" s="1"/>
-      <c r="CB22" s="1"/>
-      <c r="CC22" s="1"/>
-      <c r="CD22" s="1"/>
-      <c r="CE22" s="1"/>
-      <c r="CF22" s="1"/>
-      <c r="CG22" s="1"/>
-      <c r="CH22" s="1"/>
-      <c r="CI22" s="1"/>
-      <c r="CJ22" s="1"/>
-      <c r="CK22" s="1"/>
-      <c r="CL22" s="1"/>
-      <c r="CM22" s="1"/>
-      <c r="CN22" s="1"/>
-      <c r="CO22" s="1"/>
-      <c r="CP22" s="1"/>
-      <c r="CQ22" s="1"/>
-      <c r="CR22" s="1"/>
-      <c r="CS22" s="1"/>
-      <c r="CT22" s="1"/>
-      <c r="CU22" s="1"/>
-      <c r="CV22" s="1"/>
-      <c r="CW22" s="1"/>
-      <c r="CX22" s="1"/>
-      <c r="CY22" s="1"/>
-      <c r="CZ22" s="1"/>
-      <c r="DA22" s="1"/>
-      <c r="DB22" s="1"/>
-      <c r="DC22" s="1"/>
-      <c r="DD22" s="1"/>
-      <c r="DE22" s="1"/>
-      <c r="DF22" s="1"/>
-      <c r="DG22" s="1"/>
-      <c r="DH22" s="1"/>
-      <c r="DI22" s="1"/>
-      <c r="DJ22" s="1"/>
-      <c r="DK22" s="1"/>
-      <c r="DL22" s="1"/>
-      <c r="DM22" s="1"/>
-      <c r="DN22" s="1"/>
-      <c r="DO22" s="1"/>
-      <c r="DP22" s="1"/>
-      <c r="DQ22" s="1"/>
-      <c r="DR22" s="1"/>
-      <c r="DS22" s="1"/>
-      <c r="DT22" s="1"/>
-      <c r="DU22" s="1"/>
-      <c r="DV22" s="1"/>
-      <c r="DW22" s="1"/>
-      <c r="DX22" s="1"/>
-      <c r="DY22" s="1"/>
-      <c r="DZ22" s="1"/>
-      <c r="EA22" s="1"/>
-      <c r="EB22" s="1"/>
-      <c r="EC22" s="1"/>
-      <c r="ED22" s="1"/>
-      <c r="EE22" s="1"/>
-      <c r="EF22" s="1"/>
-      <c r="EG22" s="1"/>
-      <c r="EH22" s="1"/>
-      <c r="EI22" s="1"/>
-      <c r="EJ22" s="1"/>
-      <c r="EK22" s="1"/>
-      <c r="EL22" s="1"/>
-      <c r="EM22" s="1"/>
-      <c r="EN22" s="1"/>
-      <c r="EO22" s="1"/>
-      <c r="EP22" s="1"/>
-      <c r="EQ22" s="1"/>
-      <c r="ER22" s="1"/>
-      <c r="ES22" s="1"/>
-      <c r="ET22" s="1"/>
-      <c r="EU22" s="1"/>
-      <c r="EV22" s="1"/>
-      <c r="EW22" s="1"/>
-      <c r="EX22" s="1"/>
-      <c r="EY22" s="1"/>
-      <c r="EZ22" s="1"/>
-      <c r="FA22" s="1"/>
-      <c r="FB22" s="1"/>
-      <c r="FC22" s="1"/>
-      <c r="FD22" s="1"/>
-      <c r="FE22" s="1"/>
-      <c r="FF22" s="1"/>
-      <c r="FG22" s="1"/>
-      <c r="FH22" s="1"/>
-      <c r="FI22" s="1"/>
-      <c r="FJ22" s="1"/>
-      <c r="FK22" s="1"/>
-      <c r="FL22" s="1"/>
-      <c r="FM22" s="1"/>
-      <c r="FN22" s="1"/>
-      <c r="FO22" s="1"/>
-      <c r="FP22" s="1"/>
-      <c r="FQ22" s="1"/>
-      <c r="FR22" s="1"/>
-      <c r="FS22" s="1"/>
-      <c r="FT22" s="1"/>
-      <c r="FU22" s="1"/>
-      <c r="FV22" s="1"/>
-      <c r="FW22" s="1"/>
-      <c r="FX22" s="1"/>
-      <c r="FY22" s="1"/>
-      <c r="FZ22" s="1"/>
-      <c r="GA22" s="1"/>
-      <c r="GB22" s="1"/>
-      <c r="GC22" s="1"/>
-      <c r="GD22" s="1"/>
-      <c r="GE22" s="1"/>
+      <c r="AF22" s="76"/>
+      <c r="AG22" s="76"/>
+      <c r="AH22" s="76"/>
+      <c r="AI22" s="76"/>
+      <c r="AJ22" s="76"/>
+      <c r="AK22" s="76"/>
+      <c r="AL22" s="76"/>
+      <c r="AM22" s="76"/>
+      <c r="AN22" s="76"/>
+      <c r="AO22" s="76"/>
+      <c r="AP22" s="76"/>
+      <c r="AQ22" s="76"/>
+      <c r="AR22" s="76"/>
+      <c r="AS22" s="76"/>
+      <c r="AT22" s="76"/>
+      <c r="AU22" s="76"/>
+      <c r="AV22" s="76"/>
+      <c r="AW22" s="76"/>
+      <c r="AX22" s="76"/>
+      <c r="AY22" s="76"/>
+      <c r="AZ22" s="76"/>
+      <c r="BA22" s="76"/>
+      <c r="BB22" s="76"/>
+      <c r="BC22" s="77"/>
+      <c r="BD22" s="8"/>
+      <c r="BE22" s="8"/>
+      <c r="BF22" s="8"/>
+      <c r="BG22" s="8"/>
+      <c r="BH22" s="8"/>
+      <c r="BI22" s="8"/>
+      <c r="BJ22" s="8"/>
+      <c r="BK22" s="8"/>
+      <c r="BL22" s="8"/>
+      <c r="BM22" s="8"/>
+      <c r="BN22" s="8"/>
+      <c r="BO22" s="8"/>
+      <c r="BP22" s="8"/>
+      <c r="BQ22" s="8"/>
+      <c r="BR22" s="8"/>
+      <c r="BS22" s="8"/>
+      <c r="BT22" s="8"/>
+      <c r="BU22" s="8"/>
+      <c r="BV22" s="8"/>
+      <c r="BW22" s="8"/>
+      <c r="BX22" s="8"/>
+      <c r="BY22" s="8"/>
+      <c r="BZ22" s="8"/>
+      <c r="CA22" s="8"/>
+      <c r="CB22" s="8"/>
+      <c r="CC22" s="8"/>
+      <c r="CD22" s="8"/>
+      <c r="CE22" s="8"/>
+      <c r="CF22" s="8"/>
+      <c r="CG22" s="8"/>
+      <c r="CH22" s="8"/>
+      <c r="CI22" s="8"/>
+      <c r="CJ22" s="8"/>
+      <c r="CK22" s="8"/>
+      <c r="CL22" s="8"/>
+      <c r="CM22" s="8"/>
+      <c r="CN22" s="8"/>
+      <c r="CO22" s="8"/>
+      <c r="CP22" s="8"/>
+      <c r="CQ22" s="8"/>
+      <c r="CR22" s="8"/>
+      <c r="CS22" s="8"/>
+      <c r="CT22" s="8"/>
+      <c r="CU22" s="8"/>
+      <c r="CV22" s="8"/>
+      <c r="CW22" s="8"/>
+      <c r="CX22" s="8"/>
+      <c r="CY22" s="8"/>
+      <c r="CZ22" s="8"/>
+      <c r="DA22" s="8"/>
+      <c r="DB22" s="8"/>
+      <c r="DC22" s="8"/>
+      <c r="DD22" s="8"/>
+      <c r="DE22" s="8"/>
+      <c r="DF22" s="8"/>
+      <c r="DG22" s="8"/>
+      <c r="DH22" s="8"/>
+      <c r="DI22" s="8"/>
+      <c r="DJ22" s="8"/>
+      <c r="DK22" s="8"/>
+      <c r="DL22" s="8"/>
+      <c r="DM22" s="8"/>
+      <c r="DN22" s="8"/>
+      <c r="DO22" s="8"/>
+      <c r="DP22" s="8"/>
+      <c r="DQ22" s="8"/>
+      <c r="DR22" s="8"/>
+      <c r="DS22" s="8"/>
+      <c r="DT22" s="8"/>
+      <c r="DU22" s="8"/>
+      <c r="DV22" s="8"/>
+      <c r="DW22" s="8"/>
+      <c r="DX22" s="8"/>
+      <c r="DY22" s="8"/>
+      <c r="DZ22" s="8"/>
+      <c r="EA22" s="8"/>
+      <c r="EB22" s="8"/>
+      <c r="EC22" s="8"/>
+      <c r="ED22" s="8"/>
+      <c r="EE22" s="8"/>
+      <c r="EF22" s="8"/>
+      <c r="EG22" s="8"/>
+      <c r="EH22" s="8"/>
+      <c r="EI22" s="8"/>
+      <c r="EJ22" s="8"/>
+      <c r="EK22" s="8"/>
+      <c r="EL22" s="8"/>
+      <c r="EM22" s="8"/>
+      <c r="EN22" s="8"/>
+      <c r="EO22" s="8"/>
+      <c r="EP22" s="8"/>
+      <c r="EQ22" s="8"/>
+      <c r="ER22" s="8"/>
+      <c r="ES22" s="8"/>
+      <c r="ET22" s="8"/>
+      <c r="EU22" s="8"/>
+      <c r="EV22" s="8"/>
+      <c r="EW22" s="8"/>
+      <c r="EX22" s="8"/>
+      <c r="EY22" s="8"/>
+      <c r="EZ22" s="8"/>
+      <c r="FA22" s="8"/>
+      <c r="FB22" s="8"/>
+      <c r="FC22" s="8"/>
+      <c r="FD22" s="8"/>
+      <c r="FE22" s="8"/>
+      <c r="FF22" s="8"/>
+      <c r="FG22" s="8"/>
+      <c r="FH22" s="8"/>
+      <c r="FI22" s="8"/>
+      <c r="FJ22" s="8"/>
+      <c r="FK22" s="8"/>
+      <c r="FL22" s="8"/>
+      <c r="FM22" s="8"/>
+      <c r="FN22" s="8"/>
+      <c r="FO22" s="8"/>
+      <c r="FP22" s="8"/>
+      <c r="FQ22" s="8"/>
+      <c r="FR22" s="8"/>
+      <c r="FS22" s="8"/>
+      <c r="FT22" s="8"/>
+      <c r="FU22" s="8"/>
+      <c r="FV22" s="8"/>
+      <c r="FW22" s="8"/>
+      <c r="FX22" s="8"/>
+      <c r="FY22" s="8"/>
+      <c r="FZ22" s="8"/>
+      <c r="GA22" s="8"/>
+      <c r="GB22" s="8"/>
+      <c r="GC22" s="8"/>
+      <c r="GD22" s="8"/>
+      <c r="GE22" s="8"/>
     </row>
     <row r="23" spans="1:187" ht="15" customHeight="1">
-      <c r="A23" s="56" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="56" t="s">
+      <c r="A23" s="112"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="95"/>
+      <c r="M23" s="95"/>
+      <c r="N23" s="95"/>
+      <c r="O23" s="95"/>
+      <c r="P23" s="96"/>
+      <c r="Q23" s="118"/>
+      <c r="R23" s="119"/>
+      <c r="S23" s="119"/>
+      <c r="T23" s="119"/>
+      <c r="U23" s="119"/>
+      <c r="V23" s="120"/>
+      <c r="W23" s="106"/>
+      <c r="X23" s="107"/>
+      <c r="Y23" s="107"/>
+      <c r="Z23" s="107"/>
+      <c r="AA23" s="107"/>
+      <c r="AB23" s="107"/>
+      <c r="AC23" s="107"/>
+      <c r="AD23" s="108"/>
+      <c r="AE23" s="86"/>
+      <c r="AF23" s="87"/>
+      <c r="AG23" s="87"/>
+      <c r="AH23" s="87"/>
+      <c r="AI23" s="87"/>
+      <c r="AJ23" s="87"/>
+      <c r="AK23" s="87"/>
+      <c r="AL23" s="87"/>
+      <c r="AM23" s="87"/>
+      <c r="AN23" s="87"/>
+      <c r="AO23" s="87"/>
+      <c r="AP23" s="87"/>
+      <c r="AQ23" s="87"/>
+      <c r="AR23" s="87"/>
+      <c r="AS23" s="87"/>
+      <c r="AT23" s="87"/>
+      <c r="AU23" s="87"/>
+      <c r="AV23" s="87"/>
+      <c r="AW23" s="87"/>
+      <c r="AX23" s="87"/>
+      <c r="AY23" s="87"/>
+      <c r="AZ23" s="87"/>
+      <c r="BA23" s="87"/>
+      <c r="BB23" s="87"/>
+      <c r="BC23" s="88"/>
+      <c r="BD23" s="1"/>
+      <c r="BE23" s="1"/>
+      <c r="BF23" s="1"/>
+      <c r="BG23" s="1"/>
+      <c r="BH23" s="1"/>
+      <c r="BI23" s="1"/>
+      <c r="BJ23" s="1"/>
+      <c r="BK23" s="1"/>
+      <c r="BL23" s="1"/>
+      <c r="BM23" s="1"/>
+      <c r="BN23" s="1"/>
+      <c r="BO23" s="1"/>
+      <c r="BP23" s="1"/>
+      <c r="BQ23" s="1"/>
+      <c r="BR23" s="1"/>
+      <c r="BS23" s="1"/>
+      <c r="BT23" s="1"/>
+      <c r="BU23" s="1"/>
+      <c r="BV23" s="1"/>
+      <c r="BW23" s="1"/>
+      <c r="BX23" s="1"/>
+      <c r="BY23" s="1"/>
+      <c r="BZ23" s="1"/>
+      <c r="CA23" s="1"/>
+      <c r="CB23" s="1"/>
+      <c r="CC23" s="1"/>
+      <c r="CD23" s="1"/>
+      <c r="CE23" s="1"/>
+      <c r="CF23" s="1"/>
+      <c r="CG23" s="1"/>
+      <c r="CH23" s="1"/>
+      <c r="CI23" s="1"/>
+      <c r="CJ23" s="1"/>
+      <c r="CK23" s="1"/>
+      <c r="CL23" s="1"/>
+      <c r="CM23" s="1"/>
+      <c r="CN23" s="1"/>
+      <c r="CO23" s="1"/>
+      <c r="CP23" s="1"/>
+      <c r="CQ23" s="1"/>
+      <c r="CR23" s="1"/>
+      <c r="CS23" s="1"/>
+      <c r="CT23" s="1"/>
+      <c r="CU23" s="1"/>
+      <c r="CV23" s="1"/>
+      <c r="CW23" s="1"/>
+      <c r="CX23" s="1"/>
+      <c r="CY23" s="1"/>
+      <c r="CZ23" s="1"/>
+      <c r="DA23" s="1"/>
+      <c r="DB23" s="1"/>
+      <c r="DC23" s="1"/>
+      <c r="DD23" s="1"/>
+      <c r="DE23" s="1"/>
+      <c r="DF23" s="1"/>
+      <c r="DG23" s="1"/>
+      <c r="DH23" s="1"/>
+      <c r="DI23" s="1"/>
+      <c r="DJ23" s="1"/>
+      <c r="DK23" s="1"/>
+      <c r="DL23" s="1"/>
+      <c r="DM23" s="1"/>
+      <c r="DN23" s="1"/>
+      <c r="DO23" s="1"/>
+      <c r="DP23" s="1"/>
+      <c r="DQ23" s="1"/>
+      <c r="DR23" s="1"/>
+      <c r="DS23" s="1"/>
+      <c r="DT23" s="1"/>
+      <c r="DU23" s="1"/>
+      <c r="DV23" s="1"/>
+      <c r="DW23" s="1"/>
+      <c r="DX23" s="1"/>
+      <c r="DY23" s="1"/>
+      <c r="DZ23" s="1"/>
+      <c r="EA23" s="1"/>
+      <c r="EB23" s="1"/>
+      <c r="EC23" s="1"/>
+      <c r="ED23" s="1"/>
+      <c r="EE23" s="1"/>
+      <c r="EF23" s="1"/>
+      <c r="EG23" s="1"/>
+      <c r="EH23" s="1"/>
+      <c r="EI23" s="1"/>
+      <c r="EJ23" s="1"/>
+      <c r="EK23" s="1"/>
+      <c r="EL23" s="1"/>
+      <c r="EM23" s="1"/>
+      <c r="EN23" s="1"/>
+      <c r="EO23" s="1"/>
+      <c r="EP23" s="1"/>
+      <c r="EQ23" s="1"/>
+      <c r="ER23" s="1"/>
+      <c r="ES23" s="1"/>
+      <c r="ET23" s="1"/>
+      <c r="EU23" s="1"/>
+      <c r="EV23" s="1"/>
+      <c r="EW23" s="1"/>
+      <c r="EX23" s="1"/>
+      <c r="EY23" s="1"/>
+      <c r="EZ23" s="1"/>
+      <c r="FA23" s="1"/>
+      <c r="FB23" s="1"/>
+      <c r="FC23" s="1"/>
+      <c r="FD23" s="1"/>
+      <c r="FE23" s="1"/>
+      <c r="FF23" s="1"/>
+      <c r="FG23" s="1"/>
+      <c r="FH23" s="1"/>
+      <c r="FI23" s="1"/>
+      <c r="FJ23" s="1"/>
+      <c r="FK23" s="1"/>
+      <c r="FL23" s="1"/>
+      <c r="FM23" s="1"/>
+      <c r="FN23" s="1"/>
+      <c r="FO23" s="1"/>
+      <c r="FP23" s="1"/>
+      <c r="FQ23" s="1"/>
+      <c r="FR23" s="1"/>
+      <c r="FS23" s="1"/>
+      <c r="FT23" s="1"/>
+      <c r="FU23" s="1"/>
+      <c r="FV23" s="1"/>
+      <c r="FW23" s="1"/>
+      <c r="FX23" s="1"/>
+      <c r="FY23" s="1"/>
+      <c r="FZ23" s="1"/>
+      <c r="GA23" s="1"/>
+      <c r="GB23" s="1"/>
+      <c r="GC23" s="1"/>
+      <c r="GD23" s="1"/>
+      <c r="GE23" s="1"/>
+    </row>
+    <row r="24" spans="1:187" ht="15" customHeight="1">
+      <c r="A24" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="J23" s="57"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="57"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="57"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="53" t="s">
+      <c r="B24" s="122"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="123"/>
+      <c r="I24" s="121" t="s">
+        <v>45</v>
+      </c>
+      <c r="J24" s="122"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="122"/>
+      <c r="N24" s="122"/>
+      <c r="O24" s="122"/>
+      <c r="P24" s="123"/>
+      <c r="Q24" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="R23" s="54"/>
-      <c r="S23" s="54"/>
-      <c r="T23" s="54"/>
-      <c r="U23" s="54"/>
-      <c r="V23" s="55"/>
-      <c r="W23" s="14" t="s">
-        <v>64</v>
+      <c r="R24" s="116"/>
+      <c r="S24" s="116"/>
+      <c r="T24" s="116"/>
+      <c r="U24" s="116"/>
+      <c r="V24" s="117"/>
+      <c r="W24" s="103" t="s">
+        <v>61</v>
       </c>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
-      <c r="AB23" s="14"/>
-      <c r="AC23" s="14"/>
-      <c r="AD23" s="14"/>
-      <c r="AE23" s="62" t="s">
-        <v>47</v>
+      <c r="X24" s="104"/>
+      <c r="Y24" s="104"/>
+      <c r="Z24" s="104"/>
+      <c r="AA24" s="104"/>
+      <c r="AB24" s="104"/>
+      <c r="AC24" s="104"/>
+      <c r="AD24" s="105"/>
+      <c r="AE24" s="85" t="s">
+        <v>72</v>
       </c>
-      <c r="AF23" s="63"/>
-      <c r="AG23" s="63"/>
-      <c r="AH23" s="63"/>
-      <c r="AI23" s="63"/>
-      <c r="AJ23" s="63"/>
-      <c r="AK23" s="63"/>
-      <c r="AL23" s="63"/>
-      <c r="AM23" s="63"/>
-      <c r="AN23" s="63"/>
-      <c r="AO23" s="63"/>
-      <c r="AP23" s="63"/>
-      <c r="AQ23" s="63"/>
-      <c r="AR23" s="63"/>
-      <c r="AS23" s="63"/>
-      <c r="AT23" s="63"/>
-      <c r="AU23" s="63"/>
-      <c r="AV23" s="63"/>
-      <c r="AW23" s="63"/>
-      <c r="AX23" s="63"/>
-      <c r="AY23" s="63"/>
-      <c r="AZ23" s="63"/>
-      <c r="BA23" s="63"/>
-      <c r="BB23" s="63"/>
-      <c r="BC23" s="64"/>
-      <c r="BD23" s="8"/>
-      <c r="BE23" s="8"/>
-      <c r="BF23" s="8"/>
-      <c r="BG23" s="8"/>
-      <c r="BH23" s="8"/>
-      <c r="BI23" s="8"/>
-      <c r="BJ23" s="8"/>
-      <c r="BK23" s="8"/>
-      <c r="BL23" s="8"/>
-      <c r="BM23" s="8"/>
-      <c r="BN23" s="8"/>
-      <c r="BO23" s="8"/>
-      <c r="BP23" s="8"/>
-      <c r="BQ23" s="8"/>
-      <c r="BR23" s="8"/>
-      <c r="BS23" s="8"/>
-      <c r="BT23" s="8"/>
-      <c r="BU23" s="8"/>
-      <c r="BV23" s="8"/>
-      <c r="BW23" s="8"/>
-      <c r="BX23" s="8"/>
-      <c r="BY23" s="8"/>
-      <c r="BZ23" s="8"/>
-      <c r="CA23" s="8"/>
-      <c r="CB23" s="8"/>
-      <c r="CC23" s="8"/>
-      <c r="CD23" s="8"/>
-      <c r="CE23" s="8"/>
-      <c r="CF23" s="8"/>
-      <c r="CG23" s="8"/>
-      <c r="CH23" s="8"/>
-      <c r="CI23" s="8"/>
-      <c r="CJ23" s="8"/>
-      <c r="CK23" s="8"/>
-      <c r="CL23" s="8"/>
-      <c r="CM23" s="8"/>
-      <c r="CN23" s="8"/>
-      <c r="CO23" s="8"/>
-      <c r="CP23" s="8"/>
-      <c r="CQ23" s="8"/>
-      <c r="CR23" s="8"/>
-      <c r="CS23" s="8"/>
-      <c r="CT23" s="8"/>
-      <c r="CU23" s="8"/>
-      <c r="CV23" s="8"/>
-      <c r="CW23" s="8"/>
-      <c r="CX23" s="8"/>
-      <c r="CY23" s="8"/>
-      <c r="CZ23" s="8"/>
-      <c r="DA23" s="8"/>
-      <c r="DB23" s="8"/>
-      <c r="DC23" s="8"/>
-      <c r="DD23" s="8"/>
-      <c r="DE23" s="8"/>
-      <c r="DF23" s="8"/>
-      <c r="DG23" s="8"/>
-      <c r="DH23" s="8"/>
-      <c r="DI23" s="8"/>
-      <c r="DJ23" s="8"/>
-      <c r="DK23" s="8"/>
-      <c r="DL23" s="8"/>
-      <c r="DM23" s="8"/>
-      <c r="DN23" s="8"/>
-      <c r="DO23" s="8"/>
-      <c r="DP23" s="8"/>
-      <c r="DQ23" s="8"/>
-      <c r="DR23" s="8"/>
-      <c r="DS23" s="8"/>
-      <c r="DT23" s="8"/>
-      <c r="DU23" s="8"/>
-      <c r="DV23" s="8"/>
-      <c r="DW23" s="8"/>
-      <c r="DX23" s="8"/>
-      <c r="DY23" s="8"/>
-      <c r="DZ23" s="8"/>
-      <c r="EA23" s="8"/>
-      <c r="EB23" s="8"/>
-      <c r="EC23" s="8"/>
-      <c r="ED23" s="8"/>
-      <c r="EE23" s="8"/>
-      <c r="EF23" s="8"/>
-      <c r="EG23" s="8"/>
-      <c r="EH23" s="8"/>
-      <c r="EI23" s="8"/>
-      <c r="EJ23" s="8"/>
-      <c r="EK23" s="8"/>
-      <c r="EL23" s="8"/>
-      <c r="EM23" s="8"/>
-      <c r="EN23" s="8"/>
-      <c r="EO23" s="8"/>
-      <c r="EP23" s="8"/>
-      <c r="EQ23" s="8"/>
-      <c r="ER23" s="8"/>
-      <c r="ES23" s="8"/>
-      <c r="ET23" s="8"/>
-      <c r="EU23" s="8"/>
-      <c r="EV23" s="8"/>
-      <c r="EW23" s="8"/>
-      <c r="EX23" s="8"/>
-      <c r="EY23" s="8"/>
-      <c r="EZ23" s="8"/>
-      <c r="FA23" s="8"/>
-      <c r="FB23" s="8"/>
-      <c r="FC23" s="8"/>
-      <c r="FD23" s="8"/>
-      <c r="FE23" s="8"/>
-      <c r="FF23" s="8"/>
-      <c r="FG23" s="8"/>
-      <c r="FH23" s="8"/>
-      <c r="FI23" s="8"/>
-      <c r="FJ23" s="8"/>
-      <c r="FK23" s="8"/>
-      <c r="FL23" s="8"/>
-      <c r="FM23" s="8"/>
-      <c r="FN23" s="8"/>
-      <c r="FO23" s="8"/>
-      <c r="FP23" s="8"/>
-      <c r="FQ23" s="8"/>
-      <c r="FR23" s="8"/>
-      <c r="FS23" s="8"/>
-      <c r="FT23" s="8"/>
-      <c r="FU23" s="8"/>
-      <c r="FV23" s="8"/>
-      <c r="FW23" s="8"/>
-      <c r="FX23" s="8"/>
-      <c r="FY23" s="8"/>
-      <c r="FZ23" s="8"/>
-      <c r="GA23" s="8"/>
-      <c r="GB23" s="8"/>
-      <c r="GC23" s="8"/>
-      <c r="GD23" s="8"/>
-      <c r="GE23" s="8"/>
+      <c r="AF24" s="76"/>
+      <c r="AG24" s="76"/>
+      <c r="AH24" s="76"/>
+      <c r="AI24" s="76"/>
+      <c r="AJ24" s="76"/>
+      <c r="AK24" s="76"/>
+      <c r="AL24" s="76"/>
+      <c r="AM24" s="76"/>
+      <c r="AN24" s="76"/>
+      <c r="AO24" s="76"/>
+      <c r="AP24" s="76"/>
+      <c r="AQ24" s="76"/>
+      <c r="AR24" s="76"/>
+      <c r="AS24" s="76"/>
+      <c r="AT24" s="76"/>
+      <c r="AU24" s="76"/>
+      <c r="AV24" s="76"/>
+      <c r="AW24" s="76"/>
+      <c r="AX24" s="76"/>
+      <c r="AY24" s="76"/>
+      <c r="AZ24" s="76"/>
+      <c r="BA24" s="76"/>
+      <c r="BB24" s="76"/>
+      <c r="BC24" s="77"/>
+      <c r="BD24" s="8"/>
+      <c r="BE24" s="8"/>
+      <c r="BF24" s="8"/>
+      <c r="BG24" s="8"/>
+      <c r="BH24" s="8"/>
+      <c r="BI24" s="8"/>
+      <c r="BJ24" s="8"/>
+      <c r="BK24" s="8"/>
+      <c r="BL24" s="8"/>
+      <c r="BM24" s="8"/>
+      <c r="BN24" s="8"/>
+      <c r="BO24" s="8"/>
+      <c r="BP24" s="8"/>
+      <c r="BQ24" s="8"/>
+      <c r="BR24" s="8"/>
+      <c r="BS24" s="8"/>
+      <c r="BT24" s="8"/>
+      <c r="BU24" s="8"/>
+      <c r="BV24" s="8"/>
+      <c r="BW24" s="8"/>
+      <c r="BX24" s="8"/>
+      <c r="BY24" s="8"/>
+      <c r="BZ24" s="8"/>
+      <c r="CA24" s="8"/>
+      <c r="CB24" s="8"/>
+      <c r="CC24" s="8"/>
+      <c r="CD24" s="8"/>
+      <c r="CE24" s="8"/>
+      <c r="CF24" s="8"/>
+      <c r="CG24" s="8"/>
+      <c r="CH24" s="8"/>
+      <c r="CI24" s="8"/>
+      <c r="CJ24" s="8"/>
+      <c r="CK24" s="8"/>
+      <c r="CL24" s="8"/>
+      <c r="CM24" s="8"/>
+      <c r="CN24" s="8"/>
+      <c r="CO24" s="8"/>
+      <c r="CP24" s="8"/>
+      <c r="CQ24" s="8"/>
+      <c r="CR24" s="8"/>
+      <c r="CS24" s="8"/>
+      <c r="CT24" s="8"/>
+      <c r="CU24" s="8"/>
+      <c r="CV24" s="8"/>
+      <c r="CW24" s="8"/>
+      <c r="CX24" s="8"/>
+      <c r="CY24" s="8"/>
+      <c r="CZ24" s="8"/>
+      <c r="DA24" s="8"/>
+      <c r="DB24" s="8"/>
+      <c r="DC24" s="8"/>
+      <c r="DD24" s="8"/>
+      <c r="DE24" s="8"/>
+      <c r="DF24" s="8"/>
+      <c r="DG24" s="8"/>
+      <c r="DH24" s="8"/>
+      <c r="DI24" s="8"/>
+      <c r="DJ24" s="8"/>
+      <c r="DK24" s="8"/>
+      <c r="DL24" s="8"/>
+      <c r="DM24" s="8"/>
+      <c r="DN24" s="8"/>
+      <c r="DO24" s="8"/>
+      <c r="DP24" s="8"/>
+      <c r="DQ24" s="8"/>
+      <c r="DR24" s="8"/>
+      <c r="DS24" s="8"/>
+      <c r="DT24" s="8"/>
+      <c r="DU24" s="8"/>
+      <c r="DV24" s="8"/>
+      <c r="DW24" s="8"/>
+      <c r="DX24" s="8"/>
+      <c r="DY24" s="8"/>
+      <c r="DZ24" s="8"/>
+      <c r="EA24" s="8"/>
+      <c r="EB24" s="8"/>
+      <c r="EC24" s="8"/>
+      <c r="ED24" s="8"/>
+      <c r="EE24" s="8"/>
+      <c r="EF24" s="8"/>
+      <c r="EG24" s="8"/>
+      <c r="EH24" s="8"/>
+      <c r="EI24" s="8"/>
+      <c r="EJ24" s="8"/>
+      <c r="EK24" s="8"/>
+      <c r="EL24" s="8"/>
+      <c r="EM24" s="8"/>
+      <c r="EN24" s="8"/>
+      <c r="EO24" s="8"/>
+      <c r="EP24" s="8"/>
+      <c r="EQ24" s="8"/>
+      <c r="ER24" s="8"/>
+      <c r="ES24" s="8"/>
+      <c r="ET24" s="8"/>
+      <c r="EU24" s="8"/>
+      <c r="EV24" s="8"/>
+      <c r="EW24" s="8"/>
+      <c r="EX24" s="8"/>
+      <c r="EY24" s="8"/>
+      <c r="EZ24" s="8"/>
+      <c r="FA24" s="8"/>
+      <c r="FB24" s="8"/>
+      <c r="FC24" s="8"/>
+      <c r="FD24" s="8"/>
+      <c r="FE24" s="8"/>
+      <c r="FF24" s="8"/>
+      <c r="FG24" s="8"/>
+      <c r="FH24" s="8"/>
+      <c r="FI24" s="8"/>
+      <c r="FJ24" s="8"/>
+      <c r="FK24" s="8"/>
+      <c r="FL24" s="8"/>
+      <c r="FM24" s="8"/>
+      <c r="FN24" s="8"/>
+      <c r="FO24" s="8"/>
+      <c r="FP24" s="8"/>
+      <c r="FQ24" s="8"/>
+      <c r="FR24" s="8"/>
+      <c r="FS24" s="8"/>
+      <c r="FT24" s="8"/>
+      <c r="FU24" s="8"/>
+      <c r="FV24" s="8"/>
+      <c r="FW24" s="8"/>
+      <c r="FX24" s="8"/>
+      <c r="FY24" s="8"/>
+      <c r="FZ24" s="8"/>
+      <c r="GA24" s="8"/>
+      <c r="GB24" s="8"/>
+      <c r="GC24" s="8"/>
+      <c r="GD24" s="8"/>
+      <c r="GE24" s="8"/>
     </row>
-    <row r="24" spans="1:187" ht="15" customHeight="1">
-      <c r="A24" s="50" t="s">
+    <row r="25" spans="1:187" ht="15" customHeight="1">
+      <c r="A25" s="124"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="125"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="124"/>
+      <c r="J25" s="125"/>
+      <c r="K25" s="125"/>
+      <c r="L25" s="125"/>
+      <c r="M25" s="125"/>
+      <c r="N25" s="125"/>
+      <c r="O25" s="125"/>
+      <c r="P25" s="126"/>
+      <c r="Q25" s="118"/>
+      <c r="R25" s="119"/>
+      <c r="S25" s="119"/>
+      <c r="T25" s="119"/>
+      <c r="U25" s="119"/>
+      <c r="V25" s="120"/>
+      <c r="W25" s="106"/>
+      <c r="X25" s="107"/>
+      <c r="Y25" s="107"/>
+      <c r="Z25" s="107"/>
+      <c r="AA25" s="107"/>
+      <c r="AB25" s="107"/>
+      <c r="AC25" s="107"/>
+      <c r="AD25" s="108"/>
+      <c r="AE25" s="86"/>
+      <c r="AF25" s="87"/>
+      <c r="AG25" s="87"/>
+      <c r="AH25" s="87"/>
+      <c r="AI25" s="87"/>
+      <c r="AJ25" s="87"/>
+      <c r="AK25" s="87"/>
+      <c r="AL25" s="87"/>
+      <c r="AM25" s="87"/>
+      <c r="AN25" s="87"/>
+      <c r="AO25" s="87"/>
+      <c r="AP25" s="87"/>
+      <c r="AQ25" s="87"/>
+      <c r="AR25" s="87"/>
+      <c r="AS25" s="87"/>
+      <c r="AT25" s="87"/>
+      <c r="AU25" s="87"/>
+      <c r="AV25" s="87"/>
+      <c r="AW25" s="87"/>
+      <c r="AX25" s="87"/>
+      <c r="AY25" s="87"/>
+      <c r="AZ25" s="87"/>
+      <c r="BA25" s="87"/>
+      <c r="BB25" s="87"/>
+      <c r="BC25" s="88"/>
+      <c r="BD25" s="8"/>
+      <c r="BE25" s="8"/>
+      <c r="BF25" s="8"/>
+      <c r="BG25" s="8"/>
+      <c r="BH25" s="8"/>
+      <c r="BI25" s="8"/>
+      <c r="BJ25" s="8"/>
+      <c r="BK25" s="8"/>
+      <c r="BL25" s="8"/>
+      <c r="BM25" s="8"/>
+      <c r="BN25" s="8"/>
+      <c r="BO25" s="8"/>
+      <c r="BP25" s="8"/>
+      <c r="BQ25" s="8"/>
+      <c r="BR25" s="8"/>
+      <c r="BS25" s="8"/>
+      <c r="BT25" s="8"/>
+      <c r="BU25" s="8"/>
+      <c r="BV25" s="8"/>
+      <c r="BW25" s="8"/>
+      <c r="BX25" s="8"/>
+      <c r="BY25" s="8"/>
+      <c r="BZ25" s="8"/>
+      <c r="CA25" s="8"/>
+      <c r="CB25" s="8"/>
+      <c r="CC25" s="8"/>
+      <c r="CD25" s="8"/>
+      <c r="CE25" s="8"/>
+      <c r="CF25" s="8"/>
+      <c r="CG25" s="8"/>
+      <c r="CH25" s="8"/>
+      <c r="CI25" s="8"/>
+      <c r="CJ25" s="8"/>
+      <c r="CK25" s="8"/>
+      <c r="CL25" s="8"/>
+      <c r="CM25" s="8"/>
+      <c r="CN25" s="8"/>
+      <c r="CO25" s="8"/>
+      <c r="CP25" s="8"/>
+      <c r="CQ25" s="8"/>
+      <c r="CR25" s="8"/>
+      <c r="CS25" s="8"/>
+      <c r="CT25" s="8"/>
+      <c r="CU25" s="8"/>
+      <c r="CV25" s="8"/>
+      <c r="CW25" s="8"/>
+      <c r="CX25" s="8"/>
+      <c r="CY25" s="8"/>
+      <c r="CZ25" s="8"/>
+      <c r="DA25" s="8"/>
+      <c r="DB25" s="8"/>
+      <c r="DC25" s="8"/>
+      <c r="DD25" s="8"/>
+      <c r="DE25" s="8"/>
+      <c r="DF25" s="8"/>
+      <c r="DG25" s="8"/>
+      <c r="DH25" s="8"/>
+      <c r="DI25" s="8"/>
+      <c r="DJ25" s="8"/>
+      <c r="DK25" s="8"/>
+      <c r="DL25" s="8"/>
+      <c r="DM25" s="8"/>
+      <c r="DN25" s="8"/>
+      <c r="DO25" s="8"/>
+      <c r="DP25" s="8"/>
+      <c r="DQ25" s="8"/>
+      <c r="DR25" s="8"/>
+      <c r="DS25" s="8"/>
+      <c r="DT25" s="8"/>
+      <c r="DU25" s="8"/>
+      <c r="DV25" s="8"/>
+      <c r="DW25" s="8"/>
+      <c r="DX25" s="8"/>
+      <c r="DY25" s="8"/>
+      <c r="DZ25" s="8"/>
+      <c r="EA25" s="8"/>
+      <c r="EB25" s="8"/>
+      <c r="EC25" s="8"/>
+      <c r="ED25" s="8"/>
+      <c r="EE25" s="8"/>
+      <c r="EF25" s="8"/>
+      <c r="EG25" s="8"/>
+      <c r="EH25" s="8"/>
+      <c r="EI25" s="8"/>
+      <c r="EJ25" s="8"/>
+      <c r="EK25" s="8"/>
+      <c r="EL25" s="8"/>
+      <c r="EM25" s="8"/>
+      <c r="EN25" s="8"/>
+      <c r="EO25" s="8"/>
+      <c r="EP25" s="8"/>
+      <c r="EQ25" s="8"/>
+      <c r="ER25" s="8"/>
+      <c r="ES25" s="8"/>
+      <c r="ET25" s="8"/>
+      <c r="EU25" s="8"/>
+      <c r="EV25" s="8"/>
+      <c r="EW25" s="8"/>
+      <c r="EX25" s="8"/>
+      <c r="EY25" s="8"/>
+      <c r="EZ25" s="8"/>
+      <c r="FA25" s="8"/>
+      <c r="FB25" s="8"/>
+      <c r="FC25" s="8"/>
+      <c r="FD25" s="8"/>
+      <c r="FE25" s="8"/>
+      <c r="FF25" s="8"/>
+      <c r="FG25" s="8"/>
+      <c r="FH25" s="8"/>
+      <c r="FI25" s="8"/>
+      <c r="FJ25" s="8"/>
+      <c r="FK25" s="8"/>
+      <c r="FL25" s="8"/>
+      <c r="FM25" s="8"/>
+      <c r="FN25" s="8"/>
+      <c r="FO25" s="8"/>
+      <c r="FP25" s="8"/>
+      <c r="FQ25" s="8"/>
+      <c r="FR25" s="8"/>
+      <c r="FS25" s="8"/>
+      <c r="FT25" s="8"/>
+      <c r="FU25" s="8"/>
+      <c r="FV25" s="8"/>
+      <c r="FW25" s="8"/>
+      <c r="FX25" s="8"/>
+      <c r="FY25" s="8"/>
+      <c r="FZ25" s="8"/>
+      <c r="GA25" s="8"/>
+      <c r="GB25" s="8"/>
+      <c r="GC25" s="8"/>
+      <c r="GD25" s="8"/>
+      <c r="GE25" s="8"/>
+    </row>
+    <row r="26" spans="1:187" ht="15" customHeight="1">
+      <c r="A26" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="50" t="s">
+      <c r="B26" s="92"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="51"/>
-      <c r="P24" s="52"/>
-      <c r="Q24" s="53" t="s">
+      <c r="J26" s="92"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="92"/>
+      <c r="O26" s="92"/>
+      <c r="P26" s="93"/>
+      <c r="Q26" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="R24" s="54"/>
-      <c r="S24" s="54"/>
-      <c r="T24" s="54"/>
-      <c r="U24" s="54"/>
-      <c r="V24" s="55"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
-      <c r="AB24" s="14"/>
-      <c r="AC24" s="14"/>
-      <c r="AD24" s="14"/>
-      <c r="AE24" s="62" t="s">
-        <v>60</v>
+      <c r="R26" s="116"/>
+      <c r="S26" s="116"/>
+      <c r="T26" s="116"/>
+      <c r="U26" s="116"/>
+      <c r="V26" s="117"/>
+      <c r="W26" s="103"/>
+      <c r="X26" s="104"/>
+      <c r="Y26" s="104"/>
+      <c r="Z26" s="104"/>
+      <c r="AA26" s="104"/>
+      <c r="AB26" s="104"/>
+      <c r="AC26" s="104"/>
+      <c r="AD26" s="105"/>
+      <c r="AE26" s="85" t="s">
+        <v>73</v>
       </c>
-      <c r="AF24" s="63"/>
-      <c r="AG24" s="63"/>
-      <c r="AH24" s="63"/>
-      <c r="AI24" s="63"/>
-      <c r="AJ24" s="63"/>
-      <c r="AK24" s="63"/>
-      <c r="AL24" s="63"/>
-      <c r="AM24" s="63"/>
-      <c r="AN24" s="63"/>
-      <c r="AO24" s="63"/>
-      <c r="AP24" s="63"/>
-      <c r="AQ24" s="63"/>
-      <c r="AR24" s="63"/>
-      <c r="AS24" s="63"/>
-      <c r="AT24" s="63"/>
-      <c r="AU24" s="63"/>
-      <c r="AV24" s="63"/>
-      <c r="AW24" s="63"/>
-      <c r="AX24" s="63"/>
-      <c r="AY24" s="63"/>
-      <c r="AZ24" s="63"/>
-      <c r="BA24" s="63"/>
-      <c r="BB24" s="63"/>
-      <c r="BC24" s="64"/>
-      <c r="BD24" s="1"/>
-      <c r="BE24" s="1"/>
-      <c r="BF24" s="1"/>
-      <c r="BG24" s="1"/>
-      <c r="BH24" s="1"/>
-      <c r="BI24" s="1"/>
-      <c r="BJ24" s="1"/>
-      <c r="BK24" s="1"/>
-      <c r="BL24" s="1"/>
-      <c r="BM24" s="1"/>
-      <c r="BN24" s="1"/>
-      <c r="BO24" s="1"/>
-      <c r="BP24" s="1"/>
-      <c r="BQ24" s="1"/>
-      <c r="BR24" s="1"/>
-      <c r="BS24" s="1"/>
-      <c r="BT24" s="1"/>
-      <c r="BU24" s="1"/>
-      <c r="BV24" s="1"/>
-      <c r="BW24" s="1"/>
-      <c r="BX24" s="1"/>
-      <c r="BY24" s="1"/>
-      <c r="BZ24" s="1"/>
-      <c r="CA24" s="1"/>
-      <c r="CB24" s="1"/>
-      <c r="CC24" s="1"/>
-      <c r="CD24" s="1"/>
-      <c r="CE24" s="1"/>
-      <c r="CF24" s="1"/>
-      <c r="CG24" s="1"/>
-      <c r="CH24" s="1"/>
-      <c r="CI24" s="1"/>
-      <c r="CJ24" s="1"/>
-      <c r="CK24" s="1"/>
-      <c r="CL24" s="1"/>
-      <c r="CM24" s="1"/>
-      <c r="CN24" s="1"/>
-      <c r="CO24" s="1"/>
-      <c r="CP24" s="1"/>
-      <c r="CQ24" s="1"/>
-      <c r="CR24" s="1"/>
-      <c r="CS24" s="1"/>
-      <c r="CT24" s="1"/>
-      <c r="CU24" s="1"/>
-      <c r="CV24" s="1"/>
-      <c r="CW24" s="1"/>
-      <c r="CX24" s="1"/>
-      <c r="CY24" s="1"/>
-      <c r="CZ24" s="1"/>
-      <c r="DA24" s="1"/>
-      <c r="DB24" s="1"/>
-      <c r="DC24" s="1"/>
-      <c r="DD24" s="1"/>
-      <c r="DE24" s="1"/>
-      <c r="DF24" s="1"/>
-      <c r="DG24" s="1"/>
-      <c r="DH24" s="1"/>
-      <c r="DI24" s="1"/>
-      <c r="DJ24" s="1"/>
-      <c r="DK24" s="1"/>
-      <c r="DL24" s="1"/>
-      <c r="DM24" s="1"/>
-      <c r="DN24" s="1"/>
-      <c r="DO24" s="1"/>
-      <c r="DP24" s="1"/>
-      <c r="DQ24" s="1"/>
-      <c r="DR24" s="1"/>
-      <c r="DS24" s="1"/>
-      <c r="DT24" s="1"/>
-      <c r="DU24" s="1"/>
-      <c r="DV24" s="1"/>
-      <c r="DW24" s="1"/>
-      <c r="DX24" s="1"/>
-      <c r="DY24" s="1"/>
-      <c r="DZ24" s="1"/>
-      <c r="EA24" s="1"/>
-      <c r="EB24" s="1"/>
-      <c r="EC24" s="1"/>
-      <c r="ED24" s="1"/>
-      <c r="EE24" s="1"/>
-      <c r="EF24" s="1"/>
-      <c r="EG24" s="1"/>
-      <c r="EH24" s="1"/>
-      <c r="EI24" s="1"/>
-      <c r="EJ24" s="1"/>
-      <c r="EK24" s="1"/>
-      <c r="EL24" s="1"/>
-      <c r="EM24" s="1"/>
-      <c r="EN24" s="1"/>
-      <c r="EO24" s="1"/>
-      <c r="EP24" s="1"/>
-      <c r="EQ24" s="1"/>
-      <c r="ER24" s="1"/>
-      <c r="ES24" s="1"/>
-      <c r="ET24" s="1"/>
-      <c r="EU24" s="1"/>
-      <c r="EV24" s="1"/>
-      <c r="EW24" s="1"/>
-      <c r="EX24" s="1"/>
-      <c r="EY24" s="1"/>
-      <c r="EZ24" s="1"/>
-      <c r="FA24" s="1"/>
-      <c r="FB24" s="1"/>
-      <c r="FC24" s="1"/>
-      <c r="FD24" s="1"/>
-      <c r="FE24" s="1"/>
-      <c r="FF24" s="1"/>
-      <c r="FG24" s="1"/>
-      <c r="FH24" s="1"/>
-      <c r="FI24" s="1"/>
-      <c r="FJ24" s="1"/>
-      <c r="FK24" s="1"/>
-      <c r="FL24" s="1"/>
-      <c r="FM24" s="1"/>
-      <c r="FN24" s="1"/>
-      <c r="FO24" s="1"/>
-      <c r="FP24" s="1"/>
-      <c r="FQ24" s="1"/>
-      <c r="FR24" s="1"/>
-      <c r="FS24" s="1"/>
-      <c r="FT24" s="1"/>
-      <c r="FU24" s="1"/>
-      <c r="FV24" s="1"/>
-      <c r="FW24" s="1"/>
-      <c r="FX24" s="1"/>
-      <c r="FY24" s="1"/>
-      <c r="FZ24" s="1"/>
-      <c r="GA24" s="1"/>
-      <c r="GB24" s="1"/>
-      <c r="GC24" s="1"/>
-      <c r="GD24" s="1"/>
-      <c r="GE24" s="1"/>
-    </row>
-    <row r="25" spans="1:187" ht="15" customHeight="1">
-      <c r="A25" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
-      <c r="L25" s="51"/>
-      <c r="M25" s="51"/>
-      <c r="N25" s="51"/>
-      <c r="O25" s="51"/>
-      <c r="P25" s="52"/>
-      <c r="Q25" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="R25" s="54"/>
-      <c r="S25" s="54"/>
-      <c r="T25" s="54"/>
-      <c r="U25" s="54"/>
-      <c r="V25" s="55"/>
-      <c r="W25" s="59"/>
-      <c r="X25" s="60"/>
-      <c r="Y25" s="60"/>
-      <c r="Z25" s="60"/>
-      <c r="AA25" s="60"/>
-      <c r="AB25" s="60"/>
-      <c r="AC25" s="60"/>
-      <c r="AD25" s="61"/>
-      <c r="AE25" s="62" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF25" s="63"/>
-      <c r="AG25" s="63"/>
-      <c r="AH25" s="63"/>
-      <c r="AI25" s="63"/>
-      <c r="AJ25" s="63"/>
-      <c r="AK25" s="63"/>
-      <c r="AL25" s="63"/>
-      <c r="AM25" s="63"/>
-      <c r="AN25" s="63"/>
-      <c r="AO25" s="63"/>
-      <c r="AP25" s="63"/>
-      <c r="AQ25" s="63"/>
-      <c r="AR25" s="63"/>
-      <c r="AS25" s="63"/>
-      <c r="AT25" s="63"/>
-      <c r="AU25" s="63"/>
-      <c r="AV25" s="63"/>
-      <c r="AW25" s="63"/>
-      <c r="AX25" s="63"/>
-      <c r="AY25" s="63"/>
-      <c r="AZ25" s="63"/>
-      <c r="BA25" s="63"/>
-      <c r="BB25" s="63"/>
-      <c r="BC25" s="64"/>
-      <c r="BD25" s="1"/>
-      <c r="BE25" s="1"/>
-      <c r="BF25" s="1"/>
-      <c r="BG25" s="1"/>
-      <c r="BH25" s="1"/>
-      <c r="BI25" s="1"/>
-      <c r="BJ25" s="1"/>
-      <c r="BK25" s="1"/>
-      <c r="BL25" s="1"/>
-      <c r="BM25" s="1"/>
-      <c r="BN25" s="1"/>
-      <c r="BO25" s="1"/>
-      <c r="BP25" s="1"/>
-      <c r="BQ25" s="1"/>
-      <c r="BR25" s="1"/>
-      <c r="BS25" s="1"/>
-      <c r="BT25" s="1"/>
-      <c r="BU25" s="1"/>
-      <c r="BV25" s="1"/>
-      <c r="BW25" s="1"/>
-      <c r="BX25" s="1"/>
-      <c r="BY25" s="1"/>
-      <c r="BZ25" s="1"/>
-      <c r="CA25" s="1"/>
-      <c r="CB25" s="1"/>
-      <c r="CC25" s="1"/>
-      <c r="CD25" s="1"/>
-      <c r="CE25" s="1"/>
-      <c r="CF25" s="1"/>
-      <c r="CG25" s="1"/>
-      <c r="CH25" s="1"/>
-      <c r="CI25" s="1"/>
-      <c r="CJ25" s="1"/>
-      <c r="CK25" s="1"/>
-      <c r="CL25" s="1"/>
-      <c r="CM25" s="1"/>
-      <c r="CN25" s="1"/>
-      <c r="CO25" s="1"/>
-      <c r="CP25" s="1"/>
-      <c r="CQ25" s="1"/>
-      <c r="CR25" s="1"/>
-      <c r="CS25" s="1"/>
-      <c r="CT25" s="1"/>
-      <c r="CU25" s="1"/>
-      <c r="CV25" s="1"/>
-      <c r="CW25" s="1"/>
-      <c r="CX25" s="1"/>
-      <c r="CY25" s="1"/>
-      <c r="CZ25" s="1"/>
-      <c r="DA25" s="1"/>
-      <c r="DB25" s="1"/>
-      <c r="DC25" s="1"/>
-      <c r="DD25" s="1"/>
-      <c r="DE25" s="1"/>
-      <c r="DF25" s="1"/>
-      <c r="DG25" s="1"/>
-      <c r="DH25" s="1"/>
-      <c r="DI25" s="1"/>
-      <c r="DJ25" s="1"/>
-      <c r="DK25" s="1"/>
-      <c r="DL25" s="1"/>
-      <c r="DM25" s="1"/>
-      <c r="DN25" s="1"/>
-      <c r="DO25" s="1"/>
-      <c r="DP25" s="1"/>
-      <c r="DQ25" s="1"/>
-      <c r="DR25" s="1"/>
-      <c r="DS25" s="1"/>
-      <c r="DT25" s="1"/>
-      <c r="DU25" s="1"/>
-      <c r="DV25" s="1"/>
-      <c r="DW25" s="1"/>
-      <c r="DX25" s="1"/>
-      <c r="DY25" s="1"/>
-      <c r="DZ25" s="1"/>
-      <c r="EA25" s="1"/>
-      <c r="EB25" s="1"/>
-      <c r="EC25" s="1"/>
-      <c r="ED25" s="1"/>
-      <c r="EE25" s="1"/>
-      <c r="EF25" s="1"/>
-      <c r="EG25" s="1"/>
-      <c r="EH25" s="1"/>
-      <c r="EI25" s="1"/>
-      <c r="EJ25" s="1"/>
-      <c r="EK25" s="1"/>
-      <c r="EL25" s="1"/>
-      <c r="EM25" s="1"/>
-      <c r="EN25" s="1"/>
-      <c r="EO25" s="1"/>
-      <c r="EP25" s="1"/>
-      <c r="EQ25" s="1"/>
-      <c r="ER25" s="1"/>
-      <c r="ES25" s="1"/>
-      <c r="ET25" s="1"/>
-      <c r="EU25" s="1"/>
-      <c r="EV25" s="1"/>
-      <c r="EW25" s="1"/>
-      <c r="EX25" s="1"/>
-      <c r="EY25" s="1"/>
-      <c r="EZ25" s="1"/>
-      <c r="FA25" s="1"/>
-      <c r="FB25" s="1"/>
-      <c r="FC25" s="1"/>
-      <c r="FD25" s="1"/>
-      <c r="FE25" s="1"/>
-      <c r="FF25" s="1"/>
-      <c r="FG25" s="1"/>
-      <c r="FH25" s="1"/>
-      <c r="FI25" s="1"/>
-      <c r="FJ25" s="1"/>
-      <c r="FK25" s="1"/>
-      <c r="FL25" s="1"/>
-      <c r="FM25" s="1"/>
-      <c r="FN25" s="1"/>
-      <c r="FO25" s="1"/>
-      <c r="FP25" s="1"/>
-      <c r="FQ25" s="1"/>
-      <c r="FR25" s="1"/>
-      <c r="FS25" s="1"/>
-      <c r="FT25" s="1"/>
-      <c r="FU25" s="1"/>
-      <c r="FV25" s="1"/>
-      <c r="FW25" s="1"/>
-      <c r="FX25" s="1"/>
-      <c r="FY25" s="1"/>
-      <c r="FZ25" s="1"/>
-      <c r="GA25" s="1"/>
-      <c r="GB25" s="1"/>
-      <c r="GC25" s="1"/>
-      <c r="GD25" s="1"/>
-      <c r="GE25" s="1"/>
-    </row>
-    <row r="26" spans="1:187" ht="15" customHeight="1">
-      <c r="A26" s="56"/>
-      <c r="B26" s="57"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="57"/>
-      <c r="P26" s="58"/>
-      <c r="Q26" s="53"/>
-      <c r="R26" s="54"/>
-      <c r="S26" s="54"/>
-      <c r="T26" s="54"/>
-      <c r="U26" s="54"/>
-      <c r="V26" s="55"/>
-      <c r="W26" s="59"/>
-      <c r="X26" s="60"/>
-      <c r="Y26" s="60"/>
-      <c r="Z26" s="60"/>
-      <c r="AA26" s="60"/>
-      <c r="AB26" s="60"/>
-      <c r="AC26" s="60"/>
-      <c r="AD26" s="61"/>
-      <c r="AE26" s="62"/>
-      <c r="AF26" s="63"/>
-      <c r="AG26" s="63"/>
-      <c r="AH26" s="63"/>
-      <c r="AI26" s="63"/>
-      <c r="AJ26" s="63"/>
-      <c r="AK26" s="63"/>
-      <c r="AL26" s="63"/>
-      <c r="AM26" s="63"/>
-      <c r="AN26" s="63"/>
-      <c r="AO26" s="63"/>
-      <c r="AP26" s="63"/>
-      <c r="AQ26" s="63"/>
-      <c r="AR26" s="63"/>
-      <c r="AS26" s="63"/>
-      <c r="AT26" s="63"/>
-      <c r="AU26" s="63"/>
-      <c r="AV26" s="63"/>
-      <c r="AW26" s="63"/>
-      <c r="AX26" s="63"/>
-      <c r="AY26" s="63"/>
-      <c r="AZ26" s="63"/>
-      <c r="BA26" s="63"/>
-      <c r="BB26" s="63"/>
-      <c r="BC26" s="64"/>
+      <c r="AF26" s="76"/>
+      <c r="AG26" s="76"/>
+      <c r="AH26" s="76"/>
+      <c r="AI26" s="76"/>
+      <c r="AJ26" s="76"/>
+      <c r="AK26" s="76"/>
+      <c r="AL26" s="76"/>
+      <c r="AM26" s="76"/>
+      <c r="AN26" s="76"/>
+      <c r="AO26" s="76"/>
+      <c r="AP26" s="76"/>
+      <c r="AQ26" s="76"/>
+      <c r="AR26" s="76"/>
+      <c r="AS26" s="76"/>
+      <c r="AT26" s="76"/>
+      <c r="AU26" s="76"/>
+      <c r="AV26" s="76"/>
+      <c r="AW26" s="76"/>
+      <c r="AX26" s="76"/>
+      <c r="AY26" s="76"/>
+      <c r="AZ26" s="76"/>
+      <c r="BA26" s="76"/>
+      <c r="BB26" s="76"/>
+      <c r="BC26" s="77"/>
       <c r="BD26" s="1"/>
       <c r="BE26" s="1"/>
       <c r="BF26" s="1"/>
@@ -6281,629 +6339,637 @@
       <c r="GD26" s="1"/>
       <c r="GE26" s="1"/>
     </row>
-    <row r="27" spans="1:187" s="10" customFormat="1" ht="15" customHeight="1">
-      <c r="A27" s="68"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="72"/>
-      <c r="N27" s="72"/>
-      <c r="O27" s="72"/>
-      <c r="P27" s="73"/>
-      <c r="Q27" s="68"/>
-      <c r="R27" s="69"/>
-      <c r="S27" s="69"/>
-      <c r="T27" s="69"/>
-      <c r="U27" s="69"/>
-      <c r="V27" s="70"/>
-      <c r="W27" s="65"/>
-      <c r="X27" s="66"/>
-      <c r="Y27" s="66"/>
-      <c r="Z27" s="66"/>
-      <c r="AA27" s="66"/>
-      <c r="AB27" s="66"/>
-      <c r="AC27" s="66"/>
-      <c r="AD27" s="67"/>
-      <c r="AE27" s="62"/>
-      <c r="AF27" s="63"/>
-      <c r="AG27" s="63"/>
-      <c r="AH27" s="63"/>
-      <c r="AI27" s="63"/>
-      <c r="AJ27" s="63"/>
-      <c r="AK27" s="63"/>
-      <c r="AL27" s="63"/>
-      <c r="AM27" s="63"/>
-      <c r="AN27" s="63"/>
-      <c r="AO27" s="63"/>
-      <c r="AP27" s="63"/>
-      <c r="AQ27" s="63"/>
-      <c r="AR27" s="63"/>
-      <c r="AS27" s="63"/>
-      <c r="AT27" s="63"/>
-      <c r="AU27" s="63"/>
-      <c r="AV27" s="63"/>
-      <c r="AW27" s="63"/>
-      <c r="AX27" s="63"/>
-      <c r="AY27" s="63"/>
-      <c r="AZ27" s="63"/>
-      <c r="BA27" s="63"/>
-      <c r="BB27" s="63"/>
-      <c r="BC27" s="64"/>
-      <c r="BD27" s="9"/>
-      <c r="BE27" s="9"/>
-      <c r="BF27" s="9"/>
-      <c r="BG27" s="9"/>
-      <c r="BH27" s="9"/>
-      <c r="BI27" s="9"/>
-      <c r="BJ27" s="9"/>
-      <c r="BK27" s="9"/>
-      <c r="BL27" s="9"/>
-      <c r="BM27" s="9"/>
-      <c r="BN27" s="9"/>
-      <c r="BO27" s="9"/>
-      <c r="BP27" s="9"/>
-      <c r="BQ27" s="9"/>
-      <c r="BR27" s="9"/>
-      <c r="BS27" s="9"/>
-      <c r="BT27" s="9"/>
-      <c r="BU27" s="9"/>
-      <c r="BV27" s="9"/>
-      <c r="BW27" s="9"/>
-      <c r="BX27" s="9"/>
-      <c r="BY27" s="9"/>
-      <c r="BZ27" s="9"/>
-      <c r="CA27" s="9"/>
-      <c r="CB27" s="9"/>
-      <c r="CC27" s="9"/>
-      <c r="CD27" s="9"/>
-      <c r="CE27" s="9"/>
-      <c r="CF27" s="9"/>
-      <c r="CG27" s="9"/>
-      <c r="CH27" s="9"/>
-      <c r="CI27" s="9"/>
-      <c r="CJ27" s="9"/>
-      <c r="CK27" s="9"/>
-      <c r="CL27" s="9"/>
-      <c r="CM27" s="9"/>
-      <c r="CN27" s="9"/>
-      <c r="CO27" s="9"/>
-      <c r="CP27" s="9"/>
-      <c r="CQ27" s="9"/>
-      <c r="CR27" s="9"/>
-      <c r="CS27" s="9"/>
-      <c r="CT27" s="9"/>
-      <c r="CU27" s="9"/>
-      <c r="CV27" s="9"/>
-      <c r="CW27" s="9"/>
-      <c r="CX27" s="9"/>
-      <c r="CY27" s="9"/>
-      <c r="CZ27" s="9"/>
-      <c r="DA27" s="9"/>
-      <c r="DB27" s="9"/>
-      <c r="DC27" s="9"/>
-      <c r="DD27" s="9"/>
-      <c r="DE27" s="9"/>
-      <c r="DF27" s="9"/>
-      <c r="DG27" s="9"/>
-      <c r="DH27" s="9"/>
-      <c r="DI27" s="9"/>
-      <c r="DJ27" s="9"/>
-      <c r="DK27" s="9"/>
-      <c r="DL27" s="9"/>
-      <c r="DM27" s="9"/>
-      <c r="DN27" s="9"/>
-      <c r="DO27" s="9"/>
-      <c r="DP27" s="9"/>
-      <c r="DQ27" s="9"/>
-      <c r="DR27" s="9"/>
-      <c r="DS27" s="9"/>
-      <c r="DT27" s="9"/>
-      <c r="DU27" s="9"/>
-      <c r="DV27" s="9"/>
-      <c r="DW27" s="9"/>
-      <c r="DX27" s="9"/>
-      <c r="DY27" s="9"/>
-      <c r="DZ27" s="9"/>
-      <c r="EA27" s="9"/>
-      <c r="EB27" s="9"/>
-      <c r="EC27" s="9"/>
-      <c r="ED27" s="9"/>
-      <c r="EE27" s="9"/>
-      <c r="EF27" s="9"/>
-      <c r="EG27" s="9"/>
-      <c r="EH27" s="9"/>
-      <c r="EI27" s="9"/>
-      <c r="EJ27" s="9"/>
-      <c r="EK27" s="9"/>
-      <c r="EL27" s="9"/>
-      <c r="EM27" s="9"/>
-      <c r="EN27" s="9"/>
-      <c r="EO27" s="9"/>
-      <c r="EP27" s="9"/>
-      <c r="EQ27" s="9"/>
-      <c r="ER27" s="9"/>
-      <c r="ES27" s="9"/>
-      <c r="ET27" s="9"/>
-      <c r="EU27" s="9"/>
-      <c r="EV27" s="9"/>
-      <c r="EW27" s="9"/>
-      <c r="EX27" s="9"/>
-      <c r="EY27" s="9"/>
-      <c r="EZ27" s="9"/>
-      <c r="FA27" s="9"/>
-      <c r="FB27" s="9"/>
-      <c r="FC27" s="9"/>
-      <c r="FD27" s="9"/>
-      <c r="FE27" s="9"/>
-      <c r="FF27" s="9"/>
-      <c r="FG27" s="9"/>
-      <c r="FH27" s="9"/>
-      <c r="FI27" s="9"/>
-      <c r="FJ27" s="9"/>
-      <c r="FK27" s="9"/>
-      <c r="FL27" s="9"/>
-      <c r="FM27" s="9"/>
-      <c r="FN27" s="9"/>
-      <c r="FO27" s="9"/>
-      <c r="FP27" s="9"/>
-      <c r="FQ27" s="9"/>
-      <c r="FR27" s="9"/>
-      <c r="FS27" s="9"/>
-      <c r="FT27" s="9"/>
-      <c r="FU27" s="9"/>
-      <c r="FV27" s="9"/>
-      <c r="FW27" s="9"/>
-      <c r="FX27" s="9"/>
-      <c r="FY27" s="9"/>
-      <c r="FZ27" s="9"/>
-      <c r="GA27" s="9"/>
-      <c r="GB27" s="9"/>
-      <c r="GC27" s="9"/>
-      <c r="GD27" s="9"/>
-      <c r="GE27" s="9"/>
+    <row r="27" spans="1:187" ht="15" customHeight="1">
+      <c r="A27" s="94"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="96"/>
+      <c r="I27" s="94"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
+      <c r="M27" s="95"/>
+      <c r="N27" s="95"/>
+      <c r="O27" s="95"/>
+      <c r="P27" s="96"/>
+      <c r="Q27" s="118"/>
+      <c r="R27" s="119"/>
+      <c r="S27" s="119"/>
+      <c r="T27" s="119"/>
+      <c r="U27" s="119"/>
+      <c r="V27" s="120"/>
+      <c r="W27" s="106"/>
+      <c r="X27" s="107"/>
+      <c r="Y27" s="107"/>
+      <c r="Z27" s="107"/>
+      <c r="AA27" s="107"/>
+      <c r="AB27" s="107"/>
+      <c r="AC27" s="107"/>
+      <c r="AD27" s="108"/>
+      <c r="AE27" s="86"/>
+      <c r="AF27" s="87"/>
+      <c r="AG27" s="87"/>
+      <c r="AH27" s="87"/>
+      <c r="AI27" s="87"/>
+      <c r="AJ27" s="87"/>
+      <c r="AK27" s="87"/>
+      <c r="AL27" s="87"/>
+      <c r="AM27" s="87"/>
+      <c r="AN27" s="87"/>
+      <c r="AO27" s="87"/>
+      <c r="AP27" s="87"/>
+      <c r="AQ27" s="87"/>
+      <c r="AR27" s="87"/>
+      <c r="AS27" s="87"/>
+      <c r="AT27" s="87"/>
+      <c r="AU27" s="87"/>
+      <c r="AV27" s="87"/>
+      <c r="AW27" s="87"/>
+      <c r="AX27" s="87"/>
+      <c r="AY27" s="87"/>
+      <c r="AZ27" s="87"/>
+      <c r="BA27" s="87"/>
+      <c r="BB27" s="87"/>
+      <c r="BC27" s="88"/>
+      <c r="BD27" s="8"/>
+      <c r="BE27" s="8"/>
+      <c r="BF27" s="8"/>
+      <c r="BG27" s="8"/>
+      <c r="BH27" s="8"/>
+      <c r="BI27" s="8"/>
+      <c r="BJ27" s="8"/>
+      <c r="BK27" s="8"/>
+      <c r="BL27" s="8"/>
+      <c r="BM27" s="8"/>
+      <c r="BN27" s="8"/>
+      <c r="BO27" s="8"/>
+      <c r="BP27" s="8"/>
+      <c r="BQ27" s="8"/>
+      <c r="BR27" s="8"/>
+      <c r="BS27" s="8"/>
+      <c r="BT27" s="8"/>
+      <c r="BU27" s="8"/>
+      <c r="BV27" s="8"/>
+      <c r="BW27" s="8"/>
+      <c r="BX27" s="8"/>
+      <c r="BY27" s="8"/>
+      <c r="BZ27" s="8"/>
+      <c r="CA27" s="8"/>
+      <c r="CB27" s="8"/>
+      <c r="CC27" s="8"/>
+      <c r="CD27" s="8"/>
+      <c r="CE27" s="8"/>
+      <c r="CF27" s="8"/>
+      <c r="CG27" s="8"/>
+      <c r="CH27" s="8"/>
+      <c r="CI27" s="8"/>
+      <c r="CJ27" s="8"/>
+      <c r="CK27" s="8"/>
+      <c r="CL27" s="8"/>
+      <c r="CM27" s="8"/>
+      <c r="CN27" s="8"/>
+      <c r="CO27" s="8"/>
+      <c r="CP27" s="8"/>
+      <c r="CQ27" s="8"/>
+      <c r="CR27" s="8"/>
+      <c r="CS27" s="8"/>
+      <c r="CT27" s="8"/>
+      <c r="CU27" s="8"/>
+      <c r="CV27" s="8"/>
+      <c r="CW27" s="8"/>
+      <c r="CX27" s="8"/>
+      <c r="CY27" s="8"/>
+      <c r="CZ27" s="8"/>
+      <c r="DA27" s="8"/>
+      <c r="DB27" s="8"/>
+      <c r="DC27" s="8"/>
+      <c r="DD27" s="8"/>
+      <c r="DE27" s="8"/>
+      <c r="DF27" s="8"/>
+      <c r="DG27" s="8"/>
+      <c r="DH27" s="8"/>
+      <c r="DI27" s="8"/>
+      <c r="DJ27" s="8"/>
+      <c r="DK27" s="8"/>
+      <c r="DL27" s="8"/>
+      <c r="DM27" s="8"/>
+      <c r="DN27" s="8"/>
+      <c r="DO27" s="8"/>
+      <c r="DP27" s="8"/>
+      <c r="DQ27" s="8"/>
+      <c r="DR27" s="8"/>
+      <c r="DS27" s="8"/>
+      <c r="DT27" s="8"/>
+      <c r="DU27" s="8"/>
+      <c r="DV27" s="8"/>
+      <c r="DW27" s="8"/>
+      <c r="DX27" s="8"/>
+      <c r="DY27" s="8"/>
+      <c r="DZ27" s="8"/>
+      <c r="EA27" s="8"/>
+      <c r="EB27" s="8"/>
+      <c r="EC27" s="8"/>
+      <c r="ED27" s="8"/>
+      <c r="EE27" s="8"/>
+      <c r="EF27" s="8"/>
+      <c r="EG27" s="8"/>
+      <c r="EH27" s="8"/>
+      <c r="EI27" s="8"/>
+      <c r="EJ27" s="8"/>
+      <c r="EK27" s="8"/>
+      <c r="EL27" s="8"/>
+      <c r="EM27" s="8"/>
+      <c r="EN27" s="8"/>
+      <c r="EO27" s="8"/>
+      <c r="EP27" s="8"/>
+      <c r="EQ27" s="8"/>
+      <c r="ER27" s="8"/>
+      <c r="ES27" s="8"/>
+      <c r="ET27" s="8"/>
+      <c r="EU27" s="8"/>
+      <c r="EV27" s="8"/>
+      <c r="EW27" s="8"/>
+      <c r="EX27" s="8"/>
+      <c r="EY27" s="8"/>
+      <c r="EZ27" s="8"/>
+      <c r="FA27" s="8"/>
+      <c r="FB27" s="8"/>
+      <c r="FC27" s="8"/>
+      <c r="FD27" s="8"/>
+      <c r="FE27" s="8"/>
+      <c r="FF27" s="8"/>
+      <c r="FG27" s="8"/>
+      <c r="FH27" s="8"/>
+      <c r="FI27" s="8"/>
+      <c r="FJ27" s="8"/>
+      <c r="FK27" s="8"/>
+      <c r="FL27" s="8"/>
+      <c r="FM27" s="8"/>
+      <c r="FN27" s="8"/>
+      <c r="FO27" s="8"/>
+      <c r="FP27" s="8"/>
+      <c r="FQ27" s="8"/>
+      <c r="FR27" s="8"/>
+      <c r="FS27" s="8"/>
+      <c r="FT27" s="8"/>
+      <c r="FU27" s="8"/>
+      <c r="FV27" s="8"/>
+      <c r="FW27" s="8"/>
+      <c r="FX27" s="8"/>
+      <c r="FY27" s="8"/>
+      <c r="FZ27" s="8"/>
+      <c r="GA27" s="8"/>
+      <c r="GB27" s="8"/>
+      <c r="GC27" s="8"/>
+      <c r="GD27" s="8"/>
+      <c r="GE27" s="8"/>
     </row>
-    <row r="28" spans="1:187" s="10" customFormat="1" ht="15" customHeight="1">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
-      <c r="U28" s="12"/>
-      <c r="V28" s="12"/>
-      <c r="W28" s="14"/>
-      <c r="X28" s="14"/>
-      <c r="Y28" s="14"/>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
-      <c r="AB28" s="14"/>
-      <c r="AC28" s="14"/>
-      <c r="AD28" s="14"/>
-      <c r="AE28" s="15"/>
-      <c r="AF28" s="15"/>
-      <c r="AG28" s="15"/>
-      <c r="AH28" s="15"/>
-      <c r="AI28" s="15"/>
-      <c r="AJ28" s="15"/>
-      <c r="AK28" s="15"/>
-      <c r="AL28" s="15"/>
-      <c r="AM28" s="15"/>
-      <c r="AN28" s="15"/>
-      <c r="AO28" s="15"/>
-      <c r="AP28" s="15"/>
-      <c r="AQ28" s="15"/>
-      <c r="AR28" s="15"/>
-      <c r="AS28" s="15"/>
-      <c r="AT28" s="15"/>
-      <c r="AU28" s="15"/>
-      <c r="AV28" s="15"/>
-      <c r="AW28" s="15"/>
-      <c r="AX28" s="15"/>
-      <c r="AY28" s="15"/>
-      <c r="AZ28" s="15"/>
-      <c r="BA28" s="15"/>
-      <c r="BB28" s="15"/>
-      <c r="BC28" s="15"/>
-      <c r="BD28" s="9"/>
-      <c r="BE28" s="9"/>
-      <c r="BF28" s="9"/>
-      <c r="BG28" s="9"/>
-      <c r="BH28" s="9"/>
-      <c r="BI28" s="9"/>
-      <c r="BJ28" s="9"/>
-      <c r="BK28" s="9"/>
-      <c r="BL28" s="9"/>
-      <c r="BM28" s="9"/>
-      <c r="BN28" s="9"/>
-      <c r="BO28" s="9"/>
-      <c r="BP28" s="9"/>
-      <c r="BQ28" s="9"/>
-      <c r="BR28" s="9"/>
-      <c r="BS28" s="9"/>
-      <c r="BT28" s="9"/>
-      <c r="BU28" s="9"/>
-      <c r="BV28" s="9"/>
-      <c r="BW28" s="9"/>
-      <c r="BX28" s="9"/>
-      <c r="BY28" s="9"/>
-      <c r="BZ28" s="9"/>
-      <c r="CA28" s="9"/>
-      <c r="CB28" s="9"/>
-      <c r="CC28" s="9"/>
-      <c r="CD28" s="9"/>
-      <c r="CE28" s="9"/>
-      <c r="CF28" s="9"/>
-      <c r="CG28" s="9"/>
-      <c r="CH28" s="9"/>
-      <c r="CI28" s="9"/>
-      <c r="CJ28" s="9"/>
-      <c r="CK28" s="9"/>
-      <c r="CL28" s="9"/>
-      <c r="CM28" s="9"/>
-      <c r="CN28" s="9"/>
-      <c r="CO28" s="9"/>
-      <c r="CP28" s="9"/>
-      <c r="CQ28" s="9"/>
-      <c r="CR28" s="9"/>
-      <c r="CS28" s="9"/>
-      <c r="CT28" s="9"/>
-      <c r="CU28" s="9"/>
-      <c r="CV28" s="9"/>
-      <c r="CW28" s="9"/>
-      <c r="CX28" s="9"/>
-      <c r="CY28" s="9"/>
-      <c r="CZ28" s="9"/>
-      <c r="DA28" s="9"/>
-      <c r="DB28" s="9"/>
-      <c r="DC28" s="9"/>
-      <c r="DD28" s="9"/>
-      <c r="DE28" s="9"/>
-      <c r="DF28" s="9"/>
-      <c r="DG28" s="9"/>
-      <c r="DH28" s="9"/>
-      <c r="DI28" s="9"/>
-      <c r="DJ28" s="9"/>
-      <c r="DK28" s="9"/>
-      <c r="DL28" s="9"/>
-      <c r="DM28" s="9"/>
-      <c r="DN28" s="9"/>
-      <c r="DO28" s="9"/>
-      <c r="DP28" s="9"/>
-      <c r="DQ28" s="9"/>
-      <c r="DR28" s="9"/>
-      <c r="DS28" s="9"/>
-      <c r="DT28" s="9"/>
-      <c r="DU28" s="9"/>
-      <c r="DV28" s="9"/>
-      <c r="DW28" s="9"/>
-      <c r="DX28" s="9"/>
-      <c r="DY28" s="9"/>
-      <c r="DZ28" s="9"/>
-      <c r="EA28" s="9"/>
-      <c r="EB28" s="9"/>
-      <c r="EC28" s="9"/>
-      <c r="ED28" s="9"/>
-      <c r="EE28" s="9"/>
-      <c r="EF28" s="9"/>
-      <c r="EG28" s="9"/>
-      <c r="EH28" s="9"/>
-      <c r="EI28" s="9"/>
-      <c r="EJ28" s="9"/>
-      <c r="EK28" s="9"/>
-      <c r="EL28" s="9"/>
-      <c r="EM28" s="9"/>
-      <c r="EN28" s="9"/>
-      <c r="EO28" s="9"/>
-      <c r="EP28" s="9"/>
-      <c r="EQ28" s="9"/>
-      <c r="ER28" s="9"/>
-      <c r="ES28" s="9"/>
-      <c r="ET28" s="9"/>
-      <c r="EU28" s="9"/>
-      <c r="EV28" s="9"/>
-      <c r="EW28" s="9"/>
-      <c r="EX28" s="9"/>
-      <c r="EY28" s="9"/>
-      <c r="EZ28" s="9"/>
-      <c r="FA28" s="9"/>
-      <c r="FB28" s="9"/>
-      <c r="FC28" s="9"/>
-      <c r="FD28" s="9"/>
-      <c r="FE28" s="9"/>
-      <c r="FF28" s="9"/>
-      <c r="FG28" s="9"/>
-      <c r="FH28" s="9"/>
-      <c r="FI28" s="9"/>
-      <c r="FJ28" s="9"/>
-      <c r="FK28" s="9"/>
-      <c r="FL28" s="9"/>
-      <c r="FM28" s="9"/>
-      <c r="FN28" s="9"/>
-      <c r="FO28" s="9"/>
-      <c r="FP28" s="9"/>
-      <c r="FQ28" s="9"/>
-      <c r="FR28" s="9"/>
-      <c r="FS28" s="9"/>
-      <c r="FT28" s="9"/>
-      <c r="FU28" s="9"/>
-      <c r="FV28" s="9"/>
-      <c r="FW28" s="9"/>
-      <c r="FX28" s="9"/>
-      <c r="FY28" s="9"/>
-      <c r="FZ28" s="9"/>
-      <c r="GA28" s="9"/>
-      <c r="GB28" s="9"/>
-      <c r="GC28" s="9"/>
-      <c r="GD28" s="9"/>
-      <c r="GE28" s="9"/>
+    <row r="28" spans="1:187" ht="15" customHeight="1">
+      <c r="A28" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="51"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="J28" s="51"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="51"/>
+      <c r="M28" s="51"/>
+      <c r="N28" s="51"/>
+      <c r="O28" s="51"/>
+      <c r="P28" s="52"/>
+      <c r="Q28" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
+      <c r="W28" s="59"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="60"/>
+      <c r="Z28" s="60"/>
+      <c r="AA28" s="60"/>
+      <c r="AB28" s="60"/>
+      <c r="AC28" s="60"/>
+      <c r="AD28" s="61"/>
+      <c r="AE28" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF28" s="63"/>
+      <c r="AG28" s="63"/>
+      <c r="AH28" s="63"/>
+      <c r="AI28" s="63"/>
+      <c r="AJ28" s="63"/>
+      <c r="AK28" s="63"/>
+      <c r="AL28" s="63"/>
+      <c r="AM28" s="63"/>
+      <c r="AN28" s="63"/>
+      <c r="AO28" s="63"/>
+      <c r="AP28" s="63"/>
+      <c r="AQ28" s="63"/>
+      <c r="AR28" s="63"/>
+      <c r="AS28" s="63"/>
+      <c r="AT28" s="63"/>
+      <c r="AU28" s="63"/>
+      <c r="AV28" s="63"/>
+      <c r="AW28" s="63"/>
+      <c r="AX28" s="63"/>
+      <c r="AY28" s="63"/>
+      <c r="AZ28" s="63"/>
+      <c r="BA28" s="63"/>
+      <c r="BB28" s="63"/>
+      <c r="BC28" s="64"/>
+      <c r="BD28" s="1"/>
+      <c r="BE28" s="1"/>
+      <c r="BF28" s="1"/>
+      <c r="BG28" s="1"/>
+      <c r="BH28" s="1"/>
+      <c r="BI28" s="1"/>
+      <c r="BJ28" s="1"/>
+      <c r="BK28" s="1"/>
+      <c r="BL28" s="1"/>
+      <c r="BM28" s="1"/>
+      <c r="BN28" s="1"/>
+      <c r="BO28" s="1"/>
+      <c r="BP28" s="1"/>
+      <c r="BQ28" s="1"/>
+      <c r="BR28" s="1"/>
+      <c r="BS28" s="1"/>
+      <c r="BT28" s="1"/>
+      <c r="BU28" s="1"/>
+      <c r="BV28" s="1"/>
+      <c r="BW28" s="1"/>
+      <c r="BX28" s="1"/>
+      <c r="BY28" s="1"/>
+      <c r="BZ28" s="1"/>
+      <c r="CA28" s="1"/>
+      <c r="CB28" s="1"/>
+      <c r="CC28" s="1"/>
+      <c r="CD28" s="1"/>
+      <c r="CE28" s="1"/>
+      <c r="CF28" s="1"/>
+      <c r="CG28" s="1"/>
+      <c r="CH28" s="1"/>
+      <c r="CI28" s="1"/>
+      <c r="CJ28" s="1"/>
+      <c r="CK28" s="1"/>
+      <c r="CL28" s="1"/>
+      <c r="CM28" s="1"/>
+      <c r="CN28" s="1"/>
+      <c r="CO28" s="1"/>
+      <c r="CP28" s="1"/>
+      <c r="CQ28" s="1"/>
+      <c r="CR28" s="1"/>
+      <c r="CS28" s="1"/>
+      <c r="CT28" s="1"/>
+      <c r="CU28" s="1"/>
+      <c r="CV28" s="1"/>
+      <c r="CW28" s="1"/>
+      <c r="CX28" s="1"/>
+      <c r="CY28" s="1"/>
+      <c r="CZ28" s="1"/>
+      <c r="DA28" s="1"/>
+      <c r="DB28" s="1"/>
+      <c r="DC28" s="1"/>
+      <c r="DD28" s="1"/>
+      <c r="DE28" s="1"/>
+      <c r="DF28" s="1"/>
+      <c r="DG28" s="1"/>
+      <c r="DH28" s="1"/>
+      <c r="DI28" s="1"/>
+      <c r="DJ28" s="1"/>
+      <c r="DK28" s="1"/>
+      <c r="DL28" s="1"/>
+      <c r="DM28" s="1"/>
+      <c r="DN28" s="1"/>
+      <c r="DO28" s="1"/>
+      <c r="DP28" s="1"/>
+      <c r="DQ28" s="1"/>
+      <c r="DR28" s="1"/>
+      <c r="DS28" s="1"/>
+      <c r="DT28" s="1"/>
+      <c r="DU28" s="1"/>
+      <c r="DV28" s="1"/>
+      <c r="DW28" s="1"/>
+      <c r="DX28" s="1"/>
+      <c r="DY28" s="1"/>
+      <c r="DZ28" s="1"/>
+      <c r="EA28" s="1"/>
+      <c r="EB28" s="1"/>
+      <c r="EC28" s="1"/>
+      <c r="ED28" s="1"/>
+      <c r="EE28" s="1"/>
+      <c r="EF28" s="1"/>
+      <c r="EG28" s="1"/>
+      <c r="EH28" s="1"/>
+      <c r="EI28" s="1"/>
+      <c r="EJ28" s="1"/>
+      <c r="EK28" s="1"/>
+      <c r="EL28" s="1"/>
+      <c r="EM28" s="1"/>
+      <c r="EN28" s="1"/>
+      <c r="EO28" s="1"/>
+      <c r="EP28" s="1"/>
+      <c r="EQ28" s="1"/>
+      <c r="ER28" s="1"/>
+      <c r="ES28" s="1"/>
+      <c r="ET28" s="1"/>
+      <c r="EU28" s="1"/>
+      <c r="EV28" s="1"/>
+      <c r="EW28" s="1"/>
+      <c r="EX28" s="1"/>
+      <c r="EY28" s="1"/>
+      <c r="EZ28" s="1"/>
+      <c r="FA28" s="1"/>
+      <c r="FB28" s="1"/>
+      <c r="FC28" s="1"/>
+      <c r="FD28" s="1"/>
+      <c r="FE28" s="1"/>
+      <c r="FF28" s="1"/>
+      <c r="FG28" s="1"/>
+      <c r="FH28" s="1"/>
+      <c r="FI28" s="1"/>
+      <c r="FJ28" s="1"/>
+      <c r="FK28" s="1"/>
+      <c r="FL28" s="1"/>
+      <c r="FM28" s="1"/>
+      <c r="FN28" s="1"/>
+      <c r="FO28" s="1"/>
+      <c r="FP28" s="1"/>
+      <c r="FQ28" s="1"/>
+      <c r="FR28" s="1"/>
+      <c r="FS28" s="1"/>
+      <c r="FT28" s="1"/>
+      <c r="FU28" s="1"/>
+      <c r="FV28" s="1"/>
+      <c r="FW28" s="1"/>
+      <c r="FX28" s="1"/>
+      <c r="FY28" s="1"/>
+      <c r="FZ28" s="1"/>
+      <c r="GA28" s="1"/>
+      <c r="GB28" s="1"/>
+      <c r="GC28" s="1"/>
+      <c r="GD28" s="1"/>
+      <c r="GE28" s="1"/>
     </row>
-    <row r="29" spans="1:187" s="10" customFormat="1" ht="15" customHeight="1">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-      <c r="U29" s="12"/>
-      <c r="V29" s="12"/>
-      <c r="W29" s="14"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="14"/>
-      <c r="Z29" s="14"/>
-      <c r="AA29" s="14"/>
-      <c r="AB29" s="14"/>
-      <c r="AC29" s="14"/>
-      <c r="AD29" s="14"/>
-      <c r="AE29" s="15"/>
-      <c r="AF29" s="15"/>
-      <c r="AG29" s="15"/>
-      <c r="AH29" s="15"/>
-      <c r="AI29" s="15"/>
-      <c r="AJ29" s="15"/>
-      <c r="AK29" s="15"/>
-      <c r="AL29" s="15"/>
-      <c r="AM29" s="15"/>
-      <c r="AN29" s="15"/>
-      <c r="AO29" s="15"/>
-      <c r="AP29" s="15"/>
-      <c r="AQ29" s="15"/>
-      <c r="AR29" s="15"/>
-      <c r="AS29" s="15"/>
-      <c r="AT29" s="15"/>
-      <c r="AU29" s="15"/>
-      <c r="AV29" s="15"/>
-      <c r="AW29" s="15"/>
-      <c r="AX29" s="15"/>
-      <c r="AY29" s="15"/>
-      <c r="AZ29" s="15"/>
-      <c r="BA29" s="15"/>
-      <c r="BB29" s="15"/>
-      <c r="BC29" s="15"/>
-      <c r="BD29" s="9"/>
-      <c r="BE29" s="9"/>
-      <c r="BF29" s="9"/>
-      <c r="BG29" s="9"/>
-      <c r="BH29" s="9"/>
-      <c r="BI29" s="9"/>
-      <c r="BJ29" s="9"/>
-      <c r="BK29" s="9"/>
-      <c r="BL29" s="9"/>
-      <c r="BM29" s="9"/>
-      <c r="BN29" s="9"/>
-      <c r="BO29" s="9"/>
-      <c r="BP29" s="9"/>
-      <c r="BQ29" s="9"/>
-      <c r="BR29" s="9"/>
-      <c r="BS29" s="9"/>
-      <c r="BT29" s="9"/>
-      <c r="BU29" s="9"/>
-      <c r="BV29" s="9"/>
-      <c r="BW29" s="9"/>
-      <c r="BX29" s="9"/>
-      <c r="BY29" s="9"/>
-      <c r="BZ29" s="9"/>
-      <c r="CA29" s="9"/>
-      <c r="CB29" s="9"/>
-      <c r="CC29" s="9"/>
-      <c r="CD29" s="9"/>
-      <c r="CE29" s="9"/>
-      <c r="CF29" s="9"/>
-      <c r="CG29" s="9"/>
-      <c r="CH29" s="9"/>
-      <c r="CI29" s="9"/>
-      <c r="CJ29" s="9"/>
-      <c r="CK29" s="9"/>
-      <c r="CL29" s="9"/>
-      <c r="CM29" s="9"/>
-      <c r="CN29" s="9"/>
-      <c r="CO29" s="9"/>
-      <c r="CP29" s="9"/>
-      <c r="CQ29" s="9"/>
-      <c r="CR29" s="9"/>
-      <c r="CS29" s="9"/>
-      <c r="CT29" s="9"/>
-      <c r="CU29" s="9"/>
-      <c r="CV29" s="9"/>
-      <c r="CW29" s="9"/>
-      <c r="CX29" s="9"/>
-      <c r="CY29" s="9"/>
-      <c r="CZ29" s="9"/>
-      <c r="DA29" s="9"/>
-      <c r="DB29" s="9"/>
-      <c r="DC29" s="9"/>
-      <c r="DD29" s="9"/>
-      <c r="DE29" s="9"/>
-      <c r="DF29" s="9"/>
-      <c r="DG29" s="9"/>
-      <c r="DH29" s="9"/>
-      <c r="DI29" s="9"/>
-      <c r="DJ29" s="9"/>
-      <c r="DK29" s="9"/>
-      <c r="DL29" s="9"/>
-      <c r="DM29" s="9"/>
-      <c r="DN29" s="9"/>
-      <c r="DO29" s="9"/>
-      <c r="DP29" s="9"/>
-      <c r="DQ29" s="9"/>
-      <c r="DR29" s="9"/>
-      <c r="DS29" s="9"/>
-      <c r="DT29" s="9"/>
-      <c r="DU29" s="9"/>
-      <c r="DV29" s="9"/>
-      <c r="DW29" s="9"/>
-      <c r="DX29" s="9"/>
-      <c r="DY29" s="9"/>
-      <c r="DZ29" s="9"/>
-      <c r="EA29" s="9"/>
-      <c r="EB29" s="9"/>
-      <c r="EC29" s="9"/>
-      <c r="ED29" s="9"/>
-      <c r="EE29" s="9"/>
-      <c r="EF29" s="9"/>
-      <c r="EG29" s="9"/>
-      <c r="EH29" s="9"/>
-      <c r="EI29" s="9"/>
-      <c r="EJ29" s="9"/>
-      <c r="EK29" s="9"/>
-      <c r="EL29" s="9"/>
-      <c r="EM29" s="9"/>
-      <c r="EN29" s="9"/>
-      <c r="EO29" s="9"/>
-      <c r="EP29" s="9"/>
-      <c r="EQ29" s="9"/>
-      <c r="ER29" s="9"/>
-      <c r="ES29" s="9"/>
-      <c r="ET29" s="9"/>
-      <c r="EU29" s="9"/>
-      <c r="EV29" s="9"/>
-      <c r="EW29" s="9"/>
-      <c r="EX29" s="9"/>
-      <c r="EY29" s="9"/>
-      <c r="EZ29" s="9"/>
-      <c r="FA29" s="9"/>
-      <c r="FB29" s="9"/>
-      <c r="FC29" s="9"/>
-      <c r="FD29" s="9"/>
-      <c r="FE29" s="9"/>
-      <c r="FF29" s="9"/>
-      <c r="FG29" s="9"/>
-      <c r="FH29" s="9"/>
-      <c r="FI29" s="9"/>
-      <c r="FJ29" s="9"/>
-      <c r="FK29" s="9"/>
-      <c r="FL29" s="9"/>
-      <c r="FM29" s="9"/>
-      <c r="FN29" s="9"/>
-      <c r="FO29" s="9"/>
-      <c r="FP29" s="9"/>
-      <c r="FQ29" s="9"/>
-      <c r="FR29" s="9"/>
-      <c r="FS29" s="9"/>
-      <c r="FT29" s="9"/>
-      <c r="FU29" s="9"/>
-      <c r="FV29" s="9"/>
-      <c r="FW29" s="9"/>
-      <c r="FX29" s="9"/>
-      <c r="FY29" s="9"/>
-      <c r="FZ29" s="9"/>
-      <c r="GA29" s="9"/>
-      <c r="GB29" s="9"/>
-      <c r="GC29" s="9"/>
-      <c r="GD29" s="9"/>
-      <c r="GE29" s="9"/>
+    <row r="29" spans="1:187" ht="15" customHeight="1">
+      <c r="A29" s="56"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="53"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="54"/>
+      <c r="V29" s="55"/>
+      <c r="W29" s="59"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="60"/>
+      <c r="Z29" s="60"/>
+      <c r="AA29" s="60"/>
+      <c r="AB29" s="60"/>
+      <c r="AC29" s="60"/>
+      <c r="AD29" s="61"/>
+      <c r="AE29" s="62"/>
+      <c r="AF29" s="63"/>
+      <c r="AG29" s="63"/>
+      <c r="AH29" s="63"/>
+      <c r="AI29" s="63"/>
+      <c r="AJ29" s="63"/>
+      <c r="AK29" s="63"/>
+      <c r="AL29" s="63"/>
+      <c r="AM29" s="63"/>
+      <c r="AN29" s="63"/>
+      <c r="AO29" s="63"/>
+      <c r="AP29" s="63"/>
+      <c r="AQ29" s="63"/>
+      <c r="AR29" s="63"/>
+      <c r="AS29" s="63"/>
+      <c r="AT29" s="63"/>
+      <c r="AU29" s="63"/>
+      <c r="AV29" s="63"/>
+      <c r="AW29" s="63"/>
+      <c r="AX29" s="63"/>
+      <c r="AY29" s="63"/>
+      <c r="AZ29" s="63"/>
+      <c r="BA29" s="63"/>
+      <c r="BB29" s="63"/>
+      <c r="BC29" s="64"/>
+      <c r="BD29" s="1"/>
+      <c r="BE29" s="1"/>
+      <c r="BF29" s="1"/>
+      <c r="BG29" s="1"/>
+      <c r="BH29" s="1"/>
+      <c r="BI29" s="1"/>
+      <c r="BJ29" s="1"/>
+      <c r="BK29" s="1"/>
+      <c r="BL29" s="1"/>
+      <c r="BM29" s="1"/>
+      <c r="BN29" s="1"/>
+      <c r="BO29" s="1"/>
+      <c r="BP29" s="1"/>
+      <c r="BQ29" s="1"/>
+      <c r="BR29" s="1"/>
+      <c r="BS29" s="1"/>
+      <c r="BT29" s="1"/>
+      <c r="BU29" s="1"/>
+      <c r="BV29" s="1"/>
+      <c r="BW29" s="1"/>
+      <c r="BX29" s="1"/>
+      <c r="BY29" s="1"/>
+      <c r="BZ29" s="1"/>
+      <c r="CA29" s="1"/>
+      <c r="CB29" s="1"/>
+      <c r="CC29" s="1"/>
+      <c r="CD29" s="1"/>
+      <c r="CE29" s="1"/>
+      <c r="CF29" s="1"/>
+      <c r="CG29" s="1"/>
+      <c r="CH29" s="1"/>
+      <c r="CI29" s="1"/>
+      <c r="CJ29" s="1"/>
+      <c r="CK29" s="1"/>
+      <c r="CL29" s="1"/>
+      <c r="CM29" s="1"/>
+      <c r="CN29" s="1"/>
+      <c r="CO29" s="1"/>
+      <c r="CP29" s="1"/>
+      <c r="CQ29" s="1"/>
+      <c r="CR29" s="1"/>
+      <c r="CS29" s="1"/>
+      <c r="CT29" s="1"/>
+      <c r="CU29" s="1"/>
+      <c r="CV29" s="1"/>
+      <c r="CW29" s="1"/>
+      <c r="CX29" s="1"/>
+      <c r="CY29" s="1"/>
+      <c r="CZ29" s="1"/>
+      <c r="DA29" s="1"/>
+      <c r="DB29" s="1"/>
+      <c r="DC29" s="1"/>
+      <c r="DD29" s="1"/>
+      <c r="DE29" s="1"/>
+      <c r="DF29" s="1"/>
+      <c r="DG29" s="1"/>
+      <c r="DH29" s="1"/>
+      <c r="DI29" s="1"/>
+      <c r="DJ29" s="1"/>
+      <c r="DK29" s="1"/>
+      <c r="DL29" s="1"/>
+      <c r="DM29" s="1"/>
+      <c r="DN29" s="1"/>
+      <c r="DO29" s="1"/>
+      <c r="DP29" s="1"/>
+      <c r="DQ29" s="1"/>
+      <c r="DR29" s="1"/>
+      <c r="DS29" s="1"/>
+      <c r="DT29" s="1"/>
+      <c r="DU29" s="1"/>
+      <c r="DV29" s="1"/>
+      <c r="DW29" s="1"/>
+      <c r="DX29" s="1"/>
+      <c r="DY29" s="1"/>
+      <c r="DZ29" s="1"/>
+      <c r="EA29" s="1"/>
+      <c r="EB29" s="1"/>
+      <c r="EC29" s="1"/>
+      <c r="ED29" s="1"/>
+      <c r="EE29" s="1"/>
+      <c r="EF29" s="1"/>
+      <c r="EG29" s="1"/>
+      <c r="EH29" s="1"/>
+      <c r="EI29" s="1"/>
+      <c r="EJ29" s="1"/>
+      <c r="EK29" s="1"/>
+      <c r="EL29" s="1"/>
+      <c r="EM29" s="1"/>
+      <c r="EN29" s="1"/>
+      <c r="EO29" s="1"/>
+      <c r="EP29" s="1"/>
+      <c r="EQ29" s="1"/>
+      <c r="ER29" s="1"/>
+      <c r="ES29" s="1"/>
+      <c r="ET29" s="1"/>
+      <c r="EU29" s="1"/>
+      <c r="EV29" s="1"/>
+      <c r="EW29" s="1"/>
+      <c r="EX29" s="1"/>
+      <c r="EY29" s="1"/>
+      <c r="EZ29" s="1"/>
+      <c r="FA29" s="1"/>
+      <c r="FB29" s="1"/>
+      <c r="FC29" s="1"/>
+      <c r="FD29" s="1"/>
+      <c r="FE29" s="1"/>
+      <c r="FF29" s="1"/>
+      <c r="FG29" s="1"/>
+      <c r="FH29" s="1"/>
+      <c r="FI29" s="1"/>
+      <c r="FJ29" s="1"/>
+      <c r="FK29" s="1"/>
+      <c r="FL29" s="1"/>
+      <c r="FM29" s="1"/>
+      <c r="FN29" s="1"/>
+      <c r="FO29" s="1"/>
+      <c r="FP29" s="1"/>
+      <c r="FQ29" s="1"/>
+      <c r="FR29" s="1"/>
+      <c r="FS29" s="1"/>
+      <c r="FT29" s="1"/>
+      <c r="FU29" s="1"/>
+      <c r="FV29" s="1"/>
+      <c r="FW29" s="1"/>
+      <c r="FX29" s="1"/>
+      <c r="FY29" s="1"/>
+      <c r="FZ29" s="1"/>
+      <c r="GA29" s="1"/>
+      <c r="GB29" s="1"/>
+      <c r="GC29" s="1"/>
+      <c r="GD29" s="1"/>
+      <c r="GE29" s="1"/>
     </row>
     <row r="30" spans="1:187" s="10" customFormat="1" ht="15" customHeight="1">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="13"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="14"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="14"/>
-      <c r="AB30" s="14"/>
-      <c r="AC30" s="14"/>
-      <c r="AD30" s="14"/>
-      <c r="AE30" s="15"/>
-      <c r="AF30" s="15"/>
-      <c r="AG30" s="15"/>
-      <c r="AH30" s="15"/>
-      <c r="AI30" s="15"/>
-      <c r="AJ30" s="15"/>
-      <c r="AK30" s="15"/>
-      <c r="AL30" s="15"/>
-      <c r="AM30" s="15"/>
-      <c r="AN30" s="15"/>
-      <c r="AO30" s="15"/>
-      <c r="AP30" s="15"/>
-      <c r="AQ30" s="15"/>
-      <c r="AR30" s="15"/>
-      <c r="AS30" s="15"/>
-      <c r="AT30" s="15"/>
-      <c r="AU30" s="15"/>
-      <c r="AV30" s="15"/>
-      <c r="AW30" s="15"/>
-      <c r="AX30" s="15"/>
-      <c r="AY30" s="15"/>
-      <c r="AZ30" s="15"/>
-      <c r="BA30" s="15"/>
-      <c r="BB30" s="15"/>
-      <c r="BC30" s="15"/>
+      <c r="A30" s="68"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="73"/>
+      <c r="Q30" s="68"/>
+      <c r="R30" s="69"/>
+      <c r="S30" s="69"/>
+      <c r="T30" s="69"/>
+      <c r="U30" s="69"/>
+      <c r="V30" s="70"/>
+      <c r="W30" s="65"/>
+      <c r="X30" s="66"/>
+      <c r="Y30" s="66"/>
+      <c r="Z30" s="66"/>
+      <c r="AA30" s="66"/>
+      <c r="AB30" s="66"/>
+      <c r="AC30" s="66"/>
+      <c r="AD30" s="67"/>
+      <c r="AE30" s="62"/>
+      <c r="AF30" s="63"/>
+      <c r="AG30" s="63"/>
+      <c r="AH30" s="63"/>
+      <c r="AI30" s="63"/>
+      <c r="AJ30" s="63"/>
+      <c r="AK30" s="63"/>
+      <c r="AL30" s="63"/>
+      <c r="AM30" s="63"/>
+      <c r="AN30" s="63"/>
+      <c r="AO30" s="63"/>
+      <c r="AP30" s="63"/>
+      <c r="AQ30" s="63"/>
+      <c r="AR30" s="63"/>
+      <c r="AS30" s="63"/>
+      <c r="AT30" s="63"/>
+      <c r="AU30" s="63"/>
+      <c r="AV30" s="63"/>
+      <c r="AW30" s="63"/>
+      <c r="AX30" s="63"/>
+      <c r="AY30" s="63"/>
+      <c r="AZ30" s="63"/>
+      <c r="BA30" s="63"/>
+      <c r="BB30" s="63"/>
+      <c r="BC30" s="64"/>
       <c r="BD30" s="9"/>
       <c r="BE30" s="9"/>
       <c r="BF30" s="9"/>
@@ -7037,950 +7103,950 @@
       <c r="GD30" s="9"/>
       <c r="GE30" s="9"/>
     </row>
-    <row r="31" spans="1:187" ht="15" customHeight="1">
-      <c r="A31" s="23"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17"/>
-      <c r="T31" s="17"/>
-      <c r="U31" s="17"/>
-      <c r="V31" s="17"/>
+    <row r="31" spans="1:187" s="10" customFormat="1" ht="15" customHeight="1">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12"/>
       <c r="W31" s="14"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="18"/>
-      <c r="Z31" s="18"/>
-      <c r="AA31" s="18"/>
-      <c r="AB31" s="18"/>
-      <c r="AC31" s="18"/>
-      <c r="AD31" s="18"/>
-      <c r="AE31" s="19"/>
-      <c r="AF31" s="20"/>
-      <c r="AG31" s="20"/>
-      <c r="AH31" s="20"/>
-      <c r="AI31" s="20"/>
-      <c r="AJ31" s="20"/>
-      <c r="AK31" s="20"/>
-      <c r="AL31" s="20"/>
-      <c r="AM31" s="20"/>
-      <c r="AN31" s="20"/>
-      <c r="AO31" s="20"/>
-      <c r="AP31" s="20"/>
-      <c r="AQ31" s="20"/>
-      <c r="AR31" s="20"/>
-      <c r="AS31" s="20"/>
-      <c r="AT31" s="20"/>
-      <c r="AU31" s="20"/>
-      <c r="AV31" s="20"/>
-      <c r="AW31" s="20"/>
-      <c r="AX31" s="20"/>
-      <c r="AY31" s="20"/>
-      <c r="AZ31" s="20"/>
-      <c r="BA31" s="20"/>
-      <c r="BB31" s="20"/>
-      <c r="BC31" s="20"/>
-      <c r="BD31" s="1"/>
-      <c r="BE31" s="1"/>
-      <c r="BF31" s="1"/>
-      <c r="BG31" s="1"/>
-      <c r="BH31" s="1"/>
-      <c r="BI31" s="1"/>
-      <c r="BJ31" s="1"/>
-      <c r="BK31" s="1"/>
-      <c r="BL31" s="1"/>
-      <c r="BM31" s="1"/>
-      <c r="BN31" s="1"/>
-      <c r="BO31" s="1"/>
-      <c r="BP31" s="1"/>
-      <c r="BQ31" s="1"/>
-      <c r="BR31" s="1"/>
-      <c r="BS31" s="1"/>
-      <c r="BT31" s="1"/>
-      <c r="BU31" s="1"/>
-      <c r="BV31" s="1"/>
-      <c r="BW31" s="1"/>
-      <c r="BX31" s="1"/>
-      <c r="BY31" s="1"/>
-      <c r="BZ31" s="1"/>
-      <c r="CA31" s="1"/>
-      <c r="CB31" s="1"/>
-      <c r="CC31" s="1"/>
-      <c r="CD31" s="1"/>
-      <c r="CE31" s="1"/>
-      <c r="CF31" s="1"/>
-      <c r="CG31" s="1"/>
-      <c r="CH31" s="1"/>
-      <c r="CI31" s="1"/>
-      <c r="CJ31" s="1"/>
-      <c r="CK31" s="1"/>
-      <c r="CL31" s="1"/>
-      <c r="CM31" s="1"/>
-      <c r="CN31" s="1"/>
-      <c r="CO31" s="1"/>
-      <c r="CP31" s="1"/>
-      <c r="CQ31" s="1"/>
-      <c r="CR31" s="1"/>
-      <c r="CS31" s="1"/>
-      <c r="CT31" s="1"/>
-      <c r="CU31" s="1"/>
-      <c r="CV31" s="1"/>
-      <c r="CW31" s="1"/>
-      <c r="CX31" s="1"/>
-      <c r="CY31" s="1"/>
-      <c r="CZ31" s="1"/>
-      <c r="DA31" s="1"/>
-      <c r="DB31" s="1"/>
-      <c r="DC31" s="1"/>
-      <c r="DD31" s="1"/>
-      <c r="DE31" s="1"/>
-      <c r="DF31" s="1"/>
-      <c r="DG31" s="1"/>
-      <c r="DH31" s="1"/>
-      <c r="DI31" s="1"/>
-      <c r="DJ31" s="1"/>
-      <c r="DK31" s="1"/>
-      <c r="DL31" s="1"/>
-      <c r="DM31" s="1"/>
-      <c r="DN31" s="1"/>
-      <c r="DO31" s="1"/>
-      <c r="DP31" s="1"/>
-      <c r="DQ31" s="1"/>
-      <c r="DR31" s="1"/>
-      <c r="DS31" s="1"/>
-      <c r="DT31" s="1"/>
-      <c r="DU31" s="1"/>
-      <c r="DV31" s="1"/>
-      <c r="DW31" s="1"/>
-      <c r="DX31" s="1"/>
-      <c r="DY31" s="1"/>
-      <c r="DZ31" s="1"/>
-      <c r="EA31" s="1"/>
-      <c r="EB31" s="1"/>
-      <c r="EC31" s="1"/>
-      <c r="ED31" s="1"/>
-      <c r="EE31" s="1"/>
-      <c r="EF31" s="1"/>
-      <c r="EG31" s="1"/>
-      <c r="EH31" s="1"/>
-      <c r="EI31" s="1"/>
-      <c r="EJ31" s="1"/>
-      <c r="EK31" s="1"/>
-      <c r="EL31" s="1"/>
-      <c r="EM31" s="1"/>
-      <c r="EN31" s="1"/>
-      <c r="EO31" s="1"/>
-      <c r="EP31" s="1"/>
-      <c r="EQ31" s="1"/>
-      <c r="ER31" s="1"/>
-      <c r="ES31" s="1"/>
-      <c r="ET31" s="1"/>
-      <c r="EU31" s="1"/>
-      <c r="EV31" s="1"/>
-      <c r="EW31" s="1"/>
-      <c r="EX31" s="1"/>
-      <c r="EY31" s="1"/>
-      <c r="EZ31" s="1"/>
-      <c r="FA31" s="1"/>
-      <c r="FB31" s="1"/>
-      <c r="FC31" s="1"/>
-      <c r="FD31" s="1"/>
-      <c r="FE31" s="1"/>
-      <c r="FF31" s="1"/>
-      <c r="FG31" s="1"/>
-      <c r="FH31" s="1"/>
-      <c r="FI31" s="1"/>
-      <c r="FJ31" s="1"/>
-      <c r="FK31" s="1"/>
-      <c r="FL31" s="1"/>
-      <c r="FM31" s="1"/>
-      <c r="FN31" s="1"/>
-      <c r="FO31" s="1"/>
-      <c r="FP31" s="1"/>
-      <c r="FQ31" s="1"/>
-      <c r="FR31" s="1"/>
-      <c r="FS31" s="1"/>
-      <c r="FT31" s="1"/>
-      <c r="FU31" s="1"/>
-      <c r="FV31" s="1"/>
-      <c r="FW31" s="1"/>
-      <c r="FX31" s="1"/>
-      <c r="FY31" s="1"/>
-      <c r="FZ31" s="1"/>
-      <c r="GA31" s="1"/>
-      <c r="GB31" s="1"/>
-      <c r="GC31" s="1"/>
-      <c r="GD31" s="1"/>
-      <c r="GE31" s="1"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="14"/>
+      <c r="AE31" s="15"/>
+      <c r="AF31" s="15"/>
+      <c r="AG31" s="15"/>
+      <c r="AH31" s="15"/>
+      <c r="AI31" s="15"/>
+      <c r="AJ31" s="15"/>
+      <c r="AK31" s="15"/>
+      <c r="AL31" s="15"/>
+      <c r="AM31" s="15"/>
+      <c r="AN31" s="15"/>
+      <c r="AO31" s="15"/>
+      <c r="AP31" s="15"/>
+      <c r="AQ31" s="15"/>
+      <c r="AR31" s="15"/>
+      <c r="AS31" s="15"/>
+      <c r="AT31" s="15"/>
+      <c r="AU31" s="15"/>
+      <c r="AV31" s="15"/>
+      <c r="AW31" s="15"/>
+      <c r="AX31" s="15"/>
+      <c r="AY31" s="15"/>
+      <c r="AZ31" s="15"/>
+      <c r="BA31" s="15"/>
+      <c r="BB31" s="15"/>
+      <c r="BC31" s="15"/>
+      <c r="BD31" s="9"/>
+      <c r="BE31" s="9"/>
+      <c r="BF31" s="9"/>
+      <c r="BG31" s="9"/>
+      <c r="BH31" s="9"/>
+      <c r="BI31" s="9"/>
+      <c r="BJ31" s="9"/>
+      <c r="BK31" s="9"/>
+      <c r="BL31" s="9"/>
+      <c r="BM31" s="9"/>
+      <c r="BN31" s="9"/>
+      <c r="BO31" s="9"/>
+      <c r="BP31" s="9"/>
+      <c r="BQ31" s="9"/>
+      <c r="BR31" s="9"/>
+      <c r="BS31" s="9"/>
+      <c r="BT31" s="9"/>
+      <c r="BU31" s="9"/>
+      <c r="BV31" s="9"/>
+      <c r="BW31" s="9"/>
+      <c r="BX31" s="9"/>
+      <c r="BY31" s="9"/>
+      <c r="BZ31" s="9"/>
+      <c r="CA31" s="9"/>
+      <c r="CB31" s="9"/>
+      <c r="CC31" s="9"/>
+      <c r="CD31" s="9"/>
+      <c r="CE31" s="9"/>
+      <c r="CF31" s="9"/>
+      <c r="CG31" s="9"/>
+      <c r="CH31" s="9"/>
+      <c r="CI31" s="9"/>
+      <c r="CJ31" s="9"/>
+      <c r="CK31" s="9"/>
+      <c r="CL31" s="9"/>
+      <c r="CM31" s="9"/>
+      <c r="CN31" s="9"/>
+      <c r="CO31" s="9"/>
+      <c r="CP31" s="9"/>
+      <c r="CQ31" s="9"/>
+      <c r="CR31" s="9"/>
+      <c r="CS31" s="9"/>
+      <c r="CT31" s="9"/>
+      <c r="CU31" s="9"/>
+      <c r="CV31" s="9"/>
+      <c r="CW31" s="9"/>
+      <c r="CX31" s="9"/>
+      <c r="CY31" s="9"/>
+      <c r="CZ31" s="9"/>
+      <c r="DA31" s="9"/>
+      <c r="DB31" s="9"/>
+      <c r="DC31" s="9"/>
+      <c r="DD31" s="9"/>
+      <c r="DE31" s="9"/>
+      <c r="DF31" s="9"/>
+      <c r="DG31" s="9"/>
+      <c r="DH31" s="9"/>
+      <c r="DI31" s="9"/>
+      <c r="DJ31" s="9"/>
+      <c r="DK31" s="9"/>
+      <c r="DL31" s="9"/>
+      <c r="DM31" s="9"/>
+      <c r="DN31" s="9"/>
+      <c r="DO31" s="9"/>
+      <c r="DP31" s="9"/>
+      <c r="DQ31" s="9"/>
+      <c r="DR31" s="9"/>
+      <c r="DS31" s="9"/>
+      <c r="DT31" s="9"/>
+      <c r="DU31" s="9"/>
+      <c r="DV31" s="9"/>
+      <c r="DW31" s="9"/>
+      <c r="DX31" s="9"/>
+      <c r="DY31" s="9"/>
+      <c r="DZ31" s="9"/>
+      <c r="EA31" s="9"/>
+      <c r="EB31" s="9"/>
+      <c r="EC31" s="9"/>
+      <c r="ED31" s="9"/>
+      <c r="EE31" s="9"/>
+      <c r="EF31" s="9"/>
+      <c r="EG31" s="9"/>
+      <c r="EH31" s="9"/>
+      <c r="EI31" s="9"/>
+      <c r="EJ31" s="9"/>
+      <c r="EK31" s="9"/>
+      <c r="EL31" s="9"/>
+      <c r="EM31" s="9"/>
+      <c r="EN31" s="9"/>
+      <c r="EO31" s="9"/>
+      <c r="EP31" s="9"/>
+      <c r="EQ31" s="9"/>
+      <c r="ER31" s="9"/>
+      <c r="ES31" s="9"/>
+      <c r="ET31" s="9"/>
+      <c r="EU31" s="9"/>
+      <c r="EV31" s="9"/>
+      <c r="EW31" s="9"/>
+      <c r="EX31" s="9"/>
+      <c r="EY31" s="9"/>
+      <c r="EZ31" s="9"/>
+      <c r="FA31" s="9"/>
+      <c r="FB31" s="9"/>
+      <c r="FC31" s="9"/>
+      <c r="FD31" s="9"/>
+      <c r="FE31" s="9"/>
+      <c r="FF31" s="9"/>
+      <c r="FG31" s="9"/>
+      <c r="FH31" s="9"/>
+      <c r="FI31" s="9"/>
+      <c r="FJ31" s="9"/>
+      <c r="FK31" s="9"/>
+      <c r="FL31" s="9"/>
+      <c r="FM31" s="9"/>
+      <c r="FN31" s="9"/>
+      <c r="FO31" s="9"/>
+      <c r="FP31" s="9"/>
+      <c r="FQ31" s="9"/>
+      <c r="FR31" s="9"/>
+      <c r="FS31" s="9"/>
+      <c r="FT31" s="9"/>
+      <c r="FU31" s="9"/>
+      <c r="FV31" s="9"/>
+      <c r="FW31" s="9"/>
+      <c r="FX31" s="9"/>
+      <c r="FY31" s="9"/>
+      <c r="FZ31" s="9"/>
+      <c r="GA31" s="9"/>
+      <c r="GB31" s="9"/>
+      <c r="GC31" s="9"/>
+      <c r="GD31" s="9"/>
+      <c r="GE31" s="9"/>
     </row>
-    <row r="32" spans="1:187" ht="15" customHeight="1">
-      <c r="A32" s="23"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
-      <c r="V32" s="17"/>
-      <c r="W32" s="18"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="18"/>
-      <c r="Z32" s="18"/>
-      <c r="AA32" s="18"/>
-      <c r="AB32" s="18"/>
-      <c r="AC32" s="18"/>
-      <c r="AD32" s="18"/>
-      <c r="AE32" s="19"/>
-      <c r="AF32" s="20"/>
-      <c r="AG32" s="20"/>
-      <c r="AH32" s="20"/>
-      <c r="AI32" s="20"/>
-      <c r="AJ32" s="20"/>
-      <c r="AK32" s="20"/>
-      <c r="AL32" s="20"/>
-      <c r="AM32" s="20"/>
-      <c r="AN32" s="20"/>
-      <c r="AO32" s="20"/>
-      <c r="AP32" s="20"/>
-      <c r="AQ32" s="20"/>
-      <c r="AR32" s="20"/>
-      <c r="AS32" s="20"/>
-      <c r="AT32" s="20"/>
-      <c r="AU32" s="20"/>
-      <c r="AV32" s="20"/>
-      <c r="AW32" s="20"/>
-      <c r="AX32" s="20"/>
-      <c r="AY32" s="20"/>
-      <c r="AZ32" s="20"/>
-      <c r="BA32" s="20"/>
-      <c r="BB32" s="20"/>
-      <c r="BC32" s="20"/>
-      <c r="BD32" s="1"/>
-      <c r="BE32" s="1"/>
-      <c r="BF32" s="1"/>
-      <c r="BG32" s="1"/>
-      <c r="BH32" s="1"/>
-      <c r="BI32" s="1"/>
-      <c r="BJ32" s="1"/>
-      <c r="BK32" s="1"/>
-      <c r="BL32" s="1"/>
-      <c r="BM32" s="1"/>
-      <c r="BN32" s="1"/>
-      <c r="BO32" s="1"/>
-      <c r="BP32" s="1"/>
-      <c r="BQ32" s="1"/>
-      <c r="BR32" s="1"/>
-      <c r="BS32" s="1"/>
-      <c r="BT32" s="1"/>
-      <c r="BU32" s="1"/>
-      <c r="BV32" s="1"/>
-      <c r="BW32" s="1"/>
-      <c r="BX32" s="1"/>
-      <c r="BY32" s="1"/>
-      <c r="BZ32" s="1"/>
-      <c r="CA32" s="1"/>
-      <c r="CB32" s="1"/>
-      <c r="CC32" s="1"/>
-      <c r="CD32" s="1"/>
-      <c r="CE32" s="1"/>
-      <c r="CF32" s="1"/>
-      <c r="CG32" s="1"/>
-      <c r="CH32" s="1"/>
-      <c r="CI32" s="1"/>
-      <c r="CJ32" s="1"/>
-      <c r="CK32" s="1"/>
-      <c r="CL32" s="1"/>
-      <c r="CM32" s="1"/>
-      <c r="CN32" s="1"/>
-      <c r="CO32" s="1"/>
-      <c r="CP32" s="1"/>
-      <c r="CQ32" s="1"/>
-      <c r="CR32" s="1"/>
-      <c r="CS32" s="1"/>
-      <c r="CT32" s="1"/>
-      <c r="CU32" s="1"/>
-      <c r="CV32" s="1"/>
-      <c r="CW32" s="1"/>
-      <c r="CX32" s="1"/>
-      <c r="CY32" s="1"/>
-      <c r="CZ32" s="1"/>
-      <c r="DA32" s="1"/>
-      <c r="DB32" s="1"/>
-      <c r="DC32" s="1"/>
-      <c r="DD32" s="1"/>
-      <c r="DE32" s="1"/>
-      <c r="DF32" s="1"/>
-      <c r="DG32" s="1"/>
-      <c r="DH32" s="1"/>
-      <c r="DI32" s="1"/>
-      <c r="DJ32" s="1"/>
-      <c r="DK32" s="1"/>
-      <c r="DL32" s="1"/>
-      <c r="DM32" s="1"/>
-      <c r="DN32" s="1"/>
-      <c r="DO32" s="1"/>
-      <c r="DP32" s="1"/>
-      <c r="DQ32" s="1"/>
-      <c r="DR32" s="1"/>
-      <c r="DS32" s="1"/>
-      <c r="DT32" s="1"/>
-      <c r="DU32" s="1"/>
-      <c r="DV32" s="1"/>
-      <c r="DW32" s="1"/>
-      <c r="DX32" s="1"/>
-      <c r="DY32" s="1"/>
-      <c r="DZ32" s="1"/>
-      <c r="EA32" s="1"/>
-      <c r="EB32" s="1"/>
-      <c r="EC32" s="1"/>
-      <c r="ED32" s="1"/>
-      <c r="EE32" s="1"/>
-      <c r="EF32" s="1"/>
-      <c r="EG32" s="1"/>
-      <c r="EH32" s="1"/>
-      <c r="EI32" s="1"/>
-      <c r="EJ32" s="1"/>
-      <c r="EK32" s="1"/>
-      <c r="EL32" s="1"/>
-      <c r="EM32" s="1"/>
-      <c r="EN32" s="1"/>
-      <c r="EO32" s="1"/>
-      <c r="EP32" s="1"/>
-      <c r="EQ32" s="1"/>
-      <c r="ER32" s="1"/>
-      <c r="ES32" s="1"/>
-      <c r="ET32" s="1"/>
-      <c r="EU32" s="1"/>
-      <c r="EV32" s="1"/>
-      <c r="EW32" s="1"/>
-      <c r="EX32" s="1"/>
-      <c r="EY32" s="1"/>
-      <c r="EZ32" s="1"/>
-      <c r="FA32" s="1"/>
-      <c r="FB32" s="1"/>
-      <c r="FC32" s="1"/>
-      <c r="FD32" s="1"/>
-      <c r="FE32" s="1"/>
-      <c r="FF32" s="1"/>
-      <c r="FG32" s="1"/>
-      <c r="FH32" s="1"/>
-      <c r="FI32" s="1"/>
-      <c r="FJ32" s="1"/>
-      <c r="FK32" s="1"/>
-      <c r="FL32" s="1"/>
-      <c r="FM32" s="1"/>
-      <c r="FN32" s="1"/>
-      <c r="FO32" s="1"/>
-      <c r="FP32" s="1"/>
-      <c r="FQ32" s="1"/>
-      <c r="FR32" s="1"/>
-      <c r="FS32" s="1"/>
-      <c r="FT32" s="1"/>
-      <c r="FU32" s="1"/>
-      <c r="FV32" s="1"/>
-      <c r="FW32" s="1"/>
-      <c r="FX32" s="1"/>
-      <c r="FY32" s="1"/>
-      <c r="FZ32" s="1"/>
-      <c r="GA32" s="1"/>
-      <c r="GB32" s="1"/>
-      <c r="GC32" s="1"/>
-      <c r="GD32" s="1"/>
-      <c r="GE32" s="1"/>
+    <row r="32" spans="1:187" s="10" customFormat="1" ht="15" customHeight="1">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+      <c r="T32" s="12"/>
+      <c r="U32" s="12"/>
+      <c r="V32" s="12"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+      <c r="AA32" s="14"/>
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="14"/>
+      <c r="AE32" s="15"/>
+      <c r="AF32" s="15"/>
+      <c r="AG32" s="15"/>
+      <c r="AH32" s="15"/>
+      <c r="AI32" s="15"/>
+      <c r="AJ32" s="15"/>
+      <c r="AK32" s="15"/>
+      <c r="AL32" s="15"/>
+      <c r="AM32" s="15"/>
+      <c r="AN32" s="15"/>
+      <c r="AO32" s="15"/>
+      <c r="AP32" s="15"/>
+      <c r="AQ32" s="15"/>
+      <c r="AR32" s="15"/>
+      <c r="AS32" s="15"/>
+      <c r="AT32" s="15"/>
+      <c r="AU32" s="15"/>
+      <c r="AV32" s="15"/>
+      <c r="AW32" s="15"/>
+      <c r="AX32" s="15"/>
+      <c r="AY32" s="15"/>
+      <c r="AZ32" s="15"/>
+      <c r="BA32" s="15"/>
+      <c r="BB32" s="15"/>
+      <c r="BC32" s="15"/>
+      <c r="BD32" s="9"/>
+      <c r="BE32" s="9"/>
+      <c r="BF32" s="9"/>
+      <c r="BG32" s="9"/>
+      <c r="BH32" s="9"/>
+      <c r="BI32" s="9"/>
+      <c r="BJ32" s="9"/>
+      <c r="BK32" s="9"/>
+      <c r="BL32" s="9"/>
+      <c r="BM32" s="9"/>
+      <c r="BN32" s="9"/>
+      <c r="BO32" s="9"/>
+      <c r="BP32" s="9"/>
+      <c r="BQ32" s="9"/>
+      <c r="BR32" s="9"/>
+      <c r="BS32" s="9"/>
+      <c r="BT32" s="9"/>
+      <c r="BU32" s="9"/>
+      <c r="BV32" s="9"/>
+      <c r="BW32" s="9"/>
+      <c r="BX32" s="9"/>
+      <c r="BY32" s="9"/>
+      <c r="BZ32" s="9"/>
+      <c r="CA32" s="9"/>
+      <c r="CB32" s="9"/>
+      <c r="CC32" s="9"/>
+      <c r="CD32" s="9"/>
+      <c r="CE32" s="9"/>
+      <c r="CF32" s="9"/>
+      <c r="CG32" s="9"/>
+      <c r="CH32" s="9"/>
+      <c r="CI32" s="9"/>
+      <c r="CJ32" s="9"/>
+      <c r="CK32" s="9"/>
+      <c r="CL32" s="9"/>
+      <c r="CM32" s="9"/>
+      <c r="CN32" s="9"/>
+      <c r="CO32" s="9"/>
+      <c r="CP32" s="9"/>
+      <c r="CQ32" s="9"/>
+      <c r="CR32" s="9"/>
+      <c r="CS32" s="9"/>
+      <c r="CT32" s="9"/>
+      <c r="CU32" s="9"/>
+      <c r="CV32" s="9"/>
+      <c r="CW32" s="9"/>
+      <c r="CX32" s="9"/>
+      <c r="CY32" s="9"/>
+      <c r="CZ32" s="9"/>
+      <c r="DA32" s="9"/>
+      <c r="DB32" s="9"/>
+      <c r="DC32" s="9"/>
+      <c r="DD32" s="9"/>
+      <c r="DE32" s="9"/>
+      <c r="DF32" s="9"/>
+      <c r="DG32" s="9"/>
+      <c r="DH32" s="9"/>
+      <c r="DI32" s="9"/>
+      <c r="DJ32" s="9"/>
+      <c r="DK32" s="9"/>
+      <c r="DL32" s="9"/>
+      <c r="DM32" s="9"/>
+      <c r="DN32" s="9"/>
+      <c r="DO32" s="9"/>
+      <c r="DP32" s="9"/>
+      <c r="DQ32" s="9"/>
+      <c r="DR32" s="9"/>
+      <c r="DS32" s="9"/>
+      <c r="DT32" s="9"/>
+      <c r="DU32" s="9"/>
+      <c r="DV32" s="9"/>
+      <c r="DW32" s="9"/>
+      <c r="DX32" s="9"/>
+      <c r="DY32" s="9"/>
+      <c r="DZ32" s="9"/>
+      <c r="EA32" s="9"/>
+      <c r="EB32" s="9"/>
+      <c r="EC32" s="9"/>
+      <c r="ED32" s="9"/>
+      <c r="EE32" s="9"/>
+      <c r="EF32" s="9"/>
+      <c r="EG32" s="9"/>
+      <c r="EH32" s="9"/>
+      <c r="EI32" s="9"/>
+      <c r="EJ32" s="9"/>
+      <c r="EK32" s="9"/>
+      <c r="EL32" s="9"/>
+      <c r="EM32" s="9"/>
+      <c r="EN32" s="9"/>
+      <c r="EO32" s="9"/>
+      <c r="EP32" s="9"/>
+      <c r="EQ32" s="9"/>
+      <c r="ER32" s="9"/>
+      <c r="ES32" s="9"/>
+      <c r="ET32" s="9"/>
+      <c r="EU32" s="9"/>
+      <c r="EV32" s="9"/>
+      <c r="EW32" s="9"/>
+      <c r="EX32" s="9"/>
+      <c r="EY32" s="9"/>
+      <c r="EZ32" s="9"/>
+      <c r="FA32" s="9"/>
+      <c r="FB32" s="9"/>
+      <c r="FC32" s="9"/>
+      <c r="FD32" s="9"/>
+      <c r="FE32" s="9"/>
+      <c r="FF32" s="9"/>
+      <c r="FG32" s="9"/>
+      <c r="FH32" s="9"/>
+      <c r="FI32" s="9"/>
+      <c r="FJ32" s="9"/>
+      <c r="FK32" s="9"/>
+      <c r="FL32" s="9"/>
+      <c r="FM32" s="9"/>
+      <c r="FN32" s="9"/>
+      <c r="FO32" s="9"/>
+      <c r="FP32" s="9"/>
+      <c r="FQ32" s="9"/>
+      <c r="FR32" s="9"/>
+      <c r="FS32" s="9"/>
+      <c r="FT32" s="9"/>
+      <c r="FU32" s="9"/>
+      <c r="FV32" s="9"/>
+      <c r="FW32" s="9"/>
+      <c r="FX32" s="9"/>
+      <c r="FY32" s="9"/>
+      <c r="FZ32" s="9"/>
+      <c r="GA32" s="9"/>
+      <c r="GB32" s="9"/>
+      <c r="GC32" s="9"/>
+      <c r="GD32" s="9"/>
+      <c r="GE32" s="9"/>
     </row>
-    <row r="33" spans="1:187" ht="15" customHeight="1">
-      <c r="A33" s="23"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
-      <c r="V33" s="17"/>
+    <row r="33" spans="1:187" s="10" customFormat="1" ht="15" customHeight="1">
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="12"/>
+      <c r="R33" s="12"/>
+      <c r="S33" s="12"/>
+      <c r="T33" s="12"/>
+      <c r="U33" s="12"/>
+      <c r="V33" s="12"/>
       <c r="W33" s="14"/>
-      <c r="X33" s="18"/>
-      <c r="Y33" s="18"/>
-      <c r="Z33" s="18"/>
-      <c r="AA33" s="18"/>
-      <c r="AB33" s="18"/>
-      <c r="AC33" s="18"/>
-      <c r="AD33" s="18"/>
-      <c r="AE33" s="19"/>
-      <c r="AF33" s="20"/>
-      <c r="AG33" s="20"/>
-      <c r="AH33" s="20"/>
-      <c r="AI33" s="20"/>
-      <c r="AJ33" s="20"/>
-      <c r="AK33" s="20"/>
-      <c r="AL33" s="20"/>
-      <c r="AM33" s="20"/>
-      <c r="AN33" s="20"/>
-      <c r="AO33" s="20"/>
-      <c r="AP33" s="20"/>
-      <c r="AQ33" s="20"/>
-      <c r="AR33" s="20"/>
-      <c r="AS33" s="20"/>
-      <c r="AT33" s="20"/>
-      <c r="AU33" s="20"/>
-      <c r="AV33" s="20"/>
-      <c r="AW33" s="20"/>
-      <c r="AX33" s="20"/>
-      <c r="AY33" s="20"/>
-      <c r="AZ33" s="20"/>
-      <c r="BA33" s="20"/>
-      <c r="BB33" s="20"/>
-      <c r="BC33" s="20"/>
-      <c r="BD33" s="1"/>
-      <c r="BE33" s="1"/>
-      <c r="BF33" s="1"/>
-      <c r="BG33" s="1"/>
-      <c r="BH33" s="1"/>
-      <c r="BI33" s="1"/>
-      <c r="BJ33" s="1"/>
-      <c r="BK33" s="1"/>
-      <c r="BL33" s="1"/>
-      <c r="BM33" s="1"/>
-      <c r="BN33" s="1"/>
-      <c r="BO33" s="1"/>
-      <c r="BP33" s="1"/>
-      <c r="BQ33" s="1"/>
-      <c r="BR33" s="1"/>
-      <c r="BS33" s="1"/>
-      <c r="BT33" s="1"/>
-      <c r="BU33" s="1"/>
-      <c r="BV33" s="1"/>
-      <c r="BW33" s="1"/>
-      <c r="BX33" s="1"/>
-      <c r="BY33" s="1"/>
-      <c r="BZ33" s="1"/>
-      <c r="CA33" s="1"/>
-      <c r="CB33" s="1"/>
-      <c r="CC33" s="1"/>
-      <c r="CD33" s="1"/>
-      <c r="CE33" s="1"/>
-      <c r="CF33" s="1"/>
-      <c r="CG33" s="1"/>
-      <c r="CH33" s="1"/>
-      <c r="CI33" s="1"/>
-      <c r="CJ33" s="1"/>
-      <c r="CK33" s="1"/>
-      <c r="CL33" s="1"/>
-      <c r="CM33" s="1"/>
-      <c r="CN33" s="1"/>
-      <c r="CO33" s="1"/>
-      <c r="CP33" s="1"/>
-      <c r="CQ33" s="1"/>
-      <c r="CR33" s="1"/>
-      <c r="CS33" s="1"/>
-      <c r="CT33" s="1"/>
-      <c r="CU33" s="1"/>
-      <c r="CV33" s="1"/>
-      <c r="CW33" s="1"/>
-      <c r="CX33" s="1"/>
-      <c r="CY33" s="1"/>
-      <c r="CZ33" s="1"/>
-      <c r="DA33" s="1"/>
-      <c r="DB33" s="1"/>
-      <c r="DC33" s="1"/>
-      <c r="DD33" s="1"/>
-      <c r="DE33" s="1"/>
-      <c r="DF33" s="1"/>
-      <c r="DG33" s="1"/>
-      <c r="DH33" s="1"/>
-      <c r="DI33" s="1"/>
-      <c r="DJ33" s="1"/>
-      <c r="DK33" s="1"/>
-      <c r="DL33" s="1"/>
-      <c r="DM33" s="1"/>
-      <c r="DN33" s="1"/>
-      <c r="DO33" s="1"/>
-      <c r="DP33" s="1"/>
-      <c r="DQ33" s="1"/>
-      <c r="DR33" s="1"/>
-      <c r="DS33" s="1"/>
-      <c r="DT33" s="1"/>
-      <c r="DU33" s="1"/>
-      <c r="DV33" s="1"/>
-      <c r="DW33" s="1"/>
-      <c r="DX33" s="1"/>
-      <c r="DY33" s="1"/>
-      <c r="DZ33" s="1"/>
-      <c r="EA33" s="1"/>
-      <c r="EB33" s="1"/>
-      <c r="EC33" s="1"/>
-      <c r="ED33" s="1"/>
-      <c r="EE33" s="1"/>
-      <c r="EF33" s="1"/>
-      <c r="EG33" s="1"/>
-      <c r="EH33" s="1"/>
-      <c r="EI33" s="1"/>
-      <c r="EJ33" s="1"/>
-      <c r="EK33" s="1"/>
-      <c r="EL33" s="1"/>
-      <c r="EM33" s="1"/>
-      <c r="EN33" s="1"/>
-      <c r="EO33" s="1"/>
-      <c r="EP33" s="1"/>
-      <c r="EQ33" s="1"/>
-      <c r="ER33" s="1"/>
-      <c r="ES33" s="1"/>
-      <c r="ET33" s="1"/>
-      <c r="EU33" s="1"/>
-      <c r="EV33" s="1"/>
-      <c r="EW33" s="1"/>
-      <c r="EX33" s="1"/>
-      <c r="EY33" s="1"/>
-      <c r="EZ33" s="1"/>
-      <c r="FA33" s="1"/>
-      <c r="FB33" s="1"/>
-      <c r="FC33" s="1"/>
-      <c r="FD33" s="1"/>
-      <c r="FE33" s="1"/>
-      <c r="FF33" s="1"/>
-      <c r="FG33" s="1"/>
-      <c r="FH33" s="1"/>
-      <c r="FI33" s="1"/>
-      <c r="FJ33" s="1"/>
-      <c r="FK33" s="1"/>
-      <c r="FL33" s="1"/>
-      <c r="FM33" s="1"/>
-      <c r="FN33" s="1"/>
-      <c r="FO33" s="1"/>
-      <c r="FP33" s="1"/>
-      <c r="FQ33" s="1"/>
-      <c r="FR33" s="1"/>
-      <c r="FS33" s="1"/>
-      <c r="FT33" s="1"/>
-      <c r="FU33" s="1"/>
-      <c r="FV33" s="1"/>
-      <c r="FW33" s="1"/>
-      <c r="FX33" s="1"/>
-      <c r="FY33" s="1"/>
-      <c r="FZ33" s="1"/>
-      <c r="GA33" s="1"/>
-      <c r="GB33" s="1"/>
-      <c r="GC33" s="1"/>
-      <c r="GD33" s="1"/>
-      <c r="GE33" s="1"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="15"/>
+      <c r="AF33" s="15"/>
+      <c r="AG33" s="15"/>
+      <c r="AH33" s="15"/>
+      <c r="AI33" s="15"/>
+      <c r="AJ33" s="15"/>
+      <c r="AK33" s="15"/>
+      <c r="AL33" s="15"/>
+      <c r="AM33" s="15"/>
+      <c r="AN33" s="15"/>
+      <c r="AO33" s="15"/>
+      <c r="AP33" s="15"/>
+      <c r="AQ33" s="15"/>
+      <c r="AR33" s="15"/>
+      <c r="AS33" s="15"/>
+      <c r="AT33" s="15"/>
+      <c r="AU33" s="15"/>
+      <c r="AV33" s="15"/>
+      <c r="AW33" s="15"/>
+      <c r="AX33" s="15"/>
+      <c r="AY33" s="15"/>
+      <c r="AZ33" s="15"/>
+      <c r="BA33" s="15"/>
+      <c r="BB33" s="15"/>
+      <c r="BC33" s="15"/>
+      <c r="BD33" s="9"/>
+      <c r="BE33" s="9"/>
+      <c r="BF33" s="9"/>
+      <c r="BG33" s="9"/>
+      <c r="BH33" s="9"/>
+      <c r="BI33" s="9"/>
+      <c r="BJ33" s="9"/>
+      <c r="BK33" s="9"/>
+      <c r="BL33" s="9"/>
+      <c r="BM33" s="9"/>
+      <c r="BN33" s="9"/>
+      <c r="BO33" s="9"/>
+      <c r="BP33" s="9"/>
+      <c r="BQ33" s="9"/>
+      <c r="BR33" s="9"/>
+      <c r="BS33" s="9"/>
+      <c r="BT33" s="9"/>
+      <c r="BU33" s="9"/>
+      <c r="BV33" s="9"/>
+      <c r="BW33" s="9"/>
+      <c r="BX33" s="9"/>
+      <c r="BY33" s="9"/>
+      <c r="BZ33" s="9"/>
+      <c r="CA33" s="9"/>
+      <c r="CB33" s="9"/>
+      <c r="CC33" s="9"/>
+      <c r="CD33" s="9"/>
+      <c r="CE33" s="9"/>
+      <c r="CF33" s="9"/>
+      <c r="CG33" s="9"/>
+      <c r="CH33" s="9"/>
+      <c r="CI33" s="9"/>
+      <c r="CJ33" s="9"/>
+      <c r="CK33" s="9"/>
+      <c r="CL33" s="9"/>
+      <c r="CM33" s="9"/>
+      <c r="CN33" s="9"/>
+      <c r="CO33" s="9"/>
+      <c r="CP33" s="9"/>
+      <c r="CQ33" s="9"/>
+      <c r="CR33" s="9"/>
+      <c r="CS33" s="9"/>
+      <c r="CT33" s="9"/>
+      <c r="CU33" s="9"/>
+      <c r="CV33" s="9"/>
+      <c r="CW33" s="9"/>
+      <c r="CX33" s="9"/>
+      <c r="CY33" s="9"/>
+      <c r="CZ33" s="9"/>
+      <c r="DA33" s="9"/>
+      <c r="DB33" s="9"/>
+      <c r="DC33" s="9"/>
+      <c r="DD33" s="9"/>
+      <c r="DE33" s="9"/>
+      <c r="DF33" s="9"/>
+      <c r="DG33" s="9"/>
+      <c r="DH33" s="9"/>
+      <c r="DI33" s="9"/>
+      <c r="DJ33" s="9"/>
+      <c r="DK33" s="9"/>
+      <c r="DL33" s="9"/>
+      <c r="DM33" s="9"/>
+      <c r="DN33" s="9"/>
+      <c r="DO33" s="9"/>
+      <c r="DP33" s="9"/>
+      <c r="DQ33" s="9"/>
+      <c r="DR33" s="9"/>
+      <c r="DS33" s="9"/>
+      <c r="DT33" s="9"/>
+      <c r="DU33" s="9"/>
+      <c r="DV33" s="9"/>
+      <c r="DW33" s="9"/>
+      <c r="DX33" s="9"/>
+      <c r="DY33" s="9"/>
+      <c r="DZ33" s="9"/>
+      <c r="EA33" s="9"/>
+      <c r="EB33" s="9"/>
+      <c r="EC33" s="9"/>
+      <c r="ED33" s="9"/>
+      <c r="EE33" s="9"/>
+      <c r="EF33" s="9"/>
+      <c r="EG33" s="9"/>
+      <c r="EH33" s="9"/>
+      <c r="EI33" s="9"/>
+      <c r="EJ33" s="9"/>
+      <c r="EK33" s="9"/>
+      <c r="EL33" s="9"/>
+      <c r="EM33" s="9"/>
+      <c r="EN33" s="9"/>
+      <c r="EO33" s="9"/>
+      <c r="EP33" s="9"/>
+      <c r="EQ33" s="9"/>
+      <c r="ER33" s="9"/>
+      <c r="ES33" s="9"/>
+      <c r="ET33" s="9"/>
+      <c r="EU33" s="9"/>
+      <c r="EV33" s="9"/>
+      <c r="EW33" s="9"/>
+      <c r="EX33" s="9"/>
+      <c r="EY33" s="9"/>
+      <c r="EZ33" s="9"/>
+      <c r="FA33" s="9"/>
+      <c r="FB33" s="9"/>
+      <c r="FC33" s="9"/>
+      <c r="FD33" s="9"/>
+      <c r="FE33" s="9"/>
+      <c r="FF33" s="9"/>
+      <c r="FG33" s="9"/>
+      <c r="FH33" s="9"/>
+      <c r="FI33" s="9"/>
+      <c r="FJ33" s="9"/>
+      <c r="FK33" s="9"/>
+      <c r="FL33" s="9"/>
+      <c r="FM33" s="9"/>
+      <c r="FN33" s="9"/>
+      <c r="FO33" s="9"/>
+      <c r="FP33" s="9"/>
+      <c r="FQ33" s="9"/>
+      <c r="FR33" s="9"/>
+      <c r="FS33" s="9"/>
+      <c r="FT33" s="9"/>
+      <c r="FU33" s="9"/>
+      <c r="FV33" s="9"/>
+      <c r="FW33" s="9"/>
+      <c r="FX33" s="9"/>
+      <c r="FY33" s="9"/>
+      <c r="FZ33" s="9"/>
+      <c r="GA33" s="9"/>
+      <c r="GB33" s="9"/>
+      <c r="GC33" s="9"/>
+      <c r="GD33" s="9"/>
+      <c r="GE33" s="9"/>
     </row>
     <row r="34" spans="1:187" ht="15" customHeight="1">
-      <c r="A34" s="25"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="29"/>
-      <c r="X34" s="29"/>
-      <c r="Y34" s="29"/>
-      <c r="Z34" s="29"/>
-      <c r="AA34" s="29"/>
-      <c r="AB34" s="29"/>
-      <c r="AC34" s="29"/>
-      <c r="AD34" s="29"/>
-      <c r="AE34" s="30"/>
-      <c r="AF34" s="30"/>
-      <c r="AG34" s="30"/>
-      <c r="AH34" s="30"/>
-      <c r="AI34" s="30"/>
-      <c r="AJ34" s="30"/>
-      <c r="AK34" s="30"/>
-      <c r="AL34" s="30"/>
-      <c r="AM34" s="30"/>
-      <c r="AN34" s="30"/>
-      <c r="AO34" s="30"/>
-      <c r="AP34" s="30"/>
-      <c r="AQ34" s="30"/>
-      <c r="AR34" s="30"/>
-      <c r="AS34" s="30"/>
-      <c r="AT34" s="30"/>
-      <c r="AU34" s="30"/>
-      <c r="AV34" s="30"/>
-      <c r="AW34" s="30"/>
-      <c r="AX34" s="30"/>
-      <c r="AY34" s="30"/>
-      <c r="AZ34" s="30"/>
-      <c r="BA34" s="30"/>
-      <c r="BB34" s="30"/>
-      <c r="BC34" s="30"/>
-      <c r="BD34" s="8"/>
-      <c r="BE34" s="8"/>
-      <c r="BF34" s="8"/>
-      <c r="BG34" s="8"/>
-      <c r="BH34" s="8"/>
-      <c r="BI34" s="8"/>
-      <c r="BJ34" s="8"/>
-      <c r="BK34" s="8"/>
-      <c r="BL34" s="8"/>
-      <c r="BM34" s="8"/>
-      <c r="BN34" s="8"/>
-      <c r="BO34" s="8"/>
-      <c r="BP34" s="8"/>
-      <c r="BQ34" s="8"/>
-      <c r="BR34" s="8"/>
-      <c r="BS34" s="8"/>
-      <c r="BT34" s="8"/>
-      <c r="BU34" s="8"/>
-      <c r="BV34" s="8"/>
-      <c r="BW34" s="8"/>
-      <c r="BX34" s="8"/>
-      <c r="BY34" s="8"/>
-      <c r="BZ34" s="8"/>
-      <c r="CA34" s="8"/>
-      <c r="CB34" s="8"/>
-      <c r="CC34" s="8"/>
-      <c r="CD34" s="8"/>
-      <c r="CE34" s="8"/>
-      <c r="CF34" s="8"/>
-      <c r="CG34" s="8"/>
-      <c r="CH34" s="8"/>
-      <c r="CI34" s="8"/>
-      <c r="CJ34" s="8"/>
-      <c r="CK34" s="8"/>
-      <c r="CL34" s="8"/>
-      <c r="CM34" s="8"/>
-      <c r="CN34" s="8"/>
-      <c r="CO34" s="8"/>
-      <c r="CP34" s="8"/>
-      <c r="CQ34" s="8"/>
-      <c r="CR34" s="8"/>
-      <c r="CS34" s="8"/>
-      <c r="CT34" s="8"/>
-      <c r="CU34" s="8"/>
-      <c r="CV34" s="8"/>
-      <c r="CW34" s="8"/>
-      <c r="CX34" s="8"/>
-      <c r="CY34" s="8"/>
-      <c r="CZ34" s="8"/>
-      <c r="DA34" s="8"/>
-      <c r="DB34" s="8"/>
-      <c r="DC34" s="8"/>
-      <c r="DD34" s="8"/>
-      <c r="DE34" s="8"/>
-      <c r="DF34" s="8"/>
-      <c r="DG34" s="8"/>
-      <c r="DH34" s="8"/>
-      <c r="DI34" s="8"/>
-      <c r="DJ34" s="8"/>
-      <c r="DK34" s="8"/>
-      <c r="DL34" s="8"/>
-      <c r="DM34" s="8"/>
-      <c r="DN34" s="8"/>
-      <c r="DO34" s="8"/>
-      <c r="DP34" s="8"/>
-      <c r="DQ34" s="8"/>
-      <c r="DR34" s="8"/>
-      <c r="DS34" s="8"/>
-      <c r="DT34" s="8"/>
-      <c r="DU34" s="8"/>
-      <c r="DV34" s="8"/>
-      <c r="DW34" s="8"/>
-      <c r="DX34" s="8"/>
-      <c r="DY34" s="8"/>
-      <c r="DZ34" s="8"/>
-      <c r="EA34" s="8"/>
-      <c r="EB34" s="8"/>
-      <c r="EC34" s="8"/>
-      <c r="ED34" s="8"/>
-      <c r="EE34" s="8"/>
-      <c r="EF34" s="8"/>
-      <c r="EG34" s="8"/>
-      <c r="EH34" s="8"/>
-      <c r="EI34" s="8"/>
-      <c r="EJ34" s="8"/>
-      <c r="EK34" s="8"/>
-      <c r="EL34" s="8"/>
-      <c r="EM34" s="8"/>
-      <c r="EN34" s="8"/>
-      <c r="EO34" s="8"/>
-      <c r="EP34" s="8"/>
-      <c r="EQ34" s="8"/>
-      <c r="ER34" s="8"/>
-      <c r="ES34" s="8"/>
-      <c r="ET34" s="8"/>
-      <c r="EU34" s="8"/>
-      <c r="EV34" s="8"/>
-      <c r="EW34" s="8"/>
-      <c r="EX34" s="8"/>
-      <c r="EY34" s="8"/>
-      <c r="EZ34" s="8"/>
-      <c r="FA34" s="8"/>
-      <c r="FB34" s="8"/>
-      <c r="FC34" s="8"/>
-      <c r="FD34" s="8"/>
-      <c r="FE34" s="8"/>
-      <c r="FF34" s="8"/>
-      <c r="FG34" s="8"/>
-      <c r="FH34" s="8"/>
-      <c r="FI34" s="8"/>
-      <c r="FJ34" s="8"/>
-      <c r="FK34" s="8"/>
-      <c r="FL34" s="8"/>
-      <c r="FM34" s="8"/>
-      <c r="FN34" s="8"/>
-      <c r="FO34" s="8"/>
-      <c r="FP34" s="8"/>
-      <c r="FQ34" s="8"/>
-      <c r="FR34" s="8"/>
-      <c r="FS34" s="8"/>
-      <c r="FT34" s="8"/>
-      <c r="FU34" s="8"/>
-      <c r="FV34" s="8"/>
-      <c r="FW34" s="8"/>
-      <c r="FX34" s="8"/>
-      <c r="FY34" s="8"/>
-      <c r="FZ34" s="8"/>
-      <c r="GA34" s="8"/>
-      <c r="GB34" s="8"/>
-      <c r="GC34" s="8"/>
-      <c r="GD34" s="8"/>
-      <c r="GE34" s="8"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="14"/>
+      <c r="X34" s="18"/>
+      <c r="Y34" s="18"/>
+      <c r="Z34" s="18"/>
+      <c r="AA34" s="18"/>
+      <c r="AB34" s="18"/>
+      <c r="AC34" s="18"/>
+      <c r="AD34" s="18"/>
+      <c r="AE34" s="19"/>
+      <c r="AF34" s="20"/>
+      <c r="AG34" s="20"/>
+      <c r="AH34" s="20"/>
+      <c r="AI34" s="20"/>
+      <c r="AJ34" s="20"/>
+      <c r="AK34" s="20"/>
+      <c r="AL34" s="20"/>
+      <c r="AM34" s="20"/>
+      <c r="AN34" s="20"/>
+      <c r="AO34" s="20"/>
+      <c r="AP34" s="20"/>
+      <c r="AQ34" s="20"/>
+      <c r="AR34" s="20"/>
+      <c r="AS34" s="20"/>
+      <c r="AT34" s="20"/>
+      <c r="AU34" s="20"/>
+      <c r="AV34" s="20"/>
+      <c r="AW34" s="20"/>
+      <c r="AX34" s="20"/>
+      <c r="AY34" s="20"/>
+      <c r="AZ34" s="20"/>
+      <c r="BA34" s="20"/>
+      <c r="BB34" s="20"/>
+      <c r="BC34" s="20"/>
+      <c r="BD34" s="1"/>
+      <c r="BE34" s="1"/>
+      <c r="BF34" s="1"/>
+      <c r="BG34" s="1"/>
+      <c r="BH34" s="1"/>
+      <c r="BI34" s="1"/>
+      <c r="BJ34" s="1"/>
+      <c r="BK34" s="1"/>
+      <c r="BL34" s="1"/>
+      <c r="BM34" s="1"/>
+      <c r="BN34" s="1"/>
+      <c r="BO34" s="1"/>
+      <c r="BP34" s="1"/>
+      <c r="BQ34" s="1"/>
+      <c r="BR34" s="1"/>
+      <c r="BS34" s="1"/>
+      <c r="BT34" s="1"/>
+      <c r="BU34" s="1"/>
+      <c r="BV34" s="1"/>
+      <c r="BW34" s="1"/>
+      <c r="BX34" s="1"/>
+      <c r="BY34" s="1"/>
+      <c r="BZ34" s="1"/>
+      <c r="CA34" s="1"/>
+      <c r="CB34" s="1"/>
+      <c r="CC34" s="1"/>
+      <c r="CD34" s="1"/>
+      <c r="CE34" s="1"/>
+      <c r="CF34" s="1"/>
+      <c r="CG34" s="1"/>
+      <c r="CH34" s="1"/>
+      <c r="CI34" s="1"/>
+      <c r="CJ34" s="1"/>
+      <c r="CK34" s="1"/>
+      <c r="CL34" s="1"/>
+      <c r="CM34" s="1"/>
+      <c r="CN34" s="1"/>
+      <c r="CO34" s="1"/>
+      <c r="CP34" s="1"/>
+      <c r="CQ34" s="1"/>
+      <c r="CR34" s="1"/>
+      <c r="CS34" s="1"/>
+      <c r="CT34" s="1"/>
+      <c r="CU34" s="1"/>
+      <c r="CV34" s="1"/>
+      <c r="CW34" s="1"/>
+      <c r="CX34" s="1"/>
+      <c r="CY34" s="1"/>
+      <c r="CZ34" s="1"/>
+      <c r="DA34" s="1"/>
+      <c r="DB34" s="1"/>
+      <c r="DC34" s="1"/>
+      <c r="DD34" s="1"/>
+      <c r="DE34" s="1"/>
+      <c r="DF34" s="1"/>
+      <c r="DG34" s="1"/>
+      <c r="DH34" s="1"/>
+      <c r="DI34" s="1"/>
+      <c r="DJ34" s="1"/>
+      <c r="DK34" s="1"/>
+      <c r="DL34" s="1"/>
+      <c r="DM34" s="1"/>
+      <c r="DN34" s="1"/>
+      <c r="DO34" s="1"/>
+      <c r="DP34" s="1"/>
+      <c r="DQ34" s="1"/>
+      <c r="DR34" s="1"/>
+      <c r="DS34" s="1"/>
+      <c r="DT34" s="1"/>
+      <c r="DU34" s="1"/>
+      <c r="DV34" s="1"/>
+      <c r="DW34" s="1"/>
+      <c r="DX34" s="1"/>
+      <c r="DY34" s="1"/>
+      <c r="DZ34" s="1"/>
+      <c r="EA34" s="1"/>
+      <c r="EB34" s="1"/>
+      <c r="EC34" s="1"/>
+      <c r="ED34" s="1"/>
+      <c r="EE34" s="1"/>
+      <c r="EF34" s="1"/>
+      <c r="EG34" s="1"/>
+      <c r="EH34" s="1"/>
+      <c r="EI34" s="1"/>
+      <c r="EJ34" s="1"/>
+      <c r="EK34" s="1"/>
+      <c r="EL34" s="1"/>
+      <c r="EM34" s="1"/>
+      <c r="EN34" s="1"/>
+      <c r="EO34" s="1"/>
+      <c r="EP34" s="1"/>
+      <c r="EQ34" s="1"/>
+      <c r="ER34" s="1"/>
+      <c r="ES34" s="1"/>
+      <c r="ET34" s="1"/>
+      <c r="EU34" s="1"/>
+      <c r="EV34" s="1"/>
+      <c r="EW34" s="1"/>
+      <c r="EX34" s="1"/>
+      <c r="EY34" s="1"/>
+      <c r="EZ34" s="1"/>
+      <c r="FA34" s="1"/>
+      <c r="FB34" s="1"/>
+      <c r="FC34" s="1"/>
+      <c r="FD34" s="1"/>
+      <c r="FE34" s="1"/>
+      <c r="FF34" s="1"/>
+      <c r="FG34" s="1"/>
+      <c r="FH34" s="1"/>
+      <c r="FI34" s="1"/>
+      <c r="FJ34" s="1"/>
+      <c r="FK34" s="1"/>
+      <c r="FL34" s="1"/>
+      <c r="FM34" s="1"/>
+      <c r="FN34" s="1"/>
+      <c r="FO34" s="1"/>
+      <c r="FP34" s="1"/>
+      <c r="FQ34" s="1"/>
+      <c r="FR34" s="1"/>
+      <c r="FS34" s="1"/>
+      <c r="FT34" s="1"/>
+      <c r="FU34" s="1"/>
+      <c r="FV34" s="1"/>
+      <c r="FW34" s="1"/>
+      <c r="FX34" s="1"/>
+      <c r="FY34" s="1"/>
+      <c r="FZ34" s="1"/>
+      <c r="GA34" s="1"/>
+      <c r="GB34" s="1"/>
+      <c r="GC34" s="1"/>
+      <c r="GD34" s="1"/>
+      <c r="GE34" s="1"/>
     </row>
     <row r="35" spans="1:187" ht="15" customHeight="1">
-      <c r="A35" s="31"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="32"/>
-      <c r="X35" s="32"/>
-      <c r="Y35" s="32"/>
-      <c r="Z35" s="32"/>
-      <c r="AA35" s="32"/>
-      <c r="AB35" s="32"/>
-      <c r="AC35" s="32"/>
-      <c r="AD35" s="32"/>
-      <c r="AE35" s="24"/>
-      <c r="AF35" s="24"/>
-      <c r="AG35" s="24"/>
-      <c r="AH35" s="24"/>
-      <c r="AI35" s="24"/>
-      <c r="AJ35" s="24"/>
-      <c r="AK35" s="24"/>
-      <c r="AL35" s="24"/>
-      <c r="AM35" s="24"/>
-      <c r="AN35" s="24"/>
-      <c r="AO35" s="24"/>
-      <c r="AP35" s="24"/>
-      <c r="AQ35" s="24"/>
-      <c r="AR35" s="24"/>
-      <c r="AS35" s="24"/>
-      <c r="AT35" s="24"/>
-      <c r="AU35" s="24"/>
-      <c r="AV35" s="24"/>
-      <c r="AW35" s="24"/>
-      <c r="AX35" s="24"/>
-      <c r="AY35" s="24"/>
-      <c r="AZ35" s="24"/>
-      <c r="BA35" s="24"/>
-      <c r="BB35" s="24"/>
-      <c r="BC35" s="24"/>
-      <c r="BD35" s="8"/>
-      <c r="BE35" s="8"/>
-      <c r="BF35" s="8"/>
-      <c r="BG35" s="8"/>
-      <c r="BH35" s="8"/>
-      <c r="BI35" s="8"/>
-      <c r="BJ35" s="8"/>
-      <c r="BK35" s="8"/>
-      <c r="BL35" s="8"/>
-      <c r="BM35" s="8"/>
-      <c r="BN35" s="8"/>
-      <c r="BO35" s="8"/>
-      <c r="BP35" s="8"/>
-      <c r="BQ35" s="8"/>
-      <c r="BR35" s="8"/>
-      <c r="BS35" s="8"/>
-      <c r="BT35" s="8"/>
-      <c r="BU35" s="8"/>
-      <c r="BV35" s="8"/>
-      <c r="BW35" s="8"/>
-      <c r="BX35" s="8"/>
-      <c r="BY35" s="8"/>
-      <c r="BZ35" s="8"/>
-      <c r="CA35" s="8"/>
-      <c r="CB35" s="8"/>
-      <c r="CC35" s="8"/>
-      <c r="CD35" s="8"/>
-      <c r="CE35" s="8"/>
-      <c r="CF35" s="8"/>
-      <c r="CG35" s="8"/>
-      <c r="CH35" s="8"/>
-      <c r="CI35" s="8"/>
-      <c r="CJ35" s="8"/>
-      <c r="CK35" s="8"/>
-      <c r="CL35" s="8"/>
-      <c r="CM35" s="8"/>
-      <c r="CN35" s="8"/>
-      <c r="CO35" s="8"/>
-      <c r="CP35" s="8"/>
-      <c r="CQ35" s="8"/>
-      <c r="CR35" s="8"/>
-      <c r="CS35" s="8"/>
-      <c r="CT35" s="8"/>
-      <c r="CU35" s="8"/>
-      <c r="CV35" s="8"/>
-      <c r="CW35" s="8"/>
-      <c r="CX35" s="8"/>
-      <c r="CY35" s="8"/>
-      <c r="CZ35" s="8"/>
-      <c r="DA35" s="8"/>
-      <c r="DB35" s="8"/>
-      <c r="DC35" s="8"/>
-      <c r="DD35" s="8"/>
-      <c r="DE35" s="8"/>
-      <c r="DF35" s="8"/>
-      <c r="DG35" s="8"/>
-      <c r="DH35" s="8"/>
-      <c r="DI35" s="8"/>
-      <c r="DJ35" s="8"/>
-      <c r="DK35" s="8"/>
-      <c r="DL35" s="8"/>
-      <c r="DM35" s="8"/>
-      <c r="DN35" s="8"/>
-      <c r="DO35" s="8"/>
-      <c r="DP35" s="8"/>
-      <c r="DQ35" s="8"/>
-      <c r="DR35" s="8"/>
-      <c r="DS35" s="8"/>
-      <c r="DT35" s="8"/>
-      <c r="DU35" s="8"/>
-      <c r="DV35" s="8"/>
-      <c r="DW35" s="8"/>
-      <c r="DX35" s="8"/>
-      <c r="DY35" s="8"/>
-      <c r="DZ35" s="8"/>
-      <c r="EA35" s="8"/>
-      <c r="EB35" s="8"/>
-      <c r="EC35" s="8"/>
-      <c r="ED35" s="8"/>
-      <c r="EE35" s="8"/>
-      <c r="EF35" s="8"/>
-      <c r="EG35" s="8"/>
-      <c r="EH35" s="8"/>
-      <c r="EI35" s="8"/>
-      <c r="EJ35" s="8"/>
-      <c r="EK35" s="8"/>
-      <c r="EL35" s="8"/>
-      <c r="EM35" s="8"/>
-      <c r="EN35" s="8"/>
-      <c r="EO35" s="8"/>
-      <c r="EP35" s="8"/>
-      <c r="EQ35" s="8"/>
-      <c r="ER35" s="8"/>
-      <c r="ES35" s="8"/>
-      <c r="ET35" s="8"/>
-      <c r="EU35" s="8"/>
-      <c r="EV35" s="8"/>
-      <c r="EW35" s="8"/>
-      <c r="EX35" s="8"/>
-      <c r="EY35" s="8"/>
-      <c r="EZ35" s="8"/>
-      <c r="FA35" s="8"/>
-      <c r="FB35" s="8"/>
-      <c r="FC35" s="8"/>
-      <c r="FD35" s="8"/>
-      <c r="FE35" s="8"/>
-      <c r="FF35" s="8"/>
-      <c r="FG35" s="8"/>
-      <c r="FH35" s="8"/>
-      <c r="FI35" s="8"/>
-      <c r="FJ35" s="8"/>
-      <c r="FK35" s="8"/>
-      <c r="FL35" s="8"/>
-      <c r="FM35" s="8"/>
-      <c r="FN35" s="8"/>
-      <c r="FO35" s="8"/>
-      <c r="FP35" s="8"/>
-      <c r="FQ35" s="8"/>
-      <c r="FR35" s="8"/>
-      <c r="FS35" s="8"/>
-      <c r="FT35" s="8"/>
-      <c r="FU35" s="8"/>
-      <c r="FV35" s="8"/>
-      <c r="FW35" s="8"/>
-      <c r="FX35" s="8"/>
-      <c r="FY35" s="8"/>
-      <c r="FZ35" s="8"/>
-      <c r="GA35" s="8"/>
-      <c r="GB35" s="8"/>
-      <c r="GC35" s="8"/>
-      <c r="GD35" s="8"/>
-      <c r="GE35" s="8"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="18"/>
+      <c r="X35" s="18"/>
+      <c r="Y35" s="18"/>
+      <c r="Z35" s="18"/>
+      <c r="AA35" s="18"/>
+      <c r="AB35" s="18"/>
+      <c r="AC35" s="18"/>
+      <c r="AD35" s="18"/>
+      <c r="AE35" s="19"/>
+      <c r="AF35" s="20"/>
+      <c r="AG35" s="20"/>
+      <c r="AH35" s="20"/>
+      <c r="AI35" s="20"/>
+      <c r="AJ35" s="20"/>
+      <c r="AK35" s="20"/>
+      <c r="AL35" s="20"/>
+      <c r="AM35" s="20"/>
+      <c r="AN35" s="20"/>
+      <c r="AO35" s="20"/>
+      <c r="AP35" s="20"/>
+      <c r="AQ35" s="20"/>
+      <c r="AR35" s="20"/>
+      <c r="AS35" s="20"/>
+      <c r="AT35" s="20"/>
+      <c r="AU35" s="20"/>
+      <c r="AV35" s="20"/>
+      <c r="AW35" s="20"/>
+      <c r="AX35" s="20"/>
+      <c r="AY35" s="20"/>
+      <c r="AZ35" s="20"/>
+      <c r="BA35" s="20"/>
+      <c r="BB35" s="20"/>
+      <c r="BC35" s="20"/>
+      <c r="BD35" s="1"/>
+      <c r="BE35" s="1"/>
+      <c r="BF35" s="1"/>
+      <c r="BG35" s="1"/>
+      <c r="BH35" s="1"/>
+      <c r="BI35" s="1"/>
+      <c r="BJ35" s="1"/>
+      <c r="BK35" s="1"/>
+      <c r="BL35" s="1"/>
+      <c r="BM35" s="1"/>
+      <c r="BN35" s="1"/>
+      <c r="BO35" s="1"/>
+      <c r="BP35" s="1"/>
+      <c r="BQ35" s="1"/>
+      <c r="BR35" s="1"/>
+      <c r="BS35" s="1"/>
+      <c r="BT35" s="1"/>
+      <c r="BU35" s="1"/>
+      <c r="BV35" s="1"/>
+      <c r="BW35" s="1"/>
+      <c r="BX35" s="1"/>
+      <c r="BY35" s="1"/>
+      <c r="BZ35" s="1"/>
+      <c r="CA35" s="1"/>
+      <c r="CB35" s="1"/>
+      <c r="CC35" s="1"/>
+      <c r="CD35" s="1"/>
+      <c r="CE35" s="1"/>
+      <c r="CF35" s="1"/>
+      <c r="CG35" s="1"/>
+      <c r="CH35" s="1"/>
+      <c r="CI35" s="1"/>
+      <c r="CJ35" s="1"/>
+      <c r="CK35" s="1"/>
+      <c r="CL35" s="1"/>
+      <c r="CM35" s="1"/>
+      <c r="CN35" s="1"/>
+      <c r="CO35" s="1"/>
+      <c r="CP35" s="1"/>
+      <c r="CQ35" s="1"/>
+      <c r="CR35" s="1"/>
+      <c r="CS35" s="1"/>
+      <c r="CT35" s="1"/>
+      <c r="CU35" s="1"/>
+      <c r="CV35" s="1"/>
+      <c r="CW35" s="1"/>
+      <c r="CX35" s="1"/>
+      <c r="CY35" s="1"/>
+      <c r="CZ35" s="1"/>
+      <c r="DA35" s="1"/>
+      <c r="DB35" s="1"/>
+      <c r="DC35" s="1"/>
+      <c r="DD35" s="1"/>
+      <c r="DE35" s="1"/>
+      <c r="DF35" s="1"/>
+      <c r="DG35" s="1"/>
+      <c r="DH35" s="1"/>
+      <c r="DI35" s="1"/>
+      <c r="DJ35" s="1"/>
+      <c r="DK35" s="1"/>
+      <c r="DL35" s="1"/>
+      <c r="DM35" s="1"/>
+      <c r="DN35" s="1"/>
+      <c r="DO35" s="1"/>
+      <c r="DP35" s="1"/>
+      <c r="DQ35" s="1"/>
+      <c r="DR35" s="1"/>
+      <c r="DS35" s="1"/>
+      <c r="DT35" s="1"/>
+      <c r="DU35" s="1"/>
+      <c r="DV35" s="1"/>
+      <c r="DW35" s="1"/>
+      <c r="DX35" s="1"/>
+      <c r="DY35" s="1"/>
+      <c r="DZ35" s="1"/>
+      <c r="EA35" s="1"/>
+      <c r="EB35" s="1"/>
+      <c r="EC35" s="1"/>
+      <c r="ED35" s="1"/>
+      <c r="EE35" s="1"/>
+      <c r="EF35" s="1"/>
+      <c r="EG35" s="1"/>
+      <c r="EH35" s="1"/>
+      <c r="EI35" s="1"/>
+      <c r="EJ35" s="1"/>
+      <c r="EK35" s="1"/>
+      <c r="EL35" s="1"/>
+      <c r="EM35" s="1"/>
+      <c r="EN35" s="1"/>
+      <c r="EO35" s="1"/>
+      <c r="EP35" s="1"/>
+      <c r="EQ35" s="1"/>
+      <c r="ER35" s="1"/>
+      <c r="ES35" s="1"/>
+      <c r="ET35" s="1"/>
+      <c r="EU35" s="1"/>
+      <c r="EV35" s="1"/>
+      <c r="EW35" s="1"/>
+      <c r="EX35" s="1"/>
+      <c r="EY35" s="1"/>
+      <c r="EZ35" s="1"/>
+      <c r="FA35" s="1"/>
+      <c r="FB35" s="1"/>
+      <c r="FC35" s="1"/>
+      <c r="FD35" s="1"/>
+      <c r="FE35" s="1"/>
+      <c r="FF35" s="1"/>
+      <c r="FG35" s="1"/>
+      <c r="FH35" s="1"/>
+      <c r="FI35" s="1"/>
+      <c r="FJ35" s="1"/>
+      <c r="FK35" s="1"/>
+      <c r="FL35" s="1"/>
+      <c r="FM35" s="1"/>
+      <c r="FN35" s="1"/>
+      <c r="FO35" s="1"/>
+      <c r="FP35" s="1"/>
+      <c r="FQ35" s="1"/>
+      <c r="FR35" s="1"/>
+      <c r="FS35" s="1"/>
+      <c r="FT35" s="1"/>
+      <c r="FU35" s="1"/>
+      <c r="FV35" s="1"/>
+      <c r="FW35" s="1"/>
+      <c r="FX35" s="1"/>
+      <c r="FY35" s="1"/>
+      <c r="FZ35" s="1"/>
+      <c r="GA35" s="1"/>
+      <c r="GB35" s="1"/>
+      <c r="GC35" s="1"/>
+      <c r="GD35" s="1"/>
+      <c r="GE35" s="1"/>
     </row>
     <row r="36" spans="1:187" ht="15" customHeight="1">
       <c r="A36" s="23"/>
@@ -8172,439 +8238,439 @@
       <c r="GE36" s="1"/>
     </row>
     <row r="37" spans="1:187" ht="15" customHeight="1">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="22"/>
-      <c r="Q37" s="23"/>
-      <c r="R37" s="23"/>
-      <c r="S37" s="23"/>
-      <c r="T37" s="23"/>
-      <c r="U37" s="23"/>
-      <c r="V37" s="23"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
-      <c r="AC37" s="14"/>
-      <c r="AD37" s="14"/>
-      <c r="AE37" s="15"/>
-      <c r="AF37" s="15"/>
-      <c r="AG37" s="15"/>
-      <c r="AH37" s="15"/>
-      <c r="AI37" s="15"/>
-      <c r="AJ37" s="15"/>
-      <c r="AK37" s="15"/>
-      <c r="AL37" s="15"/>
-      <c r="AM37" s="15"/>
-      <c r="AN37" s="15"/>
-      <c r="AO37" s="15"/>
-      <c r="AP37" s="15"/>
-      <c r="AQ37" s="15"/>
-      <c r="AR37" s="15"/>
-      <c r="AS37" s="15"/>
-      <c r="AT37" s="15"/>
-      <c r="AU37" s="15"/>
-      <c r="AV37" s="15"/>
-      <c r="AW37" s="15"/>
-      <c r="AX37" s="15"/>
-      <c r="AY37" s="15"/>
-      <c r="AZ37" s="15"/>
-      <c r="BA37" s="15"/>
-      <c r="BB37" s="15"/>
-      <c r="BC37" s="15"/>
-      <c r="BD37" s="1"/>
-      <c r="BE37" s="1"/>
-      <c r="BF37" s="1"/>
-      <c r="BG37" s="1"/>
-      <c r="BH37" s="1"/>
-      <c r="BI37" s="1"/>
-      <c r="BJ37" s="1"/>
-      <c r="BK37" s="1"/>
-      <c r="BL37" s="1"/>
-      <c r="BM37" s="1"/>
-      <c r="BN37" s="1"/>
-      <c r="BO37" s="1"/>
-      <c r="BP37" s="1"/>
-      <c r="BQ37" s="1"/>
-      <c r="BR37" s="1"/>
-      <c r="BS37" s="1"/>
-      <c r="BT37" s="1"/>
-      <c r="BU37" s="1"/>
-      <c r="BV37" s="1"/>
-      <c r="BW37" s="1"/>
-      <c r="BX37" s="1"/>
-      <c r="BY37" s="1"/>
-      <c r="BZ37" s="1"/>
-      <c r="CA37" s="1"/>
-      <c r="CB37" s="1"/>
-      <c r="CC37" s="1"/>
-      <c r="CD37" s="1"/>
-      <c r="CE37" s="1"/>
-      <c r="CF37" s="1"/>
-      <c r="CG37" s="1"/>
-      <c r="CH37" s="1"/>
-      <c r="CI37" s="1"/>
-      <c r="CJ37" s="1"/>
-      <c r="CK37" s="1"/>
-      <c r="CL37" s="1"/>
-      <c r="CM37" s="1"/>
-      <c r="CN37" s="1"/>
-      <c r="CO37" s="1"/>
-      <c r="CP37" s="1"/>
-      <c r="CQ37" s="1"/>
-      <c r="CR37" s="1"/>
-      <c r="CS37" s="1"/>
-      <c r="CT37" s="1"/>
-      <c r="CU37" s="1"/>
-      <c r="CV37" s="1"/>
-      <c r="CW37" s="1"/>
-      <c r="CX37" s="1"/>
-      <c r="CY37" s="1"/>
-      <c r="CZ37" s="1"/>
-      <c r="DA37" s="1"/>
-      <c r="DB37" s="1"/>
-      <c r="DC37" s="1"/>
-      <c r="DD37" s="1"/>
-      <c r="DE37" s="1"/>
-      <c r="DF37" s="1"/>
-      <c r="DG37" s="1"/>
-      <c r="DH37" s="1"/>
-      <c r="DI37" s="1"/>
-      <c r="DJ37" s="1"/>
-      <c r="DK37" s="1"/>
-      <c r="DL37" s="1"/>
-      <c r="DM37" s="1"/>
-      <c r="DN37" s="1"/>
-      <c r="DO37" s="1"/>
-      <c r="DP37" s="1"/>
-      <c r="DQ37" s="1"/>
-      <c r="DR37" s="1"/>
-      <c r="DS37" s="1"/>
-      <c r="DT37" s="1"/>
-      <c r="DU37" s="1"/>
-      <c r="DV37" s="1"/>
-      <c r="DW37" s="1"/>
-      <c r="DX37" s="1"/>
-      <c r="DY37" s="1"/>
-      <c r="DZ37" s="1"/>
-      <c r="EA37" s="1"/>
-      <c r="EB37" s="1"/>
-      <c r="EC37" s="1"/>
-      <c r="ED37" s="1"/>
-      <c r="EE37" s="1"/>
-      <c r="EF37" s="1"/>
-      <c r="EG37" s="1"/>
-      <c r="EH37" s="1"/>
-      <c r="EI37" s="1"/>
-      <c r="EJ37" s="1"/>
-      <c r="EK37" s="1"/>
-      <c r="EL37" s="1"/>
-      <c r="EM37" s="1"/>
-      <c r="EN37" s="1"/>
-      <c r="EO37" s="1"/>
-      <c r="EP37" s="1"/>
-      <c r="EQ37" s="1"/>
-      <c r="ER37" s="1"/>
-      <c r="ES37" s="1"/>
-      <c r="ET37" s="1"/>
-      <c r="EU37" s="1"/>
-      <c r="EV37" s="1"/>
-      <c r="EW37" s="1"/>
-      <c r="EX37" s="1"/>
-      <c r="EY37" s="1"/>
-      <c r="EZ37" s="1"/>
-      <c r="FA37" s="1"/>
-      <c r="FB37" s="1"/>
-      <c r="FC37" s="1"/>
-      <c r="FD37" s="1"/>
-      <c r="FE37" s="1"/>
-      <c r="FF37" s="1"/>
-      <c r="FG37" s="1"/>
-      <c r="FH37" s="1"/>
-      <c r="FI37" s="1"/>
-      <c r="FJ37" s="1"/>
-      <c r="FK37" s="1"/>
-      <c r="FL37" s="1"/>
-      <c r="FM37" s="1"/>
-      <c r="FN37" s="1"/>
-      <c r="FO37" s="1"/>
-      <c r="FP37" s="1"/>
-      <c r="FQ37" s="1"/>
-      <c r="FR37" s="1"/>
-      <c r="FS37" s="1"/>
-      <c r="FT37" s="1"/>
-      <c r="FU37" s="1"/>
-      <c r="FV37" s="1"/>
-      <c r="FW37" s="1"/>
-      <c r="FX37" s="1"/>
-      <c r="FY37" s="1"/>
-      <c r="FZ37" s="1"/>
-      <c r="GA37" s="1"/>
-      <c r="GB37" s="1"/>
-      <c r="GC37" s="1"/>
-      <c r="GD37" s="1"/>
-      <c r="GE37" s="1"/>
+      <c r="A37" s="25"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="25"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="25"/>
+      <c r="P37" s="25"/>
+      <c r="Q37" s="25"/>
+      <c r="R37" s="25"/>
+      <c r="S37" s="25"/>
+      <c r="T37" s="25"/>
+      <c r="U37" s="25"/>
+      <c r="V37" s="25"/>
+      <c r="W37" s="29"/>
+      <c r="X37" s="29"/>
+      <c r="Y37" s="29"/>
+      <c r="Z37" s="29"/>
+      <c r="AA37" s="29"/>
+      <c r="AB37" s="29"/>
+      <c r="AC37" s="29"/>
+      <c r="AD37" s="29"/>
+      <c r="AE37" s="30"/>
+      <c r="AF37" s="30"/>
+      <c r="AG37" s="30"/>
+      <c r="AH37" s="30"/>
+      <c r="AI37" s="30"/>
+      <c r="AJ37" s="30"/>
+      <c r="AK37" s="30"/>
+      <c r="AL37" s="30"/>
+      <c r="AM37" s="30"/>
+      <c r="AN37" s="30"/>
+      <c r="AO37" s="30"/>
+      <c r="AP37" s="30"/>
+      <c r="AQ37" s="30"/>
+      <c r="AR37" s="30"/>
+      <c r="AS37" s="30"/>
+      <c r="AT37" s="30"/>
+      <c r="AU37" s="30"/>
+      <c r="AV37" s="30"/>
+      <c r="AW37" s="30"/>
+      <c r="AX37" s="30"/>
+      <c r="AY37" s="30"/>
+      <c r="AZ37" s="30"/>
+      <c r="BA37" s="30"/>
+      <c r="BB37" s="30"/>
+      <c r="BC37" s="30"/>
+      <c r="BD37" s="8"/>
+      <c r="BE37" s="8"/>
+      <c r="BF37" s="8"/>
+      <c r="BG37" s="8"/>
+      <c r="BH37" s="8"/>
+      <c r="BI37" s="8"/>
+      <c r="BJ37" s="8"/>
+      <c r="BK37" s="8"/>
+      <c r="BL37" s="8"/>
+      <c r="BM37" s="8"/>
+      <c r="BN37" s="8"/>
+      <c r="BO37" s="8"/>
+      <c r="BP37" s="8"/>
+      <c r="BQ37" s="8"/>
+      <c r="BR37" s="8"/>
+      <c r="BS37" s="8"/>
+      <c r="BT37" s="8"/>
+      <c r="BU37" s="8"/>
+      <c r="BV37" s="8"/>
+      <c r="BW37" s="8"/>
+      <c r="BX37" s="8"/>
+      <c r="BY37" s="8"/>
+      <c r="BZ37" s="8"/>
+      <c r="CA37" s="8"/>
+      <c r="CB37" s="8"/>
+      <c r="CC37" s="8"/>
+      <c r="CD37" s="8"/>
+      <c r="CE37" s="8"/>
+      <c r="CF37" s="8"/>
+      <c r="CG37" s="8"/>
+      <c r="CH37" s="8"/>
+      <c r="CI37" s="8"/>
+      <c r="CJ37" s="8"/>
+      <c r="CK37" s="8"/>
+      <c r="CL37" s="8"/>
+      <c r="CM37" s="8"/>
+      <c r="CN37" s="8"/>
+      <c r="CO37" s="8"/>
+      <c r="CP37" s="8"/>
+      <c r="CQ37" s="8"/>
+      <c r="CR37" s="8"/>
+      <c r="CS37" s="8"/>
+      <c r="CT37" s="8"/>
+      <c r="CU37" s="8"/>
+      <c r="CV37" s="8"/>
+      <c r="CW37" s="8"/>
+      <c r="CX37" s="8"/>
+      <c r="CY37" s="8"/>
+      <c r="CZ37" s="8"/>
+      <c r="DA37" s="8"/>
+      <c r="DB37" s="8"/>
+      <c r="DC37" s="8"/>
+      <c r="DD37" s="8"/>
+      <c r="DE37" s="8"/>
+      <c r="DF37" s="8"/>
+      <c r="DG37" s="8"/>
+      <c r="DH37" s="8"/>
+      <c r="DI37" s="8"/>
+      <c r="DJ37" s="8"/>
+      <c r="DK37" s="8"/>
+      <c r="DL37" s="8"/>
+      <c r="DM37" s="8"/>
+      <c r="DN37" s="8"/>
+      <c r="DO37" s="8"/>
+      <c r="DP37" s="8"/>
+      <c r="DQ37" s="8"/>
+      <c r="DR37" s="8"/>
+      <c r="DS37" s="8"/>
+      <c r="DT37" s="8"/>
+      <c r="DU37" s="8"/>
+      <c r="DV37" s="8"/>
+      <c r="DW37" s="8"/>
+      <c r="DX37" s="8"/>
+      <c r="DY37" s="8"/>
+      <c r="DZ37" s="8"/>
+      <c r="EA37" s="8"/>
+      <c r="EB37" s="8"/>
+      <c r="EC37" s="8"/>
+      <c r="ED37" s="8"/>
+      <c r="EE37" s="8"/>
+      <c r="EF37" s="8"/>
+      <c r="EG37" s="8"/>
+      <c r="EH37" s="8"/>
+      <c r="EI37" s="8"/>
+      <c r="EJ37" s="8"/>
+      <c r="EK37" s="8"/>
+      <c r="EL37" s="8"/>
+      <c r="EM37" s="8"/>
+      <c r="EN37" s="8"/>
+      <c r="EO37" s="8"/>
+      <c r="EP37" s="8"/>
+      <c r="EQ37" s="8"/>
+      <c r="ER37" s="8"/>
+      <c r="ES37" s="8"/>
+      <c r="ET37" s="8"/>
+      <c r="EU37" s="8"/>
+      <c r="EV37" s="8"/>
+      <c r="EW37" s="8"/>
+      <c r="EX37" s="8"/>
+      <c r="EY37" s="8"/>
+      <c r="EZ37" s="8"/>
+      <c r="FA37" s="8"/>
+      <c r="FB37" s="8"/>
+      <c r="FC37" s="8"/>
+      <c r="FD37" s="8"/>
+      <c r="FE37" s="8"/>
+      <c r="FF37" s="8"/>
+      <c r="FG37" s="8"/>
+      <c r="FH37" s="8"/>
+      <c r="FI37" s="8"/>
+      <c r="FJ37" s="8"/>
+      <c r="FK37" s="8"/>
+      <c r="FL37" s="8"/>
+      <c r="FM37" s="8"/>
+      <c r="FN37" s="8"/>
+      <c r="FO37" s="8"/>
+      <c r="FP37" s="8"/>
+      <c r="FQ37" s="8"/>
+      <c r="FR37" s="8"/>
+      <c r="FS37" s="8"/>
+      <c r="FT37" s="8"/>
+      <c r="FU37" s="8"/>
+      <c r="FV37" s="8"/>
+      <c r="FW37" s="8"/>
+      <c r="FX37" s="8"/>
+      <c r="FY37" s="8"/>
+      <c r="FZ37" s="8"/>
+      <c r="GA37" s="8"/>
+      <c r="GB37" s="8"/>
+      <c r="GC37" s="8"/>
+      <c r="GD37" s="8"/>
+      <c r="GE37" s="8"/>
     </row>
     <row r="38" spans="1:187" ht="15" customHeight="1">
-      <c r="A38" s="26"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="27"/>
-      <c r="M38" s="27"/>
-      <c r="N38" s="27"/>
-      <c r="O38" s="27"/>
-      <c r="P38" s="27"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="26"/>
-      <c r="V38" s="26"/>
-      <c r="W38" s="28"/>
-      <c r="X38" s="28"/>
-      <c r="Y38" s="28"/>
-      <c r="Z38" s="28"/>
-      <c r="AA38" s="28"/>
-      <c r="AB38" s="28"/>
-      <c r="AC38" s="28"/>
-      <c r="AD38" s="28"/>
-      <c r="AE38" s="16"/>
-      <c r="AF38" s="16"/>
-      <c r="AG38" s="16"/>
-      <c r="AH38" s="16"/>
-      <c r="AI38" s="16"/>
-      <c r="AJ38" s="16"/>
-      <c r="AK38" s="16"/>
-      <c r="AL38" s="16"/>
-      <c r="AM38" s="16"/>
-      <c r="AN38" s="16"/>
-      <c r="AO38" s="16"/>
-      <c r="AP38" s="16"/>
-      <c r="AQ38" s="16"/>
-      <c r="AR38" s="16"/>
-      <c r="AS38" s="16"/>
-      <c r="AT38" s="16"/>
-      <c r="AU38" s="16"/>
-      <c r="AV38" s="16"/>
-      <c r="AW38" s="16"/>
-      <c r="AX38" s="16"/>
-      <c r="AY38" s="16"/>
-      <c r="AZ38" s="16"/>
-      <c r="BA38" s="16"/>
-      <c r="BB38" s="16"/>
-      <c r="BC38" s="16"/>
-      <c r="BD38" s="1"/>
-      <c r="BE38" s="1"/>
-      <c r="BF38" s="1"/>
-      <c r="BG38" s="1"/>
-      <c r="BH38" s="1"/>
-      <c r="BI38" s="1"/>
-      <c r="BJ38" s="1"/>
-      <c r="BK38" s="1"/>
-      <c r="BL38" s="1"/>
-      <c r="BM38" s="1"/>
-      <c r="BN38" s="1"/>
-      <c r="BO38" s="1"/>
-      <c r="BP38" s="1"/>
-      <c r="BQ38" s="1"/>
-      <c r="BR38" s="1"/>
-      <c r="BS38" s="1"/>
-      <c r="BT38" s="1"/>
-      <c r="BU38" s="1"/>
-      <c r="BV38" s="1"/>
-      <c r="BW38" s="1"/>
-      <c r="BX38" s="1"/>
-      <c r="BY38" s="1"/>
-      <c r="BZ38" s="1"/>
-      <c r="CA38" s="1"/>
-      <c r="CB38" s="1"/>
-      <c r="CC38" s="1"/>
-      <c r="CD38" s="1"/>
-      <c r="CE38" s="1"/>
-      <c r="CF38" s="1"/>
-      <c r="CG38" s="1"/>
-      <c r="CH38" s="1"/>
-      <c r="CI38" s="1"/>
-      <c r="CJ38" s="1"/>
-      <c r="CK38" s="1"/>
-      <c r="CL38" s="1"/>
-      <c r="CM38" s="1"/>
-      <c r="CN38" s="1"/>
-      <c r="CO38" s="1"/>
-      <c r="CP38" s="1"/>
-      <c r="CQ38" s="1"/>
-      <c r="CR38" s="1"/>
-      <c r="CS38" s="1"/>
-      <c r="CT38" s="1"/>
-      <c r="CU38" s="1"/>
-      <c r="CV38" s="1"/>
-      <c r="CW38" s="1"/>
-      <c r="CX38" s="1"/>
-      <c r="CY38" s="1"/>
-      <c r="CZ38" s="1"/>
-      <c r="DA38" s="1"/>
-      <c r="DB38" s="1"/>
-      <c r="DC38" s="1"/>
-      <c r="DD38" s="1"/>
-      <c r="DE38" s="1"/>
-      <c r="DF38" s="1"/>
-      <c r="DG38" s="1"/>
-      <c r="DH38" s="1"/>
-      <c r="DI38" s="1"/>
-      <c r="DJ38" s="1"/>
-      <c r="DK38" s="1"/>
-      <c r="DL38" s="1"/>
-      <c r="DM38" s="1"/>
-      <c r="DN38" s="1"/>
-      <c r="DO38" s="1"/>
-      <c r="DP38" s="1"/>
-      <c r="DQ38" s="1"/>
-      <c r="DR38" s="1"/>
-      <c r="DS38" s="1"/>
-      <c r="DT38" s="1"/>
-      <c r="DU38" s="1"/>
-      <c r="DV38" s="1"/>
-      <c r="DW38" s="1"/>
-      <c r="DX38" s="1"/>
-      <c r="DY38" s="1"/>
-      <c r="DZ38" s="1"/>
-      <c r="EA38" s="1"/>
-      <c r="EB38" s="1"/>
-      <c r="EC38" s="1"/>
-      <c r="ED38" s="1"/>
-      <c r="EE38" s="1"/>
-      <c r="EF38" s="1"/>
-      <c r="EG38" s="1"/>
-      <c r="EH38" s="1"/>
-      <c r="EI38" s="1"/>
-      <c r="EJ38" s="1"/>
-      <c r="EK38" s="1"/>
-      <c r="EL38" s="1"/>
-      <c r="EM38" s="1"/>
-      <c r="EN38" s="1"/>
-      <c r="EO38" s="1"/>
-      <c r="EP38" s="1"/>
-      <c r="EQ38" s="1"/>
-      <c r="ER38" s="1"/>
-      <c r="ES38" s="1"/>
-      <c r="ET38" s="1"/>
-      <c r="EU38" s="1"/>
-      <c r="EV38" s="1"/>
-      <c r="EW38" s="1"/>
-      <c r="EX38" s="1"/>
-      <c r="EY38" s="1"/>
-      <c r="EZ38" s="1"/>
-      <c r="FA38" s="1"/>
-      <c r="FB38" s="1"/>
-      <c r="FC38" s="1"/>
-      <c r="FD38" s="1"/>
-      <c r="FE38" s="1"/>
-      <c r="FF38" s="1"/>
-      <c r="FG38" s="1"/>
-      <c r="FH38" s="1"/>
-      <c r="FI38" s="1"/>
-      <c r="FJ38" s="1"/>
-      <c r="FK38" s="1"/>
-      <c r="FL38" s="1"/>
-      <c r="FM38" s="1"/>
-      <c r="FN38" s="1"/>
-      <c r="FO38" s="1"/>
-      <c r="FP38" s="1"/>
-      <c r="FQ38" s="1"/>
-      <c r="FR38" s="1"/>
-      <c r="FS38" s="1"/>
-      <c r="FT38" s="1"/>
-      <c r="FU38" s="1"/>
-      <c r="FV38" s="1"/>
-      <c r="FW38" s="1"/>
-      <c r="FX38" s="1"/>
-      <c r="FY38" s="1"/>
-      <c r="FZ38" s="1"/>
-      <c r="GA38" s="1"/>
-      <c r="GB38" s="1"/>
-      <c r="GC38" s="1"/>
-      <c r="GD38" s="1"/>
-      <c r="GE38" s="1"/>
+      <c r="A38" s="31"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="31"/>
+      <c r="M38" s="31"/>
+      <c r="N38" s="31"/>
+      <c r="O38" s="31"/>
+      <c r="P38" s="31"/>
+      <c r="Q38" s="31"/>
+      <c r="R38" s="31"/>
+      <c r="S38" s="31"/>
+      <c r="T38" s="31"/>
+      <c r="U38" s="31"/>
+      <c r="V38" s="31"/>
+      <c r="W38" s="32"/>
+      <c r="X38" s="32"/>
+      <c r="Y38" s="32"/>
+      <c r="Z38" s="32"/>
+      <c r="AA38" s="32"/>
+      <c r="AB38" s="32"/>
+      <c r="AC38" s="32"/>
+      <c r="AD38" s="32"/>
+      <c r="AE38" s="24"/>
+      <c r="AF38" s="24"/>
+      <c r="AG38" s="24"/>
+      <c r="AH38" s="24"/>
+      <c r="AI38" s="24"/>
+      <c r="AJ38" s="24"/>
+      <c r="AK38" s="24"/>
+      <c r="AL38" s="24"/>
+      <c r="AM38" s="24"/>
+      <c r="AN38" s="24"/>
+      <c r="AO38" s="24"/>
+      <c r="AP38" s="24"/>
+      <c r="AQ38" s="24"/>
+      <c r="AR38" s="24"/>
+      <c r="AS38" s="24"/>
+      <c r="AT38" s="24"/>
+      <c r="AU38" s="24"/>
+      <c r="AV38" s="24"/>
+      <c r="AW38" s="24"/>
+      <c r="AX38" s="24"/>
+      <c r="AY38" s="24"/>
+      <c r="AZ38" s="24"/>
+      <c r="BA38" s="24"/>
+      <c r="BB38" s="24"/>
+      <c r="BC38" s="24"/>
+      <c r="BD38" s="8"/>
+      <c r="BE38" s="8"/>
+      <c r="BF38" s="8"/>
+      <c r="BG38" s="8"/>
+      <c r="BH38" s="8"/>
+      <c r="BI38" s="8"/>
+      <c r="BJ38" s="8"/>
+      <c r="BK38" s="8"/>
+      <c r="BL38" s="8"/>
+      <c r="BM38" s="8"/>
+      <c r="BN38" s="8"/>
+      <c r="BO38" s="8"/>
+      <c r="BP38" s="8"/>
+      <c r="BQ38" s="8"/>
+      <c r="BR38" s="8"/>
+      <c r="BS38" s="8"/>
+      <c r="BT38" s="8"/>
+      <c r="BU38" s="8"/>
+      <c r="BV38" s="8"/>
+      <c r="BW38" s="8"/>
+      <c r="BX38" s="8"/>
+      <c r="BY38" s="8"/>
+      <c r="BZ38" s="8"/>
+      <c r="CA38" s="8"/>
+      <c r="CB38" s="8"/>
+      <c r="CC38" s="8"/>
+      <c r="CD38" s="8"/>
+      <c r="CE38" s="8"/>
+      <c r="CF38" s="8"/>
+      <c r="CG38" s="8"/>
+      <c r="CH38" s="8"/>
+      <c r="CI38" s="8"/>
+      <c r="CJ38" s="8"/>
+      <c r="CK38" s="8"/>
+      <c r="CL38" s="8"/>
+      <c r="CM38" s="8"/>
+      <c r="CN38" s="8"/>
+      <c r="CO38" s="8"/>
+      <c r="CP38" s="8"/>
+      <c r="CQ38" s="8"/>
+      <c r="CR38" s="8"/>
+      <c r="CS38" s="8"/>
+      <c r="CT38" s="8"/>
+      <c r="CU38" s="8"/>
+      <c r="CV38" s="8"/>
+      <c r="CW38" s="8"/>
+      <c r="CX38" s="8"/>
+      <c r="CY38" s="8"/>
+      <c r="CZ38" s="8"/>
+      <c r="DA38" s="8"/>
+      <c r="DB38" s="8"/>
+      <c r="DC38" s="8"/>
+      <c r="DD38" s="8"/>
+      <c r="DE38" s="8"/>
+      <c r="DF38" s="8"/>
+      <c r="DG38" s="8"/>
+      <c r="DH38" s="8"/>
+      <c r="DI38" s="8"/>
+      <c r="DJ38" s="8"/>
+      <c r="DK38" s="8"/>
+      <c r="DL38" s="8"/>
+      <c r="DM38" s="8"/>
+      <c r="DN38" s="8"/>
+      <c r="DO38" s="8"/>
+      <c r="DP38" s="8"/>
+      <c r="DQ38" s="8"/>
+      <c r="DR38" s="8"/>
+      <c r="DS38" s="8"/>
+      <c r="DT38" s="8"/>
+      <c r="DU38" s="8"/>
+      <c r="DV38" s="8"/>
+      <c r="DW38" s="8"/>
+      <c r="DX38" s="8"/>
+      <c r="DY38" s="8"/>
+      <c r="DZ38" s="8"/>
+      <c r="EA38" s="8"/>
+      <c r="EB38" s="8"/>
+      <c r="EC38" s="8"/>
+      <c r="ED38" s="8"/>
+      <c r="EE38" s="8"/>
+      <c r="EF38" s="8"/>
+      <c r="EG38" s="8"/>
+      <c r="EH38" s="8"/>
+      <c r="EI38" s="8"/>
+      <c r="EJ38" s="8"/>
+      <c r="EK38" s="8"/>
+      <c r="EL38" s="8"/>
+      <c r="EM38" s="8"/>
+      <c r="EN38" s="8"/>
+      <c r="EO38" s="8"/>
+      <c r="EP38" s="8"/>
+      <c r="EQ38" s="8"/>
+      <c r="ER38" s="8"/>
+      <c r="ES38" s="8"/>
+      <c r="ET38" s="8"/>
+      <c r="EU38" s="8"/>
+      <c r="EV38" s="8"/>
+      <c r="EW38" s="8"/>
+      <c r="EX38" s="8"/>
+      <c r="EY38" s="8"/>
+      <c r="EZ38" s="8"/>
+      <c r="FA38" s="8"/>
+      <c r="FB38" s="8"/>
+      <c r="FC38" s="8"/>
+      <c r="FD38" s="8"/>
+      <c r="FE38" s="8"/>
+      <c r="FF38" s="8"/>
+      <c r="FG38" s="8"/>
+      <c r="FH38" s="8"/>
+      <c r="FI38" s="8"/>
+      <c r="FJ38" s="8"/>
+      <c r="FK38" s="8"/>
+      <c r="FL38" s="8"/>
+      <c r="FM38" s="8"/>
+      <c r="FN38" s="8"/>
+      <c r="FO38" s="8"/>
+      <c r="FP38" s="8"/>
+      <c r="FQ38" s="8"/>
+      <c r="FR38" s="8"/>
+      <c r="FS38" s="8"/>
+      <c r="FT38" s="8"/>
+      <c r="FU38" s="8"/>
+      <c r="FV38" s="8"/>
+      <c r="FW38" s="8"/>
+      <c r="FX38" s="8"/>
+      <c r="FY38" s="8"/>
+      <c r="FZ38" s="8"/>
+      <c r="GA38" s="8"/>
+      <c r="GB38" s="8"/>
+      <c r="GC38" s="8"/>
+      <c r="GD38" s="8"/>
+      <c r="GE38" s="8"/>
     </row>
     <row r="39" spans="1:187" ht="15" customHeight="1">
-      <c r="A39" s="26"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="27"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="26"/>
-      <c r="S39" s="26"/>
-      <c r="T39" s="26"/>
-      <c r="U39" s="26"/>
-      <c r="V39" s="26"/>
-      <c r="W39" s="28"/>
-      <c r="X39" s="28"/>
-      <c r="Y39" s="28"/>
-      <c r="Z39" s="28"/>
-      <c r="AA39" s="28"/>
-      <c r="AB39" s="28"/>
-      <c r="AC39" s="28"/>
-      <c r="AD39" s="28"/>
-      <c r="AE39" s="16"/>
-      <c r="AF39" s="16"/>
-      <c r="AG39" s="16"/>
-      <c r="AH39" s="16"/>
-      <c r="AI39" s="16"/>
-      <c r="AJ39" s="16"/>
-      <c r="AK39" s="16"/>
-      <c r="AL39" s="16"/>
-      <c r="AM39" s="16"/>
-      <c r="AN39" s="16"/>
-      <c r="AO39" s="16"/>
-      <c r="AP39" s="16"/>
-      <c r="AQ39" s="16"/>
-      <c r="AR39" s="16"/>
-      <c r="AS39" s="16"/>
-      <c r="AT39" s="16"/>
-      <c r="AU39" s="16"/>
-      <c r="AV39" s="16"/>
-      <c r="AW39" s="16"/>
-      <c r="AX39" s="16"/>
-      <c r="AY39" s="16"/>
-      <c r="AZ39" s="16"/>
-      <c r="BA39" s="16"/>
-      <c r="BB39" s="16"/>
-      <c r="BC39" s="16"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="14"/>
+      <c r="X39" s="18"/>
+      <c r="Y39" s="18"/>
+      <c r="Z39" s="18"/>
+      <c r="AA39" s="18"/>
+      <c r="AB39" s="18"/>
+      <c r="AC39" s="18"/>
+      <c r="AD39" s="18"/>
+      <c r="AE39" s="19"/>
+      <c r="AF39" s="20"/>
+      <c r="AG39" s="20"/>
+      <c r="AH39" s="20"/>
+      <c r="AI39" s="20"/>
+      <c r="AJ39" s="20"/>
+      <c r="AK39" s="20"/>
+      <c r="AL39" s="20"/>
+      <c r="AM39" s="20"/>
+      <c r="AN39" s="20"/>
+      <c r="AO39" s="20"/>
+      <c r="AP39" s="20"/>
+      <c r="AQ39" s="20"/>
+      <c r="AR39" s="20"/>
+      <c r="AS39" s="20"/>
+      <c r="AT39" s="20"/>
+      <c r="AU39" s="20"/>
+      <c r="AV39" s="20"/>
+      <c r="AW39" s="20"/>
+      <c r="AX39" s="20"/>
+      <c r="AY39" s="20"/>
+      <c r="AZ39" s="20"/>
+      <c r="BA39" s="20"/>
+      <c r="BB39" s="20"/>
+      <c r="BC39" s="20"/>
       <c r="BD39" s="1"/>
       <c r="BE39" s="1"/>
       <c r="BF39" s="1"/>
@@ -8738,29 +8804,29 @@
       <c r="GD39" s="1"/>
       <c r="GE39" s="1"/>
     </row>
-    <row r="40" spans="1:187" s="10" customFormat="1" ht="15" customHeight="1">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
-      <c r="L40" s="13"/>
-      <c r="M40" s="13"/>
-      <c r="N40" s="13"/>
-      <c r="O40" s="13"/>
-      <c r="P40" s="13"/>
-      <c r="Q40" s="12"/>
-      <c r="R40" s="12"/>
-      <c r="S40" s="12"/>
-      <c r="T40" s="12"/>
-      <c r="U40" s="12"/>
-      <c r="V40" s="12"/>
+    <row r="40" spans="1:187" ht="15" customHeight="1">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="23"/>
+      <c r="U40" s="23"/>
+      <c r="V40" s="23"/>
       <c r="W40" s="14"/>
       <c r="X40" s="14"/>
       <c r="Y40" s="14"/>
@@ -8794,138 +8860,138 @@
       <c r="BA40" s="15"/>
       <c r="BB40" s="15"/>
       <c r="BC40" s="15"/>
-      <c r="BD40" s="9"/>
-      <c r="BE40" s="9"/>
-      <c r="BF40" s="9"/>
-      <c r="BG40" s="9"/>
-      <c r="BH40" s="9"/>
-      <c r="BI40" s="9"/>
-      <c r="BJ40" s="9"/>
-      <c r="BK40" s="9"/>
-      <c r="BL40" s="9"/>
-      <c r="BM40" s="9"/>
-      <c r="BN40" s="9"/>
-      <c r="BO40" s="9"/>
-      <c r="BP40" s="9"/>
-      <c r="BQ40" s="9"/>
-      <c r="BR40" s="9"/>
-      <c r="BS40" s="9"/>
-      <c r="BT40" s="9"/>
-      <c r="BU40" s="9"/>
-      <c r="BV40" s="9"/>
-      <c r="BW40" s="9"/>
-      <c r="BX40" s="9"/>
-      <c r="BY40" s="9"/>
-      <c r="BZ40" s="9"/>
-      <c r="CA40" s="9"/>
-      <c r="CB40" s="9"/>
-      <c r="CC40" s="9"/>
-      <c r="CD40" s="9"/>
-      <c r="CE40" s="9"/>
-      <c r="CF40" s="9"/>
-      <c r="CG40" s="9"/>
-      <c r="CH40" s="9"/>
-      <c r="CI40" s="9"/>
-      <c r="CJ40" s="9"/>
-      <c r="CK40" s="9"/>
-      <c r="CL40" s="9"/>
-      <c r="CM40" s="9"/>
-      <c r="CN40" s="9"/>
-      <c r="CO40" s="9"/>
-      <c r="CP40" s="9"/>
-      <c r="CQ40" s="9"/>
-      <c r="CR40" s="9"/>
-      <c r="CS40" s="9"/>
-      <c r="CT40" s="9"/>
-      <c r="CU40" s="9"/>
-      <c r="CV40" s="9"/>
-      <c r="CW40" s="9"/>
-      <c r="CX40" s="9"/>
-      <c r="CY40" s="9"/>
-      <c r="CZ40" s="9"/>
-      <c r="DA40" s="9"/>
-      <c r="DB40" s="9"/>
-      <c r="DC40" s="9"/>
-      <c r="DD40" s="9"/>
-      <c r="DE40" s="9"/>
-      <c r="DF40" s="9"/>
-      <c r="DG40" s="9"/>
-      <c r="DH40" s="9"/>
-      <c r="DI40" s="9"/>
-      <c r="DJ40" s="9"/>
-      <c r="DK40" s="9"/>
-      <c r="DL40" s="9"/>
-      <c r="DM40" s="9"/>
-      <c r="DN40" s="9"/>
-      <c r="DO40" s="9"/>
-      <c r="DP40" s="9"/>
-      <c r="DQ40" s="9"/>
-      <c r="DR40" s="9"/>
-      <c r="DS40" s="9"/>
-      <c r="DT40" s="9"/>
-      <c r="DU40" s="9"/>
-      <c r="DV40" s="9"/>
-      <c r="DW40" s="9"/>
-      <c r="DX40" s="9"/>
-      <c r="DY40" s="9"/>
-      <c r="DZ40" s="9"/>
-      <c r="EA40" s="9"/>
-      <c r="EB40" s="9"/>
-      <c r="EC40" s="9"/>
-      <c r="ED40" s="9"/>
-      <c r="EE40" s="9"/>
-      <c r="EF40" s="9"/>
-      <c r="EG40" s="9"/>
-      <c r="EH40" s="9"/>
-      <c r="EI40" s="9"/>
-      <c r="EJ40" s="9"/>
-      <c r="EK40" s="9"/>
-      <c r="EL40" s="9"/>
-      <c r="EM40" s="9"/>
-      <c r="EN40" s="9"/>
-      <c r="EO40" s="9"/>
-      <c r="EP40" s="9"/>
-      <c r="EQ40" s="9"/>
-      <c r="ER40" s="9"/>
-      <c r="ES40" s="9"/>
-      <c r="ET40" s="9"/>
-      <c r="EU40" s="9"/>
-      <c r="EV40" s="9"/>
-      <c r="EW40" s="9"/>
-      <c r="EX40" s="9"/>
-      <c r="EY40" s="9"/>
-      <c r="EZ40" s="9"/>
-      <c r="FA40" s="9"/>
-      <c r="FB40" s="9"/>
-      <c r="FC40" s="9"/>
-      <c r="FD40" s="9"/>
-      <c r="FE40" s="9"/>
-      <c r="FF40" s="9"/>
-      <c r="FG40" s="9"/>
-      <c r="FH40" s="9"/>
-      <c r="FI40" s="9"/>
-      <c r="FJ40" s="9"/>
-      <c r="FK40" s="9"/>
-      <c r="FL40" s="9"/>
-      <c r="FM40" s="9"/>
-      <c r="FN40" s="9"/>
-      <c r="FO40" s="9"/>
-      <c r="FP40" s="9"/>
-      <c r="FQ40" s="9"/>
-      <c r="FR40" s="9"/>
-      <c r="FS40" s="9"/>
-      <c r="FT40" s="9"/>
-      <c r="FU40" s="9"/>
-      <c r="FV40" s="9"/>
-      <c r="FW40" s="9"/>
-      <c r="FX40" s="9"/>
-      <c r="FY40" s="9"/>
-      <c r="FZ40" s="9"/>
-      <c r="GA40" s="9"/>
-      <c r="GB40" s="9"/>
-      <c r="GC40" s="9"/>
-      <c r="GD40" s="9"/>
-      <c r="GE40" s="9"/>
+      <c r="BD40" s="1"/>
+      <c r="BE40" s="1"/>
+      <c r="BF40" s="1"/>
+      <c r="BG40" s="1"/>
+      <c r="BH40" s="1"/>
+      <c r="BI40" s="1"/>
+      <c r="BJ40" s="1"/>
+      <c r="BK40" s="1"/>
+      <c r="BL40" s="1"/>
+      <c r="BM40" s="1"/>
+      <c r="BN40" s="1"/>
+      <c r="BO40" s="1"/>
+      <c r="BP40" s="1"/>
+      <c r="BQ40" s="1"/>
+      <c r="BR40" s="1"/>
+      <c r="BS40" s="1"/>
+      <c r="BT40" s="1"/>
+      <c r="BU40" s="1"/>
+      <c r="BV40" s="1"/>
+      <c r="BW40" s="1"/>
+      <c r="BX40" s="1"/>
+      <c r="BY40" s="1"/>
+      <c r="BZ40" s="1"/>
+      <c r="CA40" s="1"/>
+      <c r="CB40" s="1"/>
+      <c r="CC40" s="1"/>
+      <c r="CD40" s="1"/>
+      <c r="CE40" s="1"/>
+      <c r="CF40" s="1"/>
+      <c r="CG40" s="1"/>
+      <c r="CH40" s="1"/>
+      <c r="CI40" s="1"/>
+      <c r="CJ40" s="1"/>
+      <c r="CK40" s="1"/>
+      <c r="CL40" s="1"/>
+      <c r="CM40" s="1"/>
+      <c r="CN40" s="1"/>
+      <c r="CO40" s="1"/>
+      <c r="CP40" s="1"/>
+      <c r="CQ40" s="1"/>
+      <c r="CR40" s="1"/>
+      <c r="CS40" s="1"/>
+      <c r="CT40" s="1"/>
+      <c r="CU40" s="1"/>
+      <c r="CV40" s="1"/>
+      <c r="CW40" s="1"/>
+      <c r="CX40" s="1"/>
+      <c r="CY40" s="1"/>
+      <c r="CZ40" s="1"/>
+      <c r="DA40" s="1"/>
+      <c r="DB40" s="1"/>
+      <c r="DC40" s="1"/>
+      <c r="DD40" s="1"/>
+      <c r="DE40" s="1"/>
+      <c r="DF40" s="1"/>
+      <c r="DG40" s="1"/>
+      <c r="DH40" s="1"/>
+      <c r="DI40" s="1"/>
+      <c r="DJ40" s="1"/>
+      <c r="DK40" s="1"/>
+      <c r="DL40" s="1"/>
+      <c r="DM40" s="1"/>
+      <c r="DN40" s="1"/>
+      <c r="DO40" s="1"/>
+      <c r="DP40" s="1"/>
+      <c r="DQ40" s="1"/>
+      <c r="DR40" s="1"/>
+      <c r="DS40" s="1"/>
+      <c r="DT40" s="1"/>
+      <c r="DU40" s="1"/>
+      <c r="DV40" s="1"/>
+      <c r="DW40" s="1"/>
+      <c r="DX40" s="1"/>
+      <c r="DY40" s="1"/>
+      <c r="DZ40" s="1"/>
+      <c r="EA40" s="1"/>
+      <c r="EB40" s="1"/>
+      <c r="EC40" s="1"/>
+      <c r="ED40" s="1"/>
+      <c r="EE40" s="1"/>
+      <c r="EF40" s="1"/>
+      <c r="EG40" s="1"/>
+      <c r="EH40" s="1"/>
+      <c r="EI40" s="1"/>
+      <c r="EJ40" s="1"/>
+      <c r="EK40" s="1"/>
+      <c r="EL40" s="1"/>
+      <c r="EM40" s="1"/>
+      <c r="EN40" s="1"/>
+      <c r="EO40" s="1"/>
+      <c r="EP40" s="1"/>
+      <c r="EQ40" s="1"/>
+      <c r="ER40" s="1"/>
+      <c r="ES40" s="1"/>
+      <c r="ET40" s="1"/>
+      <c r="EU40" s="1"/>
+      <c r="EV40" s="1"/>
+      <c r="EW40" s="1"/>
+      <c r="EX40" s="1"/>
+      <c r="EY40" s="1"/>
+      <c r="EZ40" s="1"/>
+      <c r="FA40" s="1"/>
+      <c r="FB40" s="1"/>
+      <c r="FC40" s="1"/>
+      <c r="FD40" s="1"/>
+      <c r="FE40" s="1"/>
+      <c r="FF40" s="1"/>
+      <c r="FG40" s="1"/>
+      <c r="FH40" s="1"/>
+      <c r="FI40" s="1"/>
+      <c r="FJ40" s="1"/>
+      <c r="FK40" s="1"/>
+      <c r="FL40" s="1"/>
+      <c r="FM40" s="1"/>
+      <c r="FN40" s="1"/>
+      <c r="FO40" s="1"/>
+      <c r="FP40" s="1"/>
+      <c r="FQ40" s="1"/>
+      <c r="FR40" s="1"/>
+      <c r="FS40" s="1"/>
+      <c r="FT40" s="1"/>
+      <c r="FU40" s="1"/>
+      <c r="FV40" s="1"/>
+      <c r="FW40" s="1"/>
+      <c r="FX40" s="1"/>
+      <c r="FY40" s="1"/>
+      <c r="FZ40" s="1"/>
+      <c r="GA40" s="1"/>
+      <c r="GB40" s="1"/>
+      <c r="GC40" s="1"/>
+      <c r="GD40" s="1"/>
+      <c r="GE40" s="1"/>
     </row>
     <row r="41" spans="1:187" ht="15" customHeight="1">
       <c r="A41" s="26"/>
@@ -9116,62 +9182,62 @@
       <c r="GD41" s="1"/>
       <c r="GE41" s="1"/>
     </row>
-    <row r="42" spans="1:187" ht="13.5" customHeight="1">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="3"/>
-      <c r="AA42" s="3"/>
-      <c r="AB42" s="3"/>
-      <c r="AC42" s="3"/>
-      <c r="AD42" s="3"/>
-      <c r="AE42" s="3"/>
-      <c r="AF42" s="3"/>
-      <c r="AG42" s="3"/>
-      <c r="AH42" s="3"/>
-      <c r="AI42" s="3"/>
-      <c r="AJ42" s="3"/>
-      <c r="AK42" s="3"/>
-      <c r="AL42" s="3"/>
-      <c r="AM42" s="3"/>
-      <c r="AN42" s="3"/>
-      <c r="AO42" s="3"/>
-      <c r="AP42" s="3"/>
-      <c r="AQ42" s="3"/>
-      <c r="AR42" s="3"/>
-      <c r="AS42" s="3"/>
-      <c r="AT42" s="3"/>
-      <c r="AU42" s="3"/>
-      <c r="AV42" s="3"/>
-      <c r="AW42" s="3"/>
-      <c r="AX42" s="3"/>
-      <c r="AY42" s="3"/>
-      <c r="AZ42" s="3"/>
-      <c r="BA42" s="3"/>
-      <c r="BB42" s="3"/>
-      <c r="BC42" s="3"/>
+    <row r="42" spans="1:187" ht="15" customHeight="1">
+      <c r="A42" s="26"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="27"/>
+      <c r="K42" s="27"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="27"/>
+      <c r="N42" s="27"/>
+      <c r="O42" s="27"/>
+      <c r="P42" s="27"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="26"/>
+      <c r="S42" s="26"/>
+      <c r="T42" s="26"/>
+      <c r="U42" s="26"/>
+      <c r="V42" s="26"/>
+      <c r="W42" s="28"/>
+      <c r="X42" s="28"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="28"/>
+      <c r="AA42" s="28"/>
+      <c r="AB42" s="28"/>
+      <c r="AC42" s="28"/>
+      <c r="AD42" s="28"/>
+      <c r="AE42" s="16"/>
+      <c r="AF42" s="16"/>
+      <c r="AG42" s="16"/>
+      <c r="AH42" s="16"/>
+      <c r="AI42" s="16"/>
+      <c r="AJ42" s="16"/>
+      <c r="AK42" s="16"/>
+      <c r="AL42" s="16"/>
+      <c r="AM42" s="16"/>
+      <c r="AN42" s="16"/>
+      <c r="AO42" s="16"/>
+      <c r="AP42" s="16"/>
+      <c r="AQ42" s="16"/>
+      <c r="AR42" s="16"/>
+      <c r="AS42" s="16"/>
+      <c r="AT42" s="16"/>
+      <c r="AU42" s="16"/>
+      <c r="AV42" s="16"/>
+      <c r="AW42" s="16"/>
+      <c r="AX42" s="16"/>
+      <c r="AY42" s="16"/>
+      <c r="AZ42" s="16"/>
+      <c r="BA42" s="16"/>
+      <c r="BB42" s="16"/>
+      <c r="BC42" s="16"/>
       <c r="BD42" s="1"/>
       <c r="BE42" s="1"/>
       <c r="BF42" s="1"/>
@@ -9305,8 +9371,586 @@
       <c r="GD42" s="1"/>
       <c r="GE42" s="1"/>
     </row>
+    <row r="43" spans="1:187" s="10" customFormat="1" ht="15" customHeight="1">
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="12"/>
+      <c r="R43" s="12"/>
+      <c r="S43" s="12"/>
+      <c r="T43" s="12"/>
+      <c r="U43" s="12"/>
+      <c r="V43" s="12"/>
+      <c r="W43" s="14"/>
+      <c r="X43" s="14"/>
+      <c r="Y43" s="14"/>
+      <c r="Z43" s="14"/>
+      <c r="AA43" s="14"/>
+      <c r="AB43" s="14"/>
+      <c r="AC43" s="14"/>
+      <c r="AD43" s="14"/>
+      <c r="AE43" s="15"/>
+      <c r="AF43" s="15"/>
+      <c r="AG43" s="15"/>
+      <c r="AH43" s="15"/>
+      <c r="AI43" s="15"/>
+      <c r="AJ43" s="15"/>
+      <c r="AK43" s="15"/>
+      <c r="AL43" s="15"/>
+      <c r="AM43" s="15"/>
+      <c r="AN43" s="15"/>
+      <c r="AO43" s="15"/>
+      <c r="AP43" s="15"/>
+      <c r="AQ43" s="15"/>
+      <c r="AR43" s="15"/>
+      <c r="AS43" s="15"/>
+      <c r="AT43" s="15"/>
+      <c r="AU43" s="15"/>
+      <c r="AV43" s="15"/>
+      <c r="AW43" s="15"/>
+      <c r="AX43" s="15"/>
+      <c r="AY43" s="15"/>
+      <c r="AZ43" s="15"/>
+      <c r="BA43" s="15"/>
+      <c r="BB43" s="15"/>
+      <c r="BC43" s="15"/>
+      <c r="BD43" s="9"/>
+      <c r="BE43" s="9"/>
+      <c r="BF43" s="9"/>
+      <c r="BG43" s="9"/>
+      <c r="BH43" s="9"/>
+      <c r="BI43" s="9"/>
+      <c r="BJ43" s="9"/>
+      <c r="BK43" s="9"/>
+      <c r="BL43" s="9"/>
+      <c r="BM43" s="9"/>
+      <c r="BN43" s="9"/>
+      <c r="BO43" s="9"/>
+      <c r="BP43" s="9"/>
+      <c r="BQ43" s="9"/>
+      <c r="BR43" s="9"/>
+      <c r="BS43" s="9"/>
+      <c r="BT43" s="9"/>
+      <c r="BU43" s="9"/>
+      <c r="BV43" s="9"/>
+      <c r="BW43" s="9"/>
+      <c r="BX43" s="9"/>
+      <c r="BY43" s="9"/>
+      <c r="BZ43" s="9"/>
+      <c r="CA43" s="9"/>
+      <c r="CB43" s="9"/>
+      <c r="CC43" s="9"/>
+      <c r="CD43" s="9"/>
+      <c r="CE43" s="9"/>
+      <c r="CF43" s="9"/>
+      <c r="CG43" s="9"/>
+      <c r="CH43" s="9"/>
+      <c r="CI43" s="9"/>
+      <c r="CJ43" s="9"/>
+      <c r="CK43" s="9"/>
+      <c r="CL43" s="9"/>
+      <c r="CM43" s="9"/>
+      <c r="CN43" s="9"/>
+      <c r="CO43" s="9"/>
+      <c r="CP43" s="9"/>
+      <c r="CQ43" s="9"/>
+      <c r="CR43" s="9"/>
+      <c r="CS43" s="9"/>
+      <c r="CT43" s="9"/>
+      <c r="CU43" s="9"/>
+      <c r="CV43" s="9"/>
+      <c r="CW43" s="9"/>
+      <c r="CX43" s="9"/>
+      <c r="CY43" s="9"/>
+      <c r="CZ43" s="9"/>
+      <c r="DA43" s="9"/>
+      <c r="DB43" s="9"/>
+      <c r="DC43" s="9"/>
+      <c r="DD43" s="9"/>
+      <c r="DE43" s="9"/>
+      <c r="DF43" s="9"/>
+      <c r="DG43" s="9"/>
+      <c r="DH43" s="9"/>
+      <c r="DI43" s="9"/>
+      <c r="DJ43" s="9"/>
+      <c r="DK43" s="9"/>
+      <c r="DL43" s="9"/>
+      <c r="DM43" s="9"/>
+      <c r="DN43" s="9"/>
+      <c r="DO43" s="9"/>
+      <c r="DP43" s="9"/>
+      <c r="DQ43" s="9"/>
+      <c r="DR43" s="9"/>
+      <c r="DS43" s="9"/>
+      <c r="DT43" s="9"/>
+      <c r="DU43" s="9"/>
+      <c r="DV43" s="9"/>
+      <c r="DW43" s="9"/>
+      <c r="DX43" s="9"/>
+      <c r="DY43" s="9"/>
+      <c r="DZ43" s="9"/>
+      <c r="EA43" s="9"/>
+      <c r="EB43" s="9"/>
+      <c r="EC43" s="9"/>
+      <c r="ED43" s="9"/>
+      <c r="EE43" s="9"/>
+      <c r="EF43" s="9"/>
+      <c r="EG43" s="9"/>
+      <c r="EH43" s="9"/>
+      <c r="EI43" s="9"/>
+      <c r="EJ43" s="9"/>
+      <c r="EK43" s="9"/>
+      <c r="EL43" s="9"/>
+      <c r="EM43" s="9"/>
+      <c r="EN43" s="9"/>
+      <c r="EO43" s="9"/>
+      <c r="EP43" s="9"/>
+      <c r="EQ43" s="9"/>
+      <c r="ER43" s="9"/>
+      <c r="ES43" s="9"/>
+      <c r="ET43" s="9"/>
+      <c r="EU43" s="9"/>
+      <c r="EV43" s="9"/>
+      <c r="EW43" s="9"/>
+      <c r="EX43" s="9"/>
+      <c r="EY43" s="9"/>
+      <c r="EZ43" s="9"/>
+      <c r="FA43" s="9"/>
+      <c r="FB43" s="9"/>
+      <c r="FC43" s="9"/>
+      <c r="FD43" s="9"/>
+      <c r="FE43" s="9"/>
+      <c r="FF43" s="9"/>
+      <c r="FG43" s="9"/>
+      <c r="FH43" s="9"/>
+      <c r="FI43" s="9"/>
+      <c r="FJ43" s="9"/>
+      <c r="FK43" s="9"/>
+      <c r="FL43" s="9"/>
+      <c r="FM43" s="9"/>
+      <c r="FN43" s="9"/>
+      <c r="FO43" s="9"/>
+      <c r="FP43" s="9"/>
+      <c r="FQ43" s="9"/>
+      <c r="FR43" s="9"/>
+      <c r="FS43" s="9"/>
+      <c r="FT43" s="9"/>
+      <c r="FU43" s="9"/>
+      <c r="FV43" s="9"/>
+      <c r="FW43" s="9"/>
+      <c r="FX43" s="9"/>
+      <c r="FY43" s="9"/>
+      <c r="FZ43" s="9"/>
+      <c r="GA43" s="9"/>
+      <c r="GB43" s="9"/>
+      <c r="GC43" s="9"/>
+      <c r="GD43" s="9"/>
+      <c r="GE43" s="9"/>
+    </row>
+    <row r="44" spans="1:187" ht="15" customHeight="1">
+      <c r="A44" s="26"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="27"/>
+      <c r="K44" s="27"/>
+      <c r="L44" s="27"/>
+      <c r="M44" s="27"/>
+      <c r="N44" s="27"/>
+      <c r="O44" s="27"/>
+      <c r="P44" s="27"/>
+      <c r="Q44" s="26"/>
+      <c r="R44" s="26"/>
+      <c r="S44" s="26"/>
+      <c r="T44" s="26"/>
+      <c r="U44" s="26"/>
+      <c r="V44" s="26"/>
+      <c r="W44" s="28"/>
+      <c r="X44" s="28"/>
+      <c r="Y44" s="28"/>
+      <c r="Z44" s="28"/>
+      <c r="AA44" s="28"/>
+      <c r="AB44" s="28"/>
+      <c r="AC44" s="28"/>
+      <c r="AD44" s="28"/>
+      <c r="AE44" s="16"/>
+      <c r="AF44" s="16"/>
+      <c r="AG44" s="16"/>
+      <c r="AH44" s="16"/>
+      <c r="AI44" s="16"/>
+      <c r="AJ44" s="16"/>
+      <c r="AK44" s="16"/>
+      <c r="AL44" s="16"/>
+      <c r="AM44" s="16"/>
+      <c r="AN44" s="16"/>
+      <c r="AO44" s="16"/>
+      <c r="AP44" s="16"/>
+      <c r="AQ44" s="16"/>
+      <c r="AR44" s="16"/>
+      <c r="AS44" s="16"/>
+      <c r="AT44" s="16"/>
+      <c r="AU44" s="16"/>
+      <c r="AV44" s="16"/>
+      <c r="AW44" s="16"/>
+      <c r="AX44" s="16"/>
+      <c r="AY44" s="16"/>
+      <c r="AZ44" s="16"/>
+      <c r="BA44" s="16"/>
+      <c r="BB44" s="16"/>
+      <c r="BC44" s="16"/>
+      <c r="BD44" s="1"/>
+      <c r="BE44" s="1"/>
+      <c r="BF44" s="1"/>
+      <c r="BG44" s="1"/>
+      <c r="BH44" s="1"/>
+      <c r="BI44" s="1"/>
+      <c r="BJ44" s="1"/>
+      <c r="BK44" s="1"/>
+      <c r="BL44" s="1"/>
+      <c r="BM44" s="1"/>
+      <c r="BN44" s="1"/>
+      <c r="BO44" s="1"/>
+      <c r="BP44" s="1"/>
+      <c r="BQ44" s="1"/>
+      <c r="BR44" s="1"/>
+      <c r="BS44" s="1"/>
+      <c r="BT44" s="1"/>
+      <c r="BU44" s="1"/>
+      <c r="BV44" s="1"/>
+      <c r="BW44" s="1"/>
+      <c r="BX44" s="1"/>
+      <c r="BY44" s="1"/>
+      <c r="BZ44" s="1"/>
+      <c r="CA44" s="1"/>
+      <c r="CB44" s="1"/>
+      <c r="CC44" s="1"/>
+      <c r="CD44" s="1"/>
+      <c r="CE44" s="1"/>
+      <c r="CF44" s="1"/>
+      <c r="CG44" s="1"/>
+      <c r="CH44" s="1"/>
+      <c r="CI44" s="1"/>
+      <c r="CJ44" s="1"/>
+      <c r="CK44" s="1"/>
+      <c r="CL44" s="1"/>
+      <c r="CM44" s="1"/>
+      <c r="CN44" s="1"/>
+      <c r="CO44" s="1"/>
+      <c r="CP44" s="1"/>
+      <c r="CQ44" s="1"/>
+      <c r="CR44" s="1"/>
+      <c r="CS44" s="1"/>
+      <c r="CT44" s="1"/>
+      <c r="CU44" s="1"/>
+      <c r="CV44" s="1"/>
+      <c r="CW44" s="1"/>
+      <c r="CX44" s="1"/>
+      <c r="CY44" s="1"/>
+      <c r="CZ44" s="1"/>
+      <c r="DA44" s="1"/>
+      <c r="DB44" s="1"/>
+      <c r="DC44" s="1"/>
+      <c r="DD44" s="1"/>
+      <c r="DE44" s="1"/>
+      <c r="DF44" s="1"/>
+      <c r="DG44" s="1"/>
+      <c r="DH44" s="1"/>
+      <c r="DI44" s="1"/>
+      <c r="DJ44" s="1"/>
+      <c r="DK44" s="1"/>
+      <c r="DL44" s="1"/>
+      <c r="DM44" s="1"/>
+      <c r="DN44" s="1"/>
+      <c r="DO44" s="1"/>
+      <c r="DP44" s="1"/>
+      <c r="DQ44" s="1"/>
+      <c r="DR44" s="1"/>
+      <c r="DS44" s="1"/>
+      <c r="DT44" s="1"/>
+      <c r="DU44" s="1"/>
+      <c r="DV44" s="1"/>
+      <c r="DW44" s="1"/>
+      <c r="DX44" s="1"/>
+      <c r="DY44" s="1"/>
+      <c r="DZ44" s="1"/>
+      <c r="EA44" s="1"/>
+      <c r="EB44" s="1"/>
+      <c r="EC44" s="1"/>
+      <c r="ED44" s="1"/>
+      <c r="EE44" s="1"/>
+      <c r="EF44" s="1"/>
+      <c r="EG44" s="1"/>
+      <c r="EH44" s="1"/>
+      <c r="EI44" s="1"/>
+      <c r="EJ44" s="1"/>
+      <c r="EK44" s="1"/>
+      <c r="EL44" s="1"/>
+      <c r="EM44" s="1"/>
+      <c r="EN44" s="1"/>
+      <c r="EO44" s="1"/>
+      <c r="EP44" s="1"/>
+      <c r="EQ44" s="1"/>
+      <c r="ER44" s="1"/>
+      <c r="ES44" s="1"/>
+      <c r="ET44" s="1"/>
+      <c r="EU44" s="1"/>
+      <c r="EV44" s="1"/>
+      <c r="EW44" s="1"/>
+      <c r="EX44" s="1"/>
+      <c r="EY44" s="1"/>
+      <c r="EZ44" s="1"/>
+      <c r="FA44" s="1"/>
+      <c r="FB44" s="1"/>
+      <c r="FC44" s="1"/>
+      <c r="FD44" s="1"/>
+      <c r="FE44" s="1"/>
+      <c r="FF44" s="1"/>
+      <c r="FG44" s="1"/>
+      <c r="FH44" s="1"/>
+      <c r="FI44" s="1"/>
+      <c r="FJ44" s="1"/>
+      <c r="FK44" s="1"/>
+      <c r="FL44" s="1"/>
+      <c r="FM44" s="1"/>
+      <c r="FN44" s="1"/>
+      <c r="FO44" s="1"/>
+      <c r="FP44" s="1"/>
+      <c r="FQ44" s="1"/>
+      <c r="FR44" s="1"/>
+      <c r="FS44" s="1"/>
+      <c r="FT44" s="1"/>
+      <c r="FU44" s="1"/>
+      <c r="FV44" s="1"/>
+      <c r="FW44" s="1"/>
+      <c r="FX44" s="1"/>
+      <c r="FY44" s="1"/>
+      <c r="FZ44" s="1"/>
+      <c r="GA44" s="1"/>
+      <c r="GB44" s="1"/>
+      <c r="GC44" s="1"/>
+      <c r="GD44" s="1"/>
+      <c r="GE44" s="1"/>
+    </row>
+    <row r="45" spans="1:187" ht="13.5" customHeight="1">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="3"/>
+      <c r="W45" s="3"/>
+      <c r="X45" s="3"/>
+      <c r="Y45" s="3"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
+      <c r="AB45" s="3"/>
+      <c r="AC45" s="3"/>
+      <c r="AD45" s="3"/>
+      <c r="AE45" s="3"/>
+      <c r="AF45" s="3"/>
+      <c r="AG45" s="3"/>
+      <c r="AH45" s="3"/>
+      <c r="AI45" s="3"/>
+      <c r="AJ45" s="3"/>
+      <c r="AK45" s="3"/>
+      <c r="AL45" s="3"/>
+      <c r="AM45" s="3"/>
+      <c r="AN45" s="3"/>
+      <c r="AO45" s="3"/>
+      <c r="AP45" s="3"/>
+      <c r="AQ45" s="3"/>
+      <c r="AR45" s="3"/>
+      <c r="AS45" s="3"/>
+      <c r="AT45" s="3"/>
+      <c r="AU45" s="3"/>
+      <c r="AV45" s="3"/>
+      <c r="AW45" s="3"/>
+      <c r="AX45" s="3"/>
+      <c r="AY45" s="3"/>
+      <c r="AZ45" s="3"/>
+      <c r="BA45" s="3"/>
+      <c r="BB45" s="3"/>
+      <c r="BC45" s="3"/>
+      <c r="BD45" s="1"/>
+      <c r="BE45" s="1"/>
+      <c r="BF45" s="1"/>
+      <c r="BG45" s="1"/>
+      <c r="BH45" s="1"/>
+      <c r="BI45" s="1"/>
+      <c r="BJ45" s="1"/>
+      <c r="BK45" s="1"/>
+      <c r="BL45" s="1"/>
+      <c r="BM45" s="1"/>
+      <c r="BN45" s="1"/>
+      <c r="BO45" s="1"/>
+      <c r="BP45" s="1"/>
+      <c r="BQ45" s="1"/>
+      <c r="BR45" s="1"/>
+      <c r="BS45" s="1"/>
+      <c r="BT45" s="1"/>
+      <c r="BU45" s="1"/>
+      <c r="BV45" s="1"/>
+      <c r="BW45" s="1"/>
+      <c r="BX45" s="1"/>
+      <c r="BY45" s="1"/>
+      <c r="BZ45" s="1"/>
+      <c r="CA45" s="1"/>
+      <c r="CB45" s="1"/>
+      <c r="CC45" s="1"/>
+      <c r="CD45" s="1"/>
+      <c r="CE45" s="1"/>
+      <c r="CF45" s="1"/>
+      <c r="CG45" s="1"/>
+      <c r="CH45" s="1"/>
+      <c r="CI45" s="1"/>
+      <c r="CJ45" s="1"/>
+      <c r="CK45" s="1"/>
+      <c r="CL45" s="1"/>
+      <c r="CM45" s="1"/>
+      <c r="CN45" s="1"/>
+      <c r="CO45" s="1"/>
+      <c r="CP45" s="1"/>
+      <c r="CQ45" s="1"/>
+      <c r="CR45" s="1"/>
+      <c r="CS45" s="1"/>
+      <c r="CT45" s="1"/>
+      <c r="CU45" s="1"/>
+      <c r="CV45" s="1"/>
+      <c r="CW45" s="1"/>
+      <c r="CX45" s="1"/>
+      <c r="CY45" s="1"/>
+      <c r="CZ45" s="1"/>
+      <c r="DA45" s="1"/>
+      <c r="DB45" s="1"/>
+      <c r="DC45" s="1"/>
+      <c r="DD45" s="1"/>
+      <c r="DE45" s="1"/>
+      <c r="DF45" s="1"/>
+      <c r="DG45" s="1"/>
+      <c r="DH45" s="1"/>
+      <c r="DI45" s="1"/>
+      <c r="DJ45" s="1"/>
+      <c r="DK45" s="1"/>
+      <c r="DL45" s="1"/>
+      <c r="DM45" s="1"/>
+      <c r="DN45" s="1"/>
+      <c r="DO45" s="1"/>
+      <c r="DP45" s="1"/>
+      <c r="DQ45" s="1"/>
+      <c r="DR45" s="1"/>
+      <c r="DS45" s="1"/>
+      <c r="DT45" s="1"/>
+      <c r="DU45" s="1"/>
+      <c r="DV45" s="1"/>
+      <c r="DW45" s="1"/>
+      <c r="DX45" s="1"/>
+      <c r="DY45" s="1"/>
+      <c r="DZ45" s="1"/>
+      <c r="EA45" s="1"/>
+      <c r="EB45" s="1"/>
+      <c r="EC45" s="1"/>
+      <c r="ED45" s="1"/>
+      <c r="EE45" s="1"/>
+      <c r="EF45" s="1"/>
+      <c r="EG45" s="1"/>
+      <c r="EH45" s="1"/>
+      <c r="EI45" s="1"/>
+      <c r="EJ45" s="1"/>
+      <c r="EK45" s="1"/>
+      <c r="EL45" s="1"/>
+      <c r="EM45" s="1"/>
+      <c r="EN45" s="1"/>
+      <c r="EO45" s="1"/>
+      <c r="EP45" s="1"/>
+      <c r="EQ45" s="1"/>
+      <c r="ER45" s="1"/>
+      <c r="ES45" s="1"/>
+      <c r="ET45" s="1"/>
+      <c r="EU45" s="1"/>
+      <c r="EV45" s="1"/>
+      <c r="EW45" s="1"/>
+      <c r="EX45" s="1"/>
+      <c r="EY45" s="1"/>
+      <c r="EZ45" s="1"/>
+      <c r="FA45" s="1"/>
+      <c r="FB45" s="1"/>
+      <c r="FC45" s="1"/>
+      <c r="FD45" s="1"/>
+      <c r="FE45" s="1"/>
+      <c r="FF45" s="1"/>
+      <c r="FG45" s="1"/>
+      <c r="FH45" s="1"/>
+      <c r="FI45" s="1"/>
+      <c r="FJ45" s="1"/>
+      <c r="FK45" s="1"/>
+      <c r="FL45" s="1"/>
+      <c r="FM45" s="1"/>
+      <c r="FN45" s="1"/>
+      <c r="FO45" s="1"/>
+      <c r="FP45" s="1"/>
+      <c r="FQ45" s="1"/>
+      <c r="FR45" s="1"/>
+      <c r="FS45" s="1"/>
+      <c r="FT45" s="1"/>
+      <c r="FU45" s="1"/>
+      <c r="FV45" s="1"/>
+      <c r="FW45" s="1"/>
+      <c r="FX45" s="1"/>
+      <c r="FY45" s="1"/>
+      <c r="FZ45" s="1"/>
+      <c r="GA45" s="1"/>
+      <c r="GB45" s="1"/>
+      <c r="GC45" s="1"/>
+      <c r="GD45" s="1"/>
+      <c r="GE45" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="184">
+    <mergeCell ref="AE22:BC23"/>
+    <mergeCell ref="A24:H25"/>
+    <mergeCell ref="I24:P25"/>
+    <mergeCell ref="Q24:V25"/>
+    <mergeCell ref="W24:AD25"/>
+    <mergeCell ref="AE24:BC25"/>
+    <mergeCell ref="A26:H27"/>
+    <mergeCell ref="AE26:BC27"/>
+    <mergeCell ref="W26:AD27"/>
+    <mergeCell ref="Q26:V27"/>
+    <mergeCell ref="I26:P27"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="I18:P18"/>
     <mergeCell ref="Q18:V18"/>
@@ -9355,12 +9999,6 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="I19:P19"/>
     <mergeCell ref="Q19:V19"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="I23:P23"/>
-    <mergeCell ref="Q23:V23"/>
-    <mergeCell ref="AE23:BC23"/>
-    <mergeCell ref="W24:AD24"/>
-    <mergeCell ref="W23:AD23"/>
     <mergeCell ref="W19:AD19"/>
     <mergeCell ref="AE19:BC19"/>
     <mergeCell ref="A20:H20"/>
@@ -9373,30 +10011,25 @@
     <mergeCell ref="Q21:V21"/>
     <mergeCell ref="W21:AD21"/>
     <mergeCell ref="AE21:BC21"/>
-    <mergeCell ref="AE22:BC22"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="AE27:BC27"/>
-    <mergeCell ref="W27:AD27"/>
-    <mergeCell ref="Q27:V27"/>
-    <mergeCell ref="I27:P27"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="AE24:BC24"/>
-    <mergeCell ref="AE25:BC25"/>
-    <mergeCell ref="AE26:BC26"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="I24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="I22:P22"/>
-    <mergeCell ref="Q22:V22"/>
-    <mergeCell ref="W22:AD22"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="I26:P26"/>
-    <mergeCell ref="Q26:V26"/>
-    <mergeCell ref="W26:AD26"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="I25:P25"/>
-    <mergeCell ref="Q25:V25"/>
-    <mergeCell ref="W25:AD25"/>
+    <mergeCell ref="AE30:BC30"/>
+    <mergeCell ref="W30:AD30"/>
+    <mergeCell ref="Q30:V30"/>
+    <mergeCell ref="I30:P30"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="AE28:BC28"/>
+    <mergeCell ref="AE29:BC29"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="I29:P29"/>
+    <mergeCell ref="Q29:V29"/>
+    <mergeCell ref="W29:AD29"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="I28:P28"/>
+    <mergeCell ref="Q28:V28"/>
+    <mergeCell ref="W28:AD28"/>
+    <mergeCell ref="A22:H23"/>
+    <mergeCell ref="I22:P23"/>
+    <mergeCell ref="Q22:V23"/>
+    <mergeCell ref="W22:AD23"/>
     <mergeCell ref="AX2:BC2"/>
     <mergeCell ref="AN1:AT1"/>
     <mergeCell ref="AU1:AW1"/>
@@ -9421,80 +10054,80 @@
     <mergeCell ref="AK1:AM1"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="AE7:BC8"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="I38:P38"/>
-    <mergeCell ref="Q38:V38"/>
-    <mergeCell ref="W38:AD38"/>
-    <mergeCell ref="W34:AD34"/>
-    <mergeCell ref="AE34:BC34"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="AE41:BC41"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="I39:P39"/>
-    <mergeCell ref="Q39:V39"/>
-    <mergeCell ref="W39:AD39"/>
-    <mergeCell ref="AE39:BC39"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="I41:P41"/>
     <mergeCell ref="Q41:V41"/>
     <mergeCell ref="W41:AD41"/>
+    <mergeCell ref="W37:AD37"/>
+    <mergeCell ref="AE37:BC37"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="AE44:BC44"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="I42:P42"/>
+    <mergeCell ref="Q42:V42"/>
+    <mergeCell ref="W42:AD42"/>
+    <mergeCell ref="AE42:BC42"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="I44:P44"/>
+    <mergeCell ref="Q44:V44"/>
+    <mergeCell ref="W44:AD44"/>
+    <mergeCell ref="Q39:V39"/>
+    <mergeCell ref="W39:AD39"/>
+    <mergeCell ref="I39:P39"/>
+    <mergeCell ref="AE39:BC39"/>
+    <mergeCell ref="I38:P38"/>
+    <mergeCell ref="Q38:V38"/>
+    <mergeCell ref="W38:AD38"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="I35:P35"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="I36:P36"/>
     <mergeCell ref="Q36:V36"/>
     <mergeCell ref="W36:AD36"/>
-    <mergeCell ref="I36:P36"/>
     <mergeCell ref="AE36:BC36"/>
-    <mergeCell ref="I35:P35"/>
-    <mergeCell ref="Q35:V35"/>
-    <mergeCell ref="W35:AD35"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="I32:P32"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="AE38:BC38"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="I37:P37"/>
+    <mergeCell ref="Q37:V37"/>
+    <mergeCell ref="AE34:BC34"/>
     <mergeCell ref="I33:P33"/>
     <mergeCell ref="Q33:V33"/>
     <mergeCell ref="W33:AD33"/>
+    <mergeCell ref="I31:P31"/>
+    <mergeCell ref="Q31:V31"/>
+    <mergeCell ref="W31:AD31"/>
     <mergeCell ref="AE33:BC33"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="AE31:BC31"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="I43:P43"/>
+    <mergeCell ref="Q43:V43"/>
+    <mergeCell ref="W43:AD43"/>
+    <mergeCell ref="AE43:BC43"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="I32:P32"/>
+    <mergeCell ref="Q32:V32"/>
+    <mergeCell ref="W32:AD32"/>
+    <mergeCell ref="AE32:BC32"/>
+    <mergeCell ref="AE41:BC41"/>
+    <mergeCell ref="Q35:V35"/>
+    <mergeCell ref="W35:AD35"/>
     <mergeCell ref="AE35:BC35"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="I34:P34"/>
-    <mergeCell ref="Q34:V34"/>
-    <mergeCell ref="AE31:BC31"/>
-    <mergeCell ref="I30:P30"/>
-    <mergeCell ref="Q30:V30"/>
-    <mergeCell ref="W30:AD30"/>
-    <mergeCell ref="I28:P28"/>
-    <mergeCell ref="Q28:V28"/>
-    <mergeCell ref="W28:AD28"/>
-    <mergeCell ref="AE30:BC30"/>
-    <mergeCell ref="AE28:BC28"/>
     <mergeCell ref="A40:H40"/>
     <mergeCell ref="I40:P40"/>
     <mergeCell ref="Q40:V40"/>
     <mergeCell ref="W40:AD40"/>
     <mergeCell ref="AE40:BC40"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="I29:P29"/>
-    <mergeCell ref="Q29:V29"/>
-    <mergeCell ref="W29:AD29"/>
-    <mergeCell ref="AE29:BC29"/>
-    <mergeCell ref="AE38:BC38"/>
-    <mergeCell ref="Q32:V32"/>
-    <mergeCell ref="W32:AD32"/>
-    <mergeCell ref="AE32:BC32"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="I37:P37"/>
-    <mergeCell ref="Q37:V37"/>
-    <mergeCell ref="W37:AD37"/>
-    <mergeCell ref="AE37:BC37"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="I31:P31"/>
-    <mergeCell ref="Q31:V31"/>
-    <mergeCell ref="W31:AD31"/>
-    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="I34:P34"/>
+    <mergeCell ref="Q34:V34"/>
+    <mergeCell ref="W34:AD34"/>
+    <mergeCell ref="A33:H33"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q9:Q13 Q15:Q41" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q9:Q13 Q15:Q22 Q24 Q26 Q28:Q44" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>部品種別</formula1>
     </dataValidation>
   </dataValidations>
@@ -9506,9 +10139,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -9565,6 +10198,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100F5656D937027614D93C88AB71AE3D10C" ma:contentTypeVersion="2" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="b60c200d0ae5f270a77b0ce61d313f15">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="75fae816-41bf-471e-909f-5205fc9f8b57" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="893732230ae29545b6addaf499a489b1" ns2:_="">
     <xsd:import namespace="75fae816-41bf-471e-909f-5205fc9f8b57"/>
@@ -9696,7 +10335,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -9705,13 +10344,16 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6750BA14-EF93-4A19-AEC6-7431BDBB93BF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{462924AE-F691-4F26-88D6-4B2DC7238578}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9729,19 +10371,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D8A1FDC-951E-4F8A-8B1E-600169D502EB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6750BA14-EF93-4A19-AEC6-7431BDBB93BF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>